--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132814790</v>
+        <v>132814710</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420678</v>
+        <v>420053</v>
       </c>
       <c r="R2" t="n">
-        <v>6794095</v>
+        <v>6793980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,41 +776,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132814785</v>
+        <v>132814771</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -826,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420460</v>
+        <v>420677</v>
       </c>
       <c r="R3" t="n">
-        <v>6794156</v>
+        <v>6794147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +863,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132814710</v>
+        <v>132814765</v>
       </c>
       <c r="B4" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,26 +892,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420053</v>
+        <v>420459</v>
       </c>
       <c r="R4" t="n">
-        <v>6793980</v>
+        <v>6794159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +968,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -990,40 +986,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132814771</v>
+        <v>132814790</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1033,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420677</v>
+        <v>420678</v>
       </c>
       <c r="R5" t="n">
-        <v>6794147</v>
+        <v>6794095</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1074,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,40 +1093,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132814765</v>
+        <v>132814785</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1138,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>420459</v>
+        <v>420460</v>
       </c>
       <c r="R6" t="n">
-        <v>6794159</v>
+        <v>6794156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132814738</v>
+        <v>132814846</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,42 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420583</v>
+        <v>420455</v>
       </c>
       <c r="R7" t="n">
-        <v>6794016</v>
+        <v>6794188</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132814744</v>
+        <v>132814738</v>
       </c>
       <c r="B8" t="n">
         <v>57953</v>
@@ -1348,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420576</v>
+        <v>420583</v>
       </c>
       <c r="R8" t="n">
-        <v>6794051</v>
+        <v>6794016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132814846</v>
+        <v>132814744</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420455</v>
+        <v>420576</v>
       </c>
       <c r="R9" t="n">
-        <v>6794188</v>
+        <v>6794051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814861</v>
+        <v>132814761</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,34 +2003,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420752</v>
+        <v>420119</v>
       </c>
       <c r="R15" t="n">
-        <v>6794099</v>
+        <v>6794010</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132814860</v>
+        <v>132814762</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,34 +2108,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420745</v>
+        <v>419986</v>
       </c>
       <c r="R16" t="n">
-        <v>6794098</v>
+        <v>6793995</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,10 +2202,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132814863</v>
+        <v>132814792</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,34 +2213,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420725</v>
+        <v>420554</v>
       </c>
       <c r="R17" t="n">
-        <v>6794081</v>
+        <v>6794096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,53 +2501,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132814773</v>
+        <v>132814861</v>
       </c>
       <c r="B20" t="n">
-        <v>57144</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>420920</v>
+        <v>420752</v>
       </c>
       <c r="R20" t="n">
-        <v>6794225</v>
+        <v>6794099</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,10 +2598,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814761</v>
+        <v>132814860</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,42 +2609,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420119</v>
+        <v>420745</v>
       </c>
       <c r="R21" t="n">
-        <v>6794010</v>
+        <v>6794098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814792</v>
+        <v>132814863</v>
       </c>
       <c r="B22" t="n">
-        <v>57132</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2698,42 +2706,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420554</v>
+        <v>420725</v>
       </c>
       <c r="R22" t="n">
-        <v>6794096</v>
+        <v>6794081</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,27 +2792,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132814762</v>
+        <v>132814773</v>
       </c>
       <c r="B23" t="n">
-        <v>57950</v>
+        <v>57144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2825,7 +2825,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419986</v>
+        <v>420920</v>
       </c>
       <c r="R23" t="n">
-        <v>6793995</v>
+        <v>6794225</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814865</v>
+        <v>132814715</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420586</v>
+        <v>420524</v>
       </c>
       <c r="R24" t="n">
-        <v>6794106</v>
+        <v>6794233</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814715</v>
+        <v>132814865</v>
       </c>
       <c r="B25" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420524</v>
+        <v>420586</v>
       </c>
       <c r="R25" t="n">
-        <v>6794233</v>
+        <v>6794106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,7 +3305,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132814864</v>
+        <v>132814832</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>420690</v>
+        <v>419983</v>
       </c>
       <c r="R28" t="n">
-        <v>6794088</v>
+        <v>6793990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132814844</v>
+        <v>132814706</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>420421</v>
+        <v>419997</v>
       </c>
       <c r="R29" t="n">
-        <v>6794149</v>
+        <v>6793998</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132814737</v>
+        <v>132814864</v>
       </c>
       <c r="B30" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3510,42 +3510,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>420586</v>
+        <v>420690</v>
       </c>
       <c r="R30" t="n">
-        <v>6794009</v>
+        <v>6794088</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132814728</v>
+        <v>132814844</v>
       </c>
       <c r="B31" t="n">
-        <v>79917</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3615,21 +3607,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3639,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>420875</v>
+        <v>420421</v>
       </c>
       <c r="R31" t="n">
-        <v>6794212</v>
+        <v>6794149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132814832</v>
+        <v>132814737</v>
       </c>
       <c r="B32" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,34 +3704,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419983</v>
+        <v>420586</v>
       </c>
       <c r="R32" t="n">
-        <v>6793990</v>
+        <v>6794009</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132814706</v>
+        <v>132814728</v>
       </c>
       <c r="B33" t="n">
-        <v>79946</v>
+        <v>79917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419997</v>
+        <v>420875</v>
       </c>
       <c r="R33" t="n">
-        <v>6793998</v>
+        <v>6794212</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132814741</v>
+        <v>132814828</v>
       </c>
       <c r="B34" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3906,42 +3906,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>420574</v>
+        <v>420306</v>
       </c>
       <c r="R34" t="n">
-        <v>6794086</v>
+        <v>6794101</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4000,10 +3992,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132814740</v>
+        <v>132814769</v>
       </c>
       <c r="B35" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,16 +4003,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4033,7 +4025,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4043,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>420104</v>
+        <v>420899</v>
       </c>
       <c r="R35" t="n">
-        <v>6794033</v>
+        <v>6794245</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4105,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132814828</v>
+        <v>132814741</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4116,34 +4108,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>420306</v>
+        <v>420574</v>
       </c>
       <c r="R36" t="n">
-        <v>6794101</v>
+        <v>6794086</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4202,10 +4202,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132814769</v>
+        <v>132814740</v>
       </c>
       <c r="B37" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4213,16 +4213,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4235,7 +4235,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>420899</v>
+        <v>420104</v>
       </c>
       <c r="R37" t="n">
-        <v>6794245</v>
+        <v>6794033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132814748</v>
+        <v>132814713</v>
       </c>
       <c r="B38" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4318,42 +4318,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420910</v>
+        <v>420131</v>
       </c>
       <c r="R38" t="n">
-        <v>6794235</v>
+        <v>6793962</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4412,10 +4404,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814767</v>
+        <v>132814701</v>
       </c>
       <c r="B39" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4423,42 +4415,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420588</v>
+        <v>420311</v>
       </c>
       <c r="R39" t="n">
-        <v>6794046</v>
+        <v>6794104</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,41 +4695,40 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814788</v>
+        <v>132814767</v>
       </c>
       <c r="B42" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4755,10 +4738,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420693</v>
+        <v>420588</v>
       </c>
       <c r="R42" t="n">
-        <v>6794082</v>
+        <v>6794046</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4799,7 +4782,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4818,41 +4800,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132814787</v>
+        <v>132814748</v>
       </c>
       <c r="B43" t="n">
-        <v>8455</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4862,10 +4843,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>420878</v>
+        <v>420910</v>
       </c>
       <c r="R43" t="n">
-        <v>6794218</v>
+        <v>6794235</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4906,7 +4887,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4925,45 +4905,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814713</v>
+        <v>132814788</v>
       </c>
       <c r="B44" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420131</v>
+        <v>420693</v>
       </c>
       <c r="R44" t="n">
-        <v>6793962</v>
+        <v>6794082</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5004,6 +4993,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5022,45 +5012,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814701</v>
+        <v>132814787</v>
       </c>
       <c r="B45" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420311</v>
+        <v>420878</v>
       </c>
       <c r="R45" t="n">
-        <v>6794104</v>
+        <v>6794218</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5101,6 +5100,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5515,54 +5515,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132814780</v>
+        <v>132814843</v>
       </c>
       <c r="B50" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>420313</v>
+        <v>420223</v>
       </c>
       <c r="R50" t="n">
-        <v>6794133</v>
+        <v>6793998</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5603,7 +5594,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5622,45 +5612,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132814843</v>
+        <v>132814780</v>
       </c>
       <c r="B51" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>420223</v>
+        <v>420313</v>
       </c>
       <c r="R51" t="n">
-        <v>6793998</v>
+        <v>6794133</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5701,6 +5700,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132814759</v>
+        <v>132814829</v>
       </c>
       <c r="B52" t="n">
-        <v>91930</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,37 +5730,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>420574</v>
+        <v>420188</v>
       </c>
       <c r="R52" t="n">
-        <v>6794086</v>
+        <v>6794047</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5801,7 +5798,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5820,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132814764</v>
+        <v>132814759</v>
       </c>
       <c r="B53" t="n">
-        <v>57950</v>
+        <v>91930</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5831,31 +5827,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5863,10 +5854,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>420073</v>
+        <v>420574</v>
       </c>
       <c r="R53" t="n">
-        <v>6793986</v>
+        <v>6794086</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5907,6 +5898,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5925,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814758</v>
+        <v>132814848</v>
       </c>
       <c r="B54" t="n">
-        <v>91930</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,37 +5928,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420939</v>
+        <v>420528</v>
       </c>
       <c r="R54" t="n">
-        <v>6794202</v>
+        <v>6794160</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6007,7 +5996,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6026,10 +6014,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132814829</v>
+        <v>132814758</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6037,34 +6025,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>420188</v>
+        <v>420939</v>
       </c>
       <c r="R55" t="n">
-        <v>6794047</v>
+        <v>6794202</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6105,6 +6096,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6123,10 +6115,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132814848</v>
+        <v>132814718</v>
       </c>
       <c r="B56" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6134,21 +6126,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6158,10 +6150,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>420528</v>
+        <v>420827</v>
       </c>
       <c r="R56" t="n">
-        <v>6794160</v>
+        <v>6794180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6220,10 +6212,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132814718</v>
+        <v>132814764</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6231,34 +6223,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>420827</v>
+        <v>420073</v>
       </c>
       <c r="R57" t="n">
-        <v>6794180</v>
+        <v>6793986</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132814729</v>
+        <v>132814837</v>
       </c>
       <c r="B58" t="n">
-        <v>79917</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>420826</v>
+        <v>420071</v>
       </c>
       <c r="R58" t="n">
-        <v>6794184</v>
+        <v>6793979</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6414,7 +6414,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132814837</v>
+        <v>132814853</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>420071</v>
+        <v>420890</v>
       </c>
       <c r="R59" t="n">
-        <v>6793979</v>
+        <v>6794166</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132814853</v>
+        <v>132814729</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>79917</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>420890</v>
+        <v>420826</v>
       </c>
       <c r="R60" t="n">
-        <v>6794166</v>
+        <v>6794184</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,53 +6608,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132814750</v>
+        <v>132814856</v>
       </c>
       <c r="B61" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>420114</v>
+        <v>420936</v>
       </c>
       <c r="R61" t="n">
-        <v>6793974</v>
+        <v>6794205</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6713,10 +6705,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132814856</v>
+        <v>132814704</v>
       </c>
       <c r="B62" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6724,21 +6716,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6748,10 +6740,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>420936</v>
+        <v>419964</v>
       </c>
       <c r="R62" t="n">
-        <v>6794205</v>
+        <v>6793993</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,45 +6802,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132814776</v>
+        <v>132814750</v>
       </c>
       <c r="B63" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>420807</v>
+        <v>420114</v>
       </c>
       <c r="R63" t="n">
-        <v>6794179</v>
+        <v>6793974</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132814704</v>
+        <v>132814776</v>
       </c>
       <c r="B64" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6918,21 +6918,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419964</v>
+        <v>420807</v>
       </c>
       <c r="R64" t="n">
-        <v>6793993</v>
+        <v>6794179</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7305,54 +7305,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132814791</v>
+        <v>132814716</v>
       </c>
       <c r="B68" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>420112</v>
+        <v>420748</v>
       </c>
       <c r="R68" t="n">
-        <v>6793976</v>
+        <v>6794107</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7393,7 +7384,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7412,7 +7402,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814716</v>
+        <v>132814719</v>
       </c>
       <c r="B69" t="n">
         <v>79946</v>
@@ -7447,10 +7437,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420748</v>
+        <v>420742</v>
       </c>
       <c r="R69" t="n">
-        <v>6794107</v>
+        <v>6794108</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7509,10 +7499,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132814794</v>
+        <v>132814766</v>
       </c>
       <c r="B70" t="n">
-        <v>56522</v>
+        <v>57950</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7520,21 +7510,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7542,7 +7532,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7552,10 +7542,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>420170</v>
+        <v>420516</v>
       </c>
       <c r="R70" t="n">
-        <v>6793954</v>
+        <v>6794196</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7614,45 +7604,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132814719</v>
+        <v>132814791</v>
       </c>
       <c r="B71" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>420742</v>
+        <v>420112</v>
       </c>
       <c r="R71" t="n">
-        <v>6794108</v>
+        <v>6793976</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7693,6 +7692,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814730</v>
+        <v>132814794</v>
       </c>
       <c r="B72" t="n">
-        <v>79917</v>
+        <v>56522</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,34 +7722,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>206004</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420787</v>
+        <v>420170</v>
       </c>
       <c r="R72" t="n">
-        <v>6794163</v>
+        <v>6793954</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7808,7 +7816,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132814727</v>
+        <v>132814730</v>
       </c>
       <c r="B73" t="n">
         <v>79917</v>
@@ -7843,10 +7851,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>420903</v>
+        <v>420787</v>
       </c>
       <c r="R73" t="n">
-        <v>6794237</v>
+        <v>6794163</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7905,10 +7913,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132814766</v>
+        <v>132814727</v>
       </c>
       <c r="B74" t="n">
-        <v>57950</v>
+        <v>79917</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7916,42 +7924,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>420516</v>
+        <v>420903</v>
       </c>
       <c r="R74" t="n">
-        <v>6794196</v>
+        <v>6794237</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132814770</v>
+        <v>132814775</v>
       </c>
       <c r="B75" t="n">
-        <v>57950</v>
+        <v>79085</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8021,31 +8021,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8053,10 +8048,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>420758</v>
+        <v>420905</v>
       </c>
       <c r="R75" t="n">
-        <v>6794147</v>
+        <v>6794232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8097,6 +8092,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8115,10 +8111,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132814775</v>
+        <v>132814726</v>
       </c>
       <c r="B76" t="n">
-        <v>79085</v>
+        <v>79917</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8126,37 +8122,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>420905</v>
+        <v>420503</v>
       </c>
       <c r="R76" t="n">
-        <v>6794232</v>
+        <v>6794242</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8197,7 +8190,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8216,10 +8208,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132814726</v>
+        <v>132814845</v>
       </c>
       <c r="B77" t="n">
-        <v>79917</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8227,21 +8219,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8251,10 +8243,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>420503</v>
+        <v>420474</v>
       </c>
       <c r="R77" t="n">
-        <v>6794242</v>
+        <v>6794142</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8313,10 +8305,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132814845</v>
+        <v>132814714</v>
       </c>
       <c r="B78" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8324,21 +8316,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8348,10 +8340,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>420474</v>
+        <v>420233</v>
       </c>
       <c r="R78" t="n">
-        <v>6794142</v>
+        <v>6793967</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8410,41 +8402,40 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132814781</v>
+        <v>132814770</v>
       </c>
       <c r="B79" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8454,10 +8445,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>420113</v>
+        <v>420758</v>
       </c>
       <c r="R79" t="n">
-        <v>6794031</v>
+        <v>6794147</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8498,7 +8489,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8517,45 +8507,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132814714</v>
+        <v>132814781</v>
       </c>
       <c r="B80" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>420233</v>
+        <v>420113</v>
       </c>
       <c r="R80" t="n">
-        <v>6793967</v>
+        <v>6794031</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8596,6 +8595,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8740,54 +8740,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132814783</v>
+        <v>132814723</v>
       </c>
       <c r="B82" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>420406</v>
+        <v>420646</v>
       </c>
       <c r="R82" t="n">
-        <v>6794117</v>
+        <v>6794161</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8828,7 +8819,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8847,10 +8837,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132814723</v>
+        <v>132814840</v>
       </c>
       <c r="B83" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8858,21 +8848,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8882,10 +8872,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>420646</v>
+        <v>420214</v>
       </c>
       <c r="R83" t="n">
-        <v>6794161</v>
+        <v>6793964</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8944,7 +8934,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132814840</v>
+        <v>132814830</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -8979,10 +8969,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>420214</v>
+        <v>420156</v>
       </c>
       <c r="R84" t="n">
-        <v>6793964</v>
+        <v>6794036</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9041,45 +9031,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132814830</v>
+        <v>132814783</v>
       </c>
       <c r="B85" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>420156</v>
+        <v>420406</v>
       </c>
       <c r="R85" t="n">
-        <v>6794036</v>
+        <v>6794117</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9120,6 +9119,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132814735</v>
+        <v>132814836</v>
       </c>
       <c r="B92" t="n">
-        <v>79917</v>
+        <v>79327</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9741,37 +9741,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>420683</v>
+        <v>420025</v>
       </c>
       <c r="R92" t="n">
-        <v>6794145</v>
+        <v>6793989</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9812,7 +9809,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9831,10 +9827,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132814725</v>
+        <v>132814849</v>
       </c>
       <c r="B93" t="n">
-        <v>79917</v>
+        <v>79327</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9842,21 +9838,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9866,10 +9862,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>420114</v>
+        <v>420548</v>
       </c>
       <c r="R93" t="n">
-        <v>6793974</v>
+        <v>6794121</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9928,10 +9924,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132814836</v>
+        <v>132814735</v>
       </c>
       <c r="B94" t="n">
-        <v>79327</v>
+        <v>79917</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9939,34 +9935,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>420025</v>
+        <v>420683</v>
       </c>
       <c r="R94" t="n">
-        <v>6793989</v>
+        <v>6794145</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10007,6 +10006,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10025,10 +10025,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132814849</v>
+        <v>132814725</v>
       </c>
       <c r="B95" t="n">
-        <v>79327</v>
+        <v>79917</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10036,21 +10036,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>420548</v>
+        <v>420114</v>
       </c>
       <c r="R95" t="n">
-        <v>6794121</v>
+        <v>6793974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10122,53 +10122,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132814751</v>
+        <v>132814852</v>
       </c>
       <c r="B96" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>420599</v>
+        <v>420835</v>
       </c>
       <c r="R96" t="n">
-        <v>6794022</v>
+        <v>6794144</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10227,32 +10219,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132814742</v>
+        <v>132814749</v>
       </c>
       <c r="B97" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10260,7 +10252,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10270,10 +10262,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>420570</v>
+        <v>420604</v>
       </c>
       <c r="R97" t="n">
-        <v>6794049</v>
+        <v>6794012</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10332,53 +10324,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132814749</v>
+        <v>132814851</v>
       </c>
       <c r="B98" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>420604</v>
+        <v>420801</v>
       </c>
       <c r="R98" t="n">
-        <v>6794012</v>
+        <v>6794114</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10437,54 +10421,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132814782</v>
+        <v>132814724</v>
       </c>
       <c r="B99" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>420074</v>
+        <v>420166</v>
       </c>
       <c r="R99" t="n">
-        <v>6793987</v>
+        <v>6793967</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10525,7 +10500,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10544,10 +10518,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132814852</v>
+        <v>132814721</v>
       </c>
       <c r="B100" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10555,21 +10529,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10579,10 +10553,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>420835</v>
+        <v>420709</v>
       </c>
       <c r="R100" t="n">
-        <v>6794144</v>
+        <v>6794077</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10641,45 +10615,53 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132814851</v>
+        <v>132814751</v>
       </c>
       <c r="B101" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>420801</v>
+        <v>420599</v>
       </c>
       <c r="R101" t="n">
-        <v>6794114</v>
+        <v>6794022</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10738,10 +10720,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132814724</v>
+        <v>132814742</v>
       </c>
       <c r="B102" t="n">
-        <v>79946</v>
+        <v>57953</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10749,34 +10731,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>420166</v>
+        <v>420570</v>
       </c>
       <c r="R102" t="n">
-        <v>6793967</v>
+        <v>6794049</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10835,45 +10825,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132814721</v>
+        <v>132814782</v>
       </c>
       <c r="B103" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>420709</v>
+        <v>420074</v>
       </c>
       <c r="R103" t="n">
-        <v>6794077</v>
+        <v>6793987</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10914,6 +10913,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132814768</v>
+        <v>132814859</v>
       </c>
       <c r="B104" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10943,42 +10943,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>420900</v>
+        <v>420739</v>
       </c>
       <c r="R104" t="n">
-        <v>6794252</v>
+        <v>6794114</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11037,10 +11029,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132814859</v>
+        <v>132814709</v>
       </c>
       <c r="B105" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11048,21 +11040,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11072,10 +11064,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>420739</v>
+        <v>420028</v>
       </c>
       <c r="R105" t="n">
-        <v>6794114</v>
+        <v>6793991</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11134,10 +11126,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132814777</v>
+        <v>132814768</v>
       </c>
       <c r="B106" t="n">
-        <v>79085</v>
+        <v>57950</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11145,34 +11137,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>420706</v>
+        <v>420900</v>
       </c>
       <c r="R106" t="n">
-        <v>6794078</v>
+        <v>6794252</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11231,10 +11231,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132814709</v>
+        <v>132814777</v>
       </c>
       <c r="B107" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11242,21 +11242,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11266,10 +11266,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>420028</v>
+        <v>420706</v>
       </c>
       <c r="R107" t="n">
-        <v>6793991</v>
+        <v>6794078</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -675,37 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132814710</v>
+        <v>132814790</v>
       </c>
       <c r="B2" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420053</v>
+        <v>420678</v>
       </c>
       <c r="R2" t="n">
-        <v>6793980</v>
+        <v>6794095</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132814771</v>
+        <v>132814710</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,31 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420677</v>
+        <v>420053</v>
       </c>
       <c r="R3" t="n">
-        <v>6794147</v>
+        <v>6793980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -881,7 +883,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132814765</v>
+        <v>132814771</v>
       </c>
       <c r="B4" t="n">
         <v>57950</v>
@@ -914,7 +916,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -924,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420459</v>
+        <v>420677</v>
       </c>
       <c r="R4" t="n">
-        <v>6794159</v>
+        <v>6794147</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,41 +988,40 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132814790</v>
+        <v>132814765</v>
       </c>
       <c r="B5" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1030,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420678</v>
+        <v>420459</v>
       </c>
       <c r="R5" t="n">
-        <v>6794095</v>
+        <v>6794159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1075,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132814846</v>
+        <v>132814738</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1211,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420455</v>
+        <v>420583</v>
       </c>
       <c r="R7" t="n">
-        <v>6794188</v>
+        <v>6794016</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132814738</v>
+        <v>132814744</v>
       </c>
       <c r="B8" t="n">
         <v>57953</v>
@@ -1340,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420583</v>
+        <v>420576</v>
       </c>
       <c r="R8" t="n">
-        <v>6794016</v>
+        <v>6794051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132814744</v>
+        <v>132814846</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1421,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420576</v>
+        <v>420455</v>
       </c>
       <c r="R9" t="n">
-        <v>6794051</v>
+        <v>6794188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132814837</v>
+        <v>132814729</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>79917</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>420071</v>
+        <v>420826</v>
       </c>
       <c r="R58" t="n">
-        <v>6793979</v>
+        <v>6794184</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6414,7 +6414,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132814853</v>
+        <v>132814837</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>420890</v>
+        <v>420071</v>
       </c>
       <c r="R59" t="n">
-        <v>6794166</v>
+        <v>6793979</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132814729</v>
+        <v>132814853</v>
       </c>
       <c r="B60" t="n">
-        <v>79917</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>420826</v>
+        <v>420890</v>
       </c>
       <c r="R60" t="n">
-        <v>6794184</v>
+        <v>6794166</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132814775</v>
+        <v>132814845</v>
       </c>
       <c r="B75" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8021,37 +8021,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>420905</v>
+        <v>420474</v>
       </c>
       <c r="R75" t="n">
-        <v>6794232</v>
+        <v>6794142</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8092,7 +8089,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8111,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132814726</v>
+        <v>132814714</v>
       </c>
       <c r="B76" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8122,21 +8118,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8146,10 +8142,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>420503</v>
+        <v>420233</v>
       </c>
       <c r="R76" t="n">
-        <v>6794242</v>
+        <v>6793967</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8208,45 +8204,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132814845</v>
+        <v>132814781</v>
       </c>
       <c r="B77" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>420474</v>
+        <v>420113</v>
       </c>
       <c r="R77" t="n">
-        <v>6794142</v>
+        <v>6794031</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8287,6 +8292,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8305,10 +8311,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132814714</v>
+        <v>132814770</v>
       </c>
       <c r="B78" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8316,34 +8322,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>420233</v>
+        <v>420758</v>
       </c>
       <c r="R78" t="n">
-        <v>6793967</v>
+        <v>6794147</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8402,10 +8416,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132814770</v>
+        <v>132814775</v>
       </c>
       <c r="B79" t="n">
-        <v>57950</v>
+        <v>79085</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8413,31 +8427,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8445,10 +8454,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>420758</v>
+        <v>420905</v>
       </c>
       <c r="R79" t="n">
-        <v>6794147</v>
+        <v>6794232</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8489,6 +8498,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8507,54 +8517,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132814781</v>
+        <v>132814726</v>
       </c>
       <c r="B80" t="n">
-        <v>8455</v>
+        <v>79917</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>420113</v>
+        <v>420503</v>
       </c>
       <c r="R80" t="n">
-        <v>6794031</v>
+        <v>6794242</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8595,7 +8596,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132814790</v>
+        <v>132814771</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>57951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420678</v>
+        <v>420677</v>
       </c>
       <c r="R2" t="n">
-        <v>6794095</v>
+        <v>6794147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132814710</v>
+        <v>132814765</v>
       </c>
       <c r="B3" t="n">
-        <v>79946</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,26 +791,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420053</v>
+        <v>420459</v>
       </c>
       <c r="R3" t="n">
-        <v>6793980</v>
+        <v>6794159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +867,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132814771</v>
+        <v>132814710</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>79947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,31 +896,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420677</v>
+        <v>420053</v>
       </c>
       <c r="R4" t="n">
-        <v>6794147</v>
+        <v>6793980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +967,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -988,40 +986,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132814765</v>
+        <v>132814790</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1031,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420459</v>
+        <v>420678</v>
       </c>
       <c r="R5" t="n">
-        <v>6794159</v>
+        <v>6794095</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,6 +1074,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>132814738</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>132814744</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>132814846</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>132814705</v>
       </c>
       <c r="B10" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>132814839</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>132814831</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>132814827</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132814732</v>
+        <v>132814711</v>
       </c>
       <c r="B14" t="n">
-        <v>79917</v>
+        <v>79947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,21 +1906,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420740</v>
+        <v>420109</v>
       </c>
       <c r="R14" t="n">
-        <v>6794120</v>
+        <v>6793976</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814761</v>
+        <v>132814712</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>79947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,42 +2003,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420119</v>
+        <v>420126</v>
       </c>
       <c r="R15" t="n">
-        <v>6794010</v>
+        <v>6793969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132814762</v>
+        <v>132814861</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>79328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,42 +2100,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419986</v>
+        <v>420752</v>
       </c>
       <c r="R16" t="n">
-        <v>6793995</v>
+        <v>6794099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132814792</v>
+        <v>132814860</v>
       </c>
       <c r="B17" t="n">
-        <v>57132</v>
+        <v>79328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2213,42 +2197,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420554</v>
+        <v>420745</v>
       </c>
       <c r="R17" t="n">
-        <v>6794096</v>
+        <v>6794098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2283,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132814711</v>
+        <v>132814863</v>
       </c>
       <c r="B18" t="n">
-        <v>79946</v>
+        <v>79328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2318,21 +2294,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2342,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>420109</v>
+        <v>420725</v>
       </c>
       <c r="R18" t="n">
-        <v>6793976</v>
+        <v>6794081</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2380,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132814712</v>
+        <v>132814761</v>
       </c>
       <c r="B19" t="n">
-        <v>79946</v>
+        <v>57951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,34 +2391,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420126</v>
+        <v>420119</v>
       </c>
       <c r="R19" t="n">
-        <v>6793969</v>
+        <v>6794010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132814861</v>
+        <v>132814762</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>57951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2512,34 +2496,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>420752</v>
+        <v>419986</v>
       </c>
       <c r="R20" t="n">
-        <v>6794099</v>
+        <v>6793995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814860</v>
+        <v>132814792</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>57133</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,34 +2601,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420745</v>
+        <v>420554</v>
       </c>
       <c r="R21" t="n">
-        <v>6794098</v>
+        <v>6794096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,45 +2695,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814863</v>
+        <v>132814773</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>57145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420725</v>
+        <v>420920</v>
       </c>
       <c r="R22" t="n">
-        <v>6794081</v>
+        <v>6794225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,53 +2800,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132814773</v>
+        <v>132814732</v>
       </c>
       <c r="B23" t="n">
-        <v>57144</v>
+        <v>79918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>420920</v>
+        <v>420740</v>
       </c>
       <c r="R23" t="n">
-        <v>6794225</v>
+        <v>6794120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,45 +2897,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814715</v>
+        <v>132814786</v>
       </c>
       <c r="B24" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420524</v>
+        <v>420459</v>
       </c>
       <c r="R24" t="n">
-        <v>6794233</v>
+        <v>6794178</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,6 +2985,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2994,45 +3004,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814865</v>
+        <v>132814784</v>
       </c>
       <c r="B25" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420586</v>
+        <v>420420</v>
       </c>
       <c r="R25" t="n">
-        <v>6794106</v>
+        <v>6794140</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3073,6 +3092,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3091,54 +3111,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132814786</v>
+        <v>132814715</v>
       </c>
       <c r="B26" t="n">
-        <v>8455</v>
+        <v>79947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>420459</v>
+        <v>420524</v>
       </c>
       <c r="R26" t="n">
-        <v>6794178</v>
+        <v>6794233</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,7 +3190,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3198,54 +3208,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132814784</v>
+        <v>132814865</v>
       </c>
       <c r="B27" t="n">
-        <v>8455</v>
+        <v>79328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>420420</v>
+        <v>420586</v>
       </c>
       <c r="R27" t="n">
-        <v>6794140</v>
+        <v>6794106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3286,7 +3287,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132814832</v>
+        <v>132814737</v>
       </c>
       <c r="B28" t="n">
-        <v>79327</v>
+        <v>57954</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3316,34 +3316,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419983</v>
+        <v>420586</v>
       </c>
       <c r="R28" t="n">
-        <v>6793990</v>
+        <v>6794009</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3402,10 +3410,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132814706</v>
+        <v>132814728</v>
       </c>
       <c r="B29" t="n">
-        <v>79946</v>
+        <v>79918</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3421,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3445,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419997</v>
+        <v>420875</v>
       </c>
       <c r="R29" t="n">
-        <v>6793998</v>
+        <v>6794212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,10 +3507,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132814864</v>
+        <v>132814832</v>
       </c>
       <c r="B30" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3534,10 +3542,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>420690</v>
+        <v>419983</v>
       </c>
       <c r="R30" t="n">
-        <v>6794088</v>
+        <v>6793990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,10 +3604,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132814844</v>
+        <v>132814706</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>79947</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,21 +3615,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3631,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>420421</v>
+        <v>419997</v>
       </c>
       <c r="R31" t="n">
-        <v>6794149</v>
+        <v>6793998</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132814737</v>
+        <v>132814864</v>
       </c>
       <c r="B32" t="n">
-        <v>57953</v>
+        <v>79328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,42 +3712,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>420586</v>
+        <v>420690</v>
       </c>
       <c r="R32" t="n">
-        <v>6794009</v>
+        <v>6794088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132814728</v>
+        <v>132814844</v>
       </c>
       <c r="B33" t="n">
-        <v>79917</v>
+        <v>79328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>420875</v>
+        <v>420421</v>
       </c>
       <c r="R33" t="n">
-        <v>6794212</v>
+        <v>6794149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3898,7 +3898,7 @@
         <v>132814828</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>132814769</v>
       </c>
       <c r="B35" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>132814741</v>
       </c>
       <c r="B36" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>132814740</v>
       </c>
       <c r="B37" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132814713</v>
+        <v>132814767</v>
       </c>
       <c r="B38" t="n">
-        <v>79946</v>
+        <v>57951</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4318,34 +4318,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420131</v>
+        <v>420588</v>
       </c>
       <c r="R38" t="n">
-        <v>6793962</v>
+        <v>6794046</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4404,10 +4412,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814701</v>
+        <v>132814847</v>
       </c>
       <c r="B39" t="n">
-        <v>79946</v>
+        <v>79328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4415,21 +4423,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4439,10 +4447,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420311</v>
+        <v>420443</v>
       </c>
       <c r="R39" t="n">
-        <v>6794104</v>
+        <v>6794222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4501,10 +4509,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132814847</v>
+        <v>132814838</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4536,10 +4544,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>420443</v>
+        <v>420073</v>
       </c>
       <c r="R40" t="n">
-        <v>6794222</v>
+        <v>6793986</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4598,10 +4606,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132814838</v>
+        <v>132814713</v>
       </c>
       <c r="B41" t="n">
-        <v>79327</v>
+        <v>79947</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4609,21 +4617,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4641,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>420073</v>
+        <v>420131</v>
       </c>
       <c r="R41" t="n">
-        <v>6793986</v>
+        <v>6793962</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,10 +4703,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814767</v>
+        <v>132814701</v>
       </c>
       <c r="B42" t="n">
-        <v>57950</v>
+        <v>79947</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,42 +4714,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420588</v>
+        <v>420311</v>
       </c>
       <c r="R42" t="n">
-        <v>6794046</v>
+        <v>6794104</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>132814748</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,40 +5119,41 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132814763</v>
+        <v>132814780</v>
       </c>
       <c r="B46" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5162,10 +5163,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>420057</v>
+        <v>420313</v>
       </c>
       <c r="R46" t="n">
-        <v>6793966</v>
+        <v>6794133</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5206,6 +5207,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5224,10 +5226,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132814857</v>
+        <v>132814763</v>
       </c>
       <c r="B47" t="n">
-        <v>79327</v>
+        <v>57951</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5235,34 +5237,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>420920</v>
+        <v>420057</v>
       </c>
       <c r="R47" t="n">
-        <v>6794226</v>
+        <v>6793966</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5321,10 +5331,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132814858</v>
+        <v>132814857</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5356,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>420778</v>
+        <v>420920</v>
       </c>
       <c r="R48" t="n">
-        <v>6794174</v>
+        <v>6794226</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5418,10 +5428,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132814841</v>
+        <v>132814858</v>
       </c>
       <c r="B49" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5453,10 +5463,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>420224</v>
+        <v>420778</v>
       </c>
       <c r="R49" t="n">
-        <v>6793969</v>
+        <v>6794174</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5515,10 +5525,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132814843</v>
+        <v>132814841</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5550,10 +5560,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>420223</v>
+        <v>420224</v>
       </c>
       <c r="R50" t="n">
-        <v>6793998</v>
+        <v>6793969</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5612,54 +5622,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132814780</v>
+        <v>132814843</v>
       </c>
       <c r="B51" t="n">
-        <v>8455</v>
+        <v>79328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>420313</v>
+        <v>420223</v>
       </c>
       <c r="R51" t="n">
-        <v>6794133</v>
+        <v>6793998</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5700,7 +5701,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132814829</v>
+        <v>132814764</v>
       </c>
       <c r="B52" t="n">
-        <v>79327</v>
+        <v>57951</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,34 +5730,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>420188</v>
+        <v>420073</v>
       </c>
       <c r="R52" t="n">
-        <v>6794047</v>
+        <v>6793986</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5816,10 +5824,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132814759</v>
+        <v>132814829</v>
       </c>
       <c r="B53" t="n">
-        <v>91930</v>
+        <v>79328</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,37 +5835,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>420574</v>
+        <v>420188</v>
       </c>
       <c r="R53" t="n">
-        <v>6794086</v>
+        <v>6794047</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5903,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5917,10 +5921,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814848</v>
+        <v>132814759</v>
       </c>
       <c r="B54" t="n">
-        <v>79327</v>
+        <v>91931</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5928,34 +5932,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420528</v>
+        <v>420574</v>
       </c>
       <c r="R54" t="n">
-        <v>6794160</v>
+        <v>6794086</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5996,6 +6003,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6014,10 +6022,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132814758</v>
+        <v>132814848</v>
       </c>
       <c r="B55" t="n">
-        <v>91930</v>
+        <v>79328</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6025,37 +6033,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>420939</v>
+        <v>420528</v>
       </c>
       <c r="R55" t="n">
-        <v>6794202</v>
+        <v>6794160</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6096,7 +6101,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6115,10 +6119,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132814718</v>
+        <v>132814758</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>91931</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6126,34 +6130,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>420827</v>
+        <v>420939</v>
       </c>
       <c r="R56" t="n">
-        <v>6794180</v>
+        <v>6794202</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6194,6 +6201,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6212,10 +6220,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132814764</v>
+        <v>132814718</v>
       </c>
       <c r="B57" t="n">
-        <v>57950</v>
+        <v>79947</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6223,42 +6231,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>420073</v>
+        <v>420827</v>
       </c>
       <c r="R57" t="n">
-        <v>6793986</v>
+        <v>6794180</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132814729</v>
+        <v>132814837</v>
       </c>
       <c r="B58" t="n">
-        <v>79917</v>
+        <v>79328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>420826</v>
+        <v>420071</v>
       </c>
       <c r="R58" t="n">
-        <v>6794184</v>
+        <v>6793979</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132814837</v>
+        <v>132814853</v>
       </c>
       <c r="B59" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>420071</v>
+        <v>420890</v>
       </c>
       <c r="R59" t="n">
-        <v>6793979</v>
+        <v>6794166</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132814853</v>
+        <v>132814729</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>79918</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>420890</v>
+        <v>420826</v>
       </c>
       <c r="R60" t="n">
-        <v>6794166</v>
+        <v>6794184</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6611,7 +6611,7 @@
         <v>132814856</v>
       </c>
       <c r="B61" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>132814704</v>
       </c>
       <c r="B62" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>132814750</v>
       </c>
       <c r="B63" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>132814776</v>
       </c>
       <c r="B64" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7004,54 +7004,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132814789</v>
+        <v>132814720</v>
       </c>
       <c r="B65" t="n">
-        <v>8455</v>
+        <v>79947</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>420681</v>
+        <v>420755</v>
       </c>
       <c r="R65" t="n">
-        <v>6794073</v>
+        <v>6794087</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7092,7 +7083,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7111,45 +7101,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132814720</v>
+        <v>132814789</v>
       </c>
       <c r="B66" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>420755</v>
+        <v>420681</v>
       </c>
       <c r="R66" t="n">
-        <v>6794087</v>
+        <v>6794073</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,6 +7189,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132814826</v>
+        <v>132814794</v>
       </c>
       <c r="B67" t="n">
-        <v>79327</v>
+        <v>56522</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7219,34 +7219,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>420418</v>
+        <v>420170</v>
       </c>
       <c r="R67" t="n">
-        <v>6794158</v>
+        <v>6793954</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7305,10 +7313,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132814716</v>
+        <v>132814766</v>
       </c>
       <c r="B68" t="n">
-        <v>79946</v>
+        <v>57951</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7316,34 +7324,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>420748</v>
+        <v>420516</v>
       </c>
       <c r="R68" t="n">
-        <v>6794107</v>
+        <v>6794196</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7402,10 +7418,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814719</v>
+        <v>132814826</v>
       </c>
       <c r="B69" t="n">
-        <v>79946</v>
+        <v>79328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7413,21 +7429,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7437,10 +7453,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420742</v>
+        <v>420418</v>
       </c>
       <c r="R69" t="n">
-        <v>6794108</v>
+        <v>6794158</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7499,10 +7515,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132814766</v>
+        <v>132814716</v>
       </c>
       <c r="B70" t="n">
-        <v>57950</v>
+        <v>79947</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7510,42 +7526,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>420516</v>
+        <v>420748</v>
       </c>
       <c r="R70" t="n">
-        <v>6794196</v>
+        <v>6794107</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7604,54 +7612,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132814791</v>
+        <v>132814719</v>
       </c>
       <c r="B71" t="n">
-        <v>8455</v>
+        <v>79947</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>420112</v>
+        <v>420742</v>
       </c>
       <c r="R71" t="n">
-        <v>6793976</v>
+        <v>6794108</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7692,7 +7691,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7711,40 +7709,41 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814794</v>
+        <v>132814791</v>
       </c>
       <c r="B72" t="n">
-        <v>56522</v>
+        <v>8455</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -7754,10 +7753,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420170</v>
+        <v>420112</v>
       </c>
       <c r="R72" t="n">
-        <v>6793954</v>
+        <v>6793976</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7798,6 +7797,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>132814730</v>
       </c>
       <c r="B73" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>132814727</v>
       </c>
       <c r="B74" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132814845</v>
+        <v>132814770</v>
       </c>
       <c r="B75" t="n">
-        <v>79327</v>
+        <v>57951</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8021,34 +8021,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>420474</v>
+        <v>420758</v>
       </c>
       <c r="R75" t="n">
-        <v>6794142</v>
+        <v>6794147</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8107,10 +8115,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132814714</v>
+        <v>132814845</v>
       </c>
       <c r="B76" t="n">
-        <v>79946</v>
+        <v>79328</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,21 +8126,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8150,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>420233</v>
+        <v>420474</v>
       </c>
       <c r="R76" t="n">
-        <v>6793967</v>
+        <v>6794142</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8204,54 +8212,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132814781</v>
+        <v>132814714</v>
       </c>
       <c r="B77" t="n">
-        <v>8455</v>
+        <v>79947</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>420113</v>
+        <v>420233</v>
       </c>
       <c r="R77" t="n">
-        <v>6794031</v>
+        <v>6793967</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8292,7 +8291,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8311,40 +8309,41 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132814770</v>
+        <v>132814781</v>
       </c>
       <c r="B78" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8354,10 +8353,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>420758</v>
+        <v>420113</v>
       </c>
       <c r="R78" t="n">
-        <v>6794147</v>
+        <v>6794031</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8398,6 +8397,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>132814775</v>
       </c>
       <c r="B79" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>132814726</v>
       </c>
       <c r="B80" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8614,37 +8614,43 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132814866</v>
+        <v>132814783</v>
       </c>
       <c r="B81" t="n">
-        <v>78334</v>
+        <v>8455</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8652,10 +8658,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>420768</v>
+        <v>420406</v>
       </c>
       <c r="R81" t="n">
-        <v>6794178</v>
+        <v>6794117</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8699,31 +8705,6 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -8740,45 +8721,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132814723</v>
+        <v>132814779</v>
       </c>
       <c r="B82" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>420646</v>
+        <v>420605</v>
       </c>
       <c r="R82" t="n">
-        <v>6794161</v>
+        <v>6794008</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8819,6 +8809,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8837,10 +8828,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132814840</v>
+        <v>132814866</v>
       </c>
       <c r="B83" t="n">
-        <v>79327</v>
+        <v>78335</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8848,34 +8839,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>420214</v>
+        <v>420768</v>
       </c>
       <c r="R83" t="n">
-        <v>6793964</v>
+        <v>6794178</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8916,8 +8910,34 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -8934,10 +8954,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132814830</v>
+        <v>132814723</v>
       </c>
       <c r="B84" t="n">
-        <v>79327</v>
+        <v>79947</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8945,21 +8965,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8969,10 +8989,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>420156</v>
+        <v>420646</v>
       </c>
       <c r="R84" t="n">
-        <v>6794036</v>
+        <v>6794161</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9031,54 +9051,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132814783</v>
+        <v>132814840</v>
       </c>
       <c r="B85" t="n">
-        <v>8455</v>
+        <v>79328</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>420406</v>
+        <v>420214</v>
       </c>
       <c r="R85" t="n">
-        <v>6794117</v>
+        <v>6793964</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9119,7 +9130,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9138,54 +9148,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132814779</v>
+        <v>132814830</v>
       </c>
       <c r="B86" t="n">
-        <v>8455</v>
+        <v>79328</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>420605</v>
+        <v>420156</v>
       </c>
       <c r="R86" t="n">
-        <v>6794008</v>
+        <v>6794036</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9226,7 +9227,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>132814702</v>
       </c>
       <c r="B87" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>132814850</v>
       </c>
       <c r="B88" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>132814833</v>
       </c>
       <c r="B89" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>132814734</v>
       </c>
       <c r="B90" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>132814731</v>
       </c>
       <c r="B91" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132814836</v>
+        <v>132814735</v>
       </c>
       <c r="B92" t="n">
-        <v>79327</v>
+        <v>79918</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9741,34 +9741,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>420025</v>
+        <v>420683</v>
       </c>
       <c r="R92" t="n">
-        <v>6793989</v>
+        <v>6794145</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9809,6 +9812,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9827,10 +9831,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132814849</v>
+        <v>132814725</v>
       </c>
       <c r="B93" t="n">
-        <v>79327</v>
+        <v>79918</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9838,21 +9842,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9862,10 +9866,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>420548</v>
+        <v>420114</v>
       </c>
       <c r="R93" t="n">
-        <v>6794121</v>
+        <v>6793974</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9924,10 +9928,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132814735</v>
+        <v>132814836</v>
       </c>
       <c r="B94" t="n">
-        <v>79917</v>
+        <v>79328</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9935,37 +9939,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>420683</v>
+        <v>420025</v>
       </c>
       <c r="R94" t="n">
-        <v>6794145</v>
+        <v>6793989</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10006,7 +10007,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10025,10 +10025,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132814725</v>
+        <v>132814849</v>
       </c>
       <c r="B95" t="n">
-        <v>79917</v>
+        <v>79328</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10036,21 +10036,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>420114</v>
+        <v>420548</v>
       </c>
       <c r="R95" t="n">
-        <v>6793974</v>
+        <v>6794121</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10122,45 +10122,53 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132814852</v>
+        <v>132814751</v>
       </c>
       <c r="B96" t="n">
-        <v>79327</v>
+        <v>57142</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>420835</v>
+        <v>420599</v>
       </c>
       <c r="R96" t="n">
-        <v>6794144</v>
+        <v>6794022</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10222,7 +10230,7 @@
         <v>132814749</v>
       </c>
       <c r="B97" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10324,10 +10332,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132814851</v>
+        <v>132814852</v>
       </c>
       <c r="B98" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10359,10 +10367,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>420801</v>
+        <v>420835</v>
       </c>
       <c r="R98" t="n">
-        <v>6794114</v>
+        <v>6794144</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10421,10 +10429,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132814724</v>
+        <v>132814851</v>
       </c>
       <c r="B99" t="n">
-        <v>79946</v>
+        <v>79328</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10432,21 +10440,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10456,10 +10464,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>420166</v>
+        <v>420801</v>
       </c>
       <c r="R99" t="n">
-        <v>6793967</v>
+        <v>6794114</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10518,10 +10526,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132814721</v>
+        <v>132814724</v>
       </c>
       <c r="B100" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10553,10 +10561,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>420709</v>
+        <v>420166</v>
       </c>
       <c r="R100" t="n">
-        <v>6794077</v>
+        <v>6793967</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10615,53 +10623,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132814751</v>
+        <v>132814721</v>
       </c>
       <c r="B101" t="n">
-        <v>57141</v>
+        <v>79947</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>420599</v>
+        <v>420709</v>
       </c>
       <c r="R101" t="n">
-        <v>6794022</v>
+        <v>6794077</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10723,7 +10723,7 @@
         <v>132814742</v>
       </c>
       <c r="B102" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132814859</v>
+        <v>132814768</v>
       </c>
       <c r="B104" t="n">
-        <v>79327</v>
+        <v>57951</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10943,34 +10943,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>420739</v>
+        <v>420900</v>
       </c>
       <c r="R104" t="n">
-        <v>6794114</v>
+        <v>6794252</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11029,10 +11037,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132814709</v>
+        <v>132814859</v>
       </c>
       <c r="B105" t="n">
-        <v>79946</v>
+        <v>79328</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11040,21 +11048,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11064,10 +11072,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>420028</v>
+        <v>420739</v>
       </c>
       <c r="R105" t="n">
-        <v>6793991</v>
+        <v>6794114</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11126,10 +11134,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132814768</v>
+        <v>132814709</v>
       </c>
       <c r="B106" t="n">
-        <v>57950</v>
+        <v>79947</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11137,42 +11145,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>420900</v>
+        <v>420028</v>
       </c>
       <c r="R106" t="n">
-        <v>6794252</v>
+        <v>6793991</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11234,7 +11234,7 @@
         <v>132814777</v>
       </c>
       <c r="B107" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11325,6 +11325,741 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>132814815</v>
+      </c>
+      <c r="B108" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Floj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>420901</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6794246</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>132814820</v>
+      </c>
+      <c r="B109" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Floj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>420740</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6794115</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>132814801</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Floj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>420233</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6793977</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>132814805</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Floj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>420522</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6794224</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>132814811</v>
+      </c>
+      <c r="B112" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Floj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>420631</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6794041</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>132814823</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Floj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>420695</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6794083</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>132814812</v>
+      </c>
+      <c r="B114" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Floj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>420621</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6794058</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132814738</v>
+        <v>132814846</v>
       </c>
       <c r="B7" t="n">
-        <v>57954</v>
+        <v>79328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,42 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420583</v>
+        <v>420455</v>
       </c>
       <c r="R7" t="n">
-        <v>6794016</v>
+        <v>6794188</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132814744</v>
+        <v>132814738</v>
       </c>
       <c r="B8" t="n">
         <v>57954</v>
@@ -1348,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420576</v>
+        <v>420583</v>
       </c>
       <c r="R8" t="n">
-        <v>6794051</v>
+        <v>6794016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132814846</v>
+        <v>132814744</v>
       </c>
       <c r="B9" t="n">
-        <v>79328</v>
+        <v>57954</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420455</v>
+        <v>420576</v>
       </c>
       <c r="R9" t="n">
-        <v>6794188</v>
+        <v>6794051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132814705</v>
+        <v>132814831</v>
       </c>
       <c r="B10" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419964</v>
+        <v>420020</v>
       </c>
       <c r="R10" t="n">
-        <v>6793990</v>
+        <v>6794011</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132814839</v>
+        <v>132814827</v>
       </c>
       <c r="B11" t="n">
         <v>79328</v>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>420171</v>
+        <v>420331</v>
       </c>
       <c r="R11" t="n">
-        <v>6793959</v>
+        <v>6794169</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132814831</v>
+        <v>132814839</v>
       </c>
       <c r="B12" t="n">
         <v>79328</v>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>420020</v>
+        <v>420171</v>
       </c>
       <c r="R12" t="n">
-        <v>6794011</v>
+        <v>6793959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132814827</v>
+        <v>132814705</v>
       </c>
       <c r="B13" t="n">
-        <v>79328</v>
+        <v>79947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>420331</v>
+        <v>419964</v>
       </c>
       <c r="R13" t="n">
-        <v>6794169</v>
+        <v>6793990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132814711</v>
+        <v>132814732</v>
       </c>
       <c r="B14" t="n">
-        <v>79947</v>
+        <v>79918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,21 +1906,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420109</v>
+        <v>420740</v>
       </c>
       <c r="R14" t="n">
-        <v>6793976</v>
+        <v>6794120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814712</v>
+        <v>132814861</v>
       </c>
       <c r="B15" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420126</v>
+        <v>420752</v>
       </c>
       <c r="R15" t="n">
-        <v>6793969</v>
+        <v>6794099</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132814861</v>
+        <v>132814863</v>
       </c>
       <c r="B16" t="n">
         <v>79328</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420752</v>
+        <v>420725</v>
       </c>
       <c r="R16" t="n">
-        <v>6794099</v>
+        <v>6794081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132814860</v>
+        <v>132814761</v>
       </c>
       <c r="B17" t="n">
-        <v>79328</v>
+        <v>57951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,34 +2197,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420745</v>
+        <v>420119</v>
       </c>
       <c r="R17" t="n">
-        <v>6794098</v>
+        <v>6794010</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2283,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132814863</v>
+        <v>132814762</v>
       </c>
       <c r="B18" t="n">
-        <v>79328</v>
+        <v>57951</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2294,34 +2302,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>420725</v>
+        <v>419986</v>
       </c>
       <c r="R18" t="n">
-        <v>6794081</v>
+        <v>6793995</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,10 +2396,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132814761</v>
+        <v>132814860</v>
       </c>
       <c r="B19" t="n">
-        <v>57951</v>
+        <v>79328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,42 +2407,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420119</v>
+        <v>420745</v>
       </c>
       <c r="R19" t="n">
-        <v>6794010</v>
+        <v>6794098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,27 +2493,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132814762</v>
+        <v>132814773</v>
       </c>
       <c r="B20" t="n">
-        <v>57951</v>
+        <v>57145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2518,7 +2526,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2528,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419986</v>
+        <v>420920</v>
       </c>
       <c r="R20" t="n">
-        <v>6793995</v>
+        <v>6794225</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,53 +2703,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814773</v>
+        <v>132814711</v>
       </c>
       <c r="B22" t="n">
-        <v>57145</v>
+        <v>79947</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420920</v>
+        <v>420109</v>
       </c>
       <c r="R22" t="n">
-        <v>6794225</v>
+        <v>6793976</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132814732</v>
+        <v>132814712</v>
       </c>
       <c r="B23" t="n">
-        <v>79918</v>
+        <v>79947</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>420740</v>
+        <v>420126</v>
       </c>
       <c r="R23" t="n">
-        <v>6794120</v>
+        <v>6793969</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,54 +2897,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814786</v>
+        <v>132814865</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>79328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420459</v>
+        <v>420586</v>
       </c>
       <c r="R24" t="n">
-        <v>6794178</v>
+        <v>6794106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2985,7 +2976,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3004,54 +2994,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814784</v>
+        <v>132814715</v>
       </c>
       <c r="B25" t="n">
-        <v>8455</v>
+        <v>79947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420420</v>
+        <v>420524</v>
       </c>
       <c r="R25" t="n">
-        <v>6794140</v>
+        <v>6794233</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3092,7 +3073,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3111,45 +3091,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132814715</v>
+        <v>132814786</v>
       </c>
       <c r="B26" t="n">
-        <v>79947</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>420524</v>
+        <v>420459</v>
       </c>
       <c r="R26" t="n">
-        <v>6794233</v>
+        <v>6794178</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3179,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3208,45 +3198,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132814865</v>
+        <v>132814784</v>
       </c>
       <c r="B27" t="n">
-        <v>79328</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>420586</v>
+        <v>420420</v>
       </c>
       <c r="R27" t="n">
-        <v>6794106</v>
+        <v>6794140</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3287,6 +3286,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132814737</v>
+        <v>132814864</v>
       </c>
       <c r="B28" t="n">
-        <v>57954</v>
+        <v>79328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3316,42 +3316,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>420586</v>
+        <v>420690</v>
       </c>
       <c r="R28" t="n">
-        <v>6794009</v>
+        <v>6794088</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3410,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132814728</v>
+        <v>132814832</v>
       </c>
       <c r="B29" t="n">
-        <v>79918</v>
+        <v>79328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3421,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3445,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>420875</v>
+        <v>419983</v>
       </c>
       <c r="R29" t="n">
-        <v>6794212</v>
+        <v>6793990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3507,7 +3499,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132814832</v>
+        <v>132814844</v>
       </c>
       <c r="B30" t="n">
         <v>79328</v>
@@ -3542,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419983</v>
+        <v>420421</v>
       </c>
       <c r="R30" t="n">
-        <v>6793990</v>
+        <v>6794149</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3701,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132814864</v>
+        <v>132814737</v>
       </c>
       <c r="B32" t="n">
-        <v>79328</v>
+        <v>57954</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,34 +3704,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>420690</v>
+        <v>420586</v>
       </c>
       <c r="R32" t="n">
-        <v>6794088</v>
+        <v>6794009</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132814844</v>
+        <v>132814728</v>
       </c>
       <c r="B33" t="n">
-        <v>79328</v>
+        <v>79918</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>420421</v>
+        <v>420875</v>
       </c>
       <c r="R33" t="n">
-        <v>6794149</v>
+        <v>6794212</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4307,40 +4307,41 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132814767</v>
+        <v>132814788</v>
       </c>
       <c r="B38" t="n">
-        <v>57951</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4350,10 +4351,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420588</v>
+        <v>420693</v>
       </c>
       <c r="R38" t="n">
-        <v>6794046</v>
+        <v>6794082</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4394,6 +4395,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4412,45 +4414,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814847</v>
+        <v>132814787</v>
       </c>
       <c r="B39" t="n">
-        <v>79328</v>
+        <v>8455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420443</v>
+        <v>420878</v>
       </c>
       <c r="R39" t="n">
-        <v>6794222</v>
+        <v>6794218</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4491,6 +4502,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4509,7 +4521,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132814838</v>
+        <v>132814847</v>
       </c>
       <c r="B40" t="n">
         <v>79328</v>
@@ -4544,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>420073</v>
+        <v>420443</v>
       </c>
       <c r="R40" t="n">
-        <v>6793986</v>
+        <v>6794222</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4606,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132814713</v>
+        <v>132814748</v>
       </c>
       <c r="B41" t="n">
-        <v>79947</v>
+        <v>57954</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4617,34 +4629,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>420131</v>
+        <v>420910</v>
       </c>
       <c r="R41" t="n">
-        <v>6793962</v>
+        <v>6794235</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4703,10 +4723,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814701</v>
+        <v>132814838</v>
       </c>
       <c r="B42" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4714,21 +4734,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4738,10 +4758,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420311</v>
+        <v>420073</v>
       </c>
       <c r="R42" t="n">
-        <v>6794104</v>
+        <v>6793986</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4800,10 +4820,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132814748</v>
+        <v>132814713</v>
       </c>
       <c r="B43" t="n">
-        <v>57954</v>
+        <v>79947</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4811,42 +4831,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>420910</v>
+        <v>420131</v>
       </c>
       <c r="R43" t="n">
-        <v>6794235</v>
+        <v>6793962</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4905,54 +4917,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814788</v>
+        <v>132814701</v>
       </c>
       <c r="B44" t="n">
-        <v>8455</v>
+        <v>79947</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420693</v>
+        <v>420311</v>
       </c>
       <c r="R44" t="n">
-        <v>6794082</v>
+        <v>6794104</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4993,7 +4996,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5012,41 +5014,40 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814787</v>
+        <v>132814767</v>
       </c>
       <c r="B45" t="n">
-        <v>8455</v>
+        <v>57951</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5056,10 +5057,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420878</v>
+        <v>420588</v>
       </c>
       <c r="R45" t="n">
-        <v>6794218</v>
+        <v>6794046</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,7 +5101,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5119,54 +5119,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132814780</v>
+        <v>132814857</v>
       </c>
       <c r="B46" t="n">
-        <v>8455</v>
+        <v>79328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>420313</v>
+        <v>420920</v>
       </c>
       <c r="R46" t="n">
-        <v>6794133</v>
+        <v>6794226</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5207,7 +5198,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5226,10 +5216,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132814763</v>
+        <v>132814858</v>
       </c>
       <c r="B47" t="n">
-        <v>57951</v>
+        <v>79328</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,42 +5227,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>420057</v>
+        <v>420778</v>
       </c>
       <c r="R47" t="n">
-        <v>6793966</v>
+        <v>6794174</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5331,45 +5313,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132814857</v>
+        <v>132814780</v>
       </c>
       <c r="B48" t="n">
-        <v>79328</v>
+        <v>8455</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>420920</v>
+        <v>420313</v>
       </c>
       <c r="R48" t="n">
-        <v>6794226</v>
+        <v>6794133</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5410,6 +5401,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5428,10 +5420,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132814858</v>
+        <v>132814763</v>
       </c>
       <c r="B49" t="n">
-        <v>79328</v>
+        <v>57951</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5439,34 +5431,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>420778</v>
+        <v>420057</v>
       </c>
       <c r="R49" t="n">
-        <v>6794174</v>
+        <v>6793966</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132814764</v>
+        <v>132814759</v>
       </c>
       <c r="B52" t="n">
-        <v>57951</v>
+        <v>91933</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,31 +5730,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5762,10 +5757,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>420073</v>
+        <v>420574</v>
       </c>
       <c r="R52" t="n">
-        <v>6793986</v>
+        <v>6794086</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5806,6 +5801,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5824,10 +5820,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132814829</v>
+        <v>132814758</v>
       </c>
       <c r="B53" t="n">
-        <v>79328</v>
+        <v>91933</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5835,34 +5831,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>420188</v>
+        <v>420939</v>
       </c>
       <c r="R53" t="n">
-        <v>6794047</v>
+        <v>6794202</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5903,6 +5902,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814759</v>
+        <v>132814829</v>
       </c>
       <c r="B54" t="n">
-        <v>91931</v>
+        <v>79328</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5932,37 +5932,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420574</v>
+        <v>420188</v>
       </c>
       <c r="R54" t="n">
-        <v>6794086</v>
+        <v>6794047</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6003,7 +6000,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6119,10 +6115,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132814758</v>
+        <v>132814764</v>
       </c>
       <c r="B56" t="n">
-        <v>91931</v>
+        <v>57951</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6130,26 +6126,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6157,10 +6158,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>420939</v>
+        <v>420073</v>
       </c>
       <c r="R56" t="n">
-        <v>6794202</v>
+        <v>6793986</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6201,7 +6202,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132814856</v>
+        <v>132814776</v>
       </c>
       <c r="B61" t="n">
-        <v>79328</v>
+        <v>79086</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>420936</v>
+        <v>420807</v>
       </c>
       <c r="R61" t="n">
-        <v>6794205</v>
+        <v>6794179</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132814704</v>
+        <v>132814856</v>
       </c>
       <c r="B62" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6716,21 +6716,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419964</v>
+        <v>420936</v>
       </c>
       <c r="R62" t="n">
-        <v>6793993</v>
+        <v>6794205</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6802,53 +6802,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132814750</v>
+        <v>132814704</v>
       </c>
       <c r="B63" t="n">
-        <v>57142</v>
+        <v>79947</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>420114</v>
+        <v>419964</v>
       </c>
       <c r="R63" t="n">
-        <v>6793974</v>
+        <v>6793993</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,45 +6899,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132814776</v>
+        <v>132814750</v>
       </c>
       <c r="B64" t="n">
-        <v>79086</v>
+        <v>57142</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>420807</v>
+        <v>420114</v>
       </c>
       <c r="R64" t="n">
-        <v>6794179</v>
+        <v>6793974</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132814794</v>
+        <v>132814719</v>
       </c>
       <c r="B67" t="n">
-        <v>56522</v>
+        <v>79947</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7219,42 +7219,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>206004</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>420170</v>
+        <v>420742</v>
       </c>
       <c r="R67" t="n">
-        <v>6793954</v>
+        <v>6794108</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7313,10 +7305,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132814766</v>
+        <v>132814794</v>
       </c>
       <c r="B68" t="n">
-        <v>57951</v>
+        <v>56522</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7324,21 +7316,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7346,7 +7338,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7356,10 +7348,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>420516</v>
+        <v>420170</v>
       </c>
       <c r="R68" t="n">
-        <v>6794196</v>
+        <v>6793954</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7418,45 +7410,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814826</v>
+        <v>132814791</v>
       </c>
       <c r="B69" t="n">
-        <v>79328</v>
+        <v>8455</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420418</v>
+        <v>420112</v>
       </c>
       <c r="R69" t="n">
-        <v>6794158</v>
+        <v>6793976</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7497,6 +7498,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7515,10 +7517,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132814716</v>
+        <v>132814826</v>
       </c>
       <c r="B70" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7526,21 +7528,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7550,10 +7552,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>420748</v>
+        <v>420418</v>
       </c>
       <c r="R70" t="n">
-        <v>6794107</v>
+        <v>6794158</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7612,7 +7614,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132814719</v>
+        <v>132814716</v>
       </c>
       <c r="B71" t="n">
         <v>79947</v>
@@ -7647,10 +7649,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>420742</v>
+        <v>420748</v>
       </c>
       <c r="R71" t="n">
-        <v>6794108</v>
+        <v>6794107</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7709,41 +7711,40 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814791</v>
+        <v>132814766</v>
       </c>
       <c r="B72" t="n">
-        <v>8455</v>
+        <v>57951</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -7753,10 +7754,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420112</v>
+        <v>420516</v>
       </c>
       <c r="R72" t="n">
-        <v>6793976</v>
+        <v>6794196</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7797,7 +7798,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132814770</v>
+        <v>132814714</v>
       </c>
       <c r="B75" t="n">
-        <v>57951</v>
+        <v>79947</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8021,42 +8021,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>420758</v>
+        <v>420233</v>
       </c>
       <c r="R75" t="n">
-        <v>6794147</v>
+        <v>6793967</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8212,10 +8204,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132814714</v>
+        <v>132814770</v>
       </c>
       <c r="B77" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8223,34 +8215,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>420233</v>
+        <v>420758</v>
       </c>
       <c r="R77" t="n">
-        <v>6793967</v>
+        <v>6794147</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8614,54 +8614,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132814783</v>
+        <v>132814830</v>
       </c>
       <c r="B81" t="n">
-        <v>8455</v>
+        <v>79328</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>420406</v>
+        <v>420156</v>
       </c>
       <c r="R81" t="n">
-        <v>6794117</v>
+        <v>6794036</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8702,7 +8693,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8721,7 +8711,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132814779</v>
+        <v>132814783</v>
       </c>
       <c r="B82" t="n">
         <v>8455</v>
@@ -8765,10 +8755,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>420605</v>
+        <v>420406</v>
       </c>
       <c r="R82" t="n">
-        <v>6794008</v>
+        <v>6794117</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9148,45 +9138,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132814830</v>
+        <v>132814779</v>
       </c>
       <c r="B86" t="n">
-        <v>79328</v>
+        <v>8455</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>420156</v>
+        <v>420605</v>
       </c>
       <c r="R86" t="n">
-        <v>6794036</v>
+        <v>6794008</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9227,6 +9226,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132814702</v>
+        <v>132814833</v>
       </c>
       <c r="B87" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,21 +9256,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>420119</v>
+        <v>419996</v>
       </c>
       <c r="R87" t="n">
-        <v>6794012</v>
+        <v>6793995</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132814850</v>
+        <v>132814702</v>
       </c>
       <c r="B88" t="n">
-        <v>79328</v>
+        <v>79947</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9353,21 +9353,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9377,10 +9377,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>420549</v>
+        <v>420119</v>
       </c>
       <c r="R88" t="n">
-        <v>6794103</v>
+        <v>6794012</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9439,7 +9439,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132814833</v>
+        <v>132814850</v>
       </c>
       <c r="B89" t="n">
         <v>79328</v>
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419996</v>
+        <v>420549</v>
       </c>
       <c r="R89" t="n">
-        <v>6793995</v>
+        <v>6794103</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132814735</v>
+        <v>132814836</v>
       </c>
       <c r="B92" t="n">
-        <v>79918</v>
+        <v>79328</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9741,37 +9741,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>420683</v>
+        <v>420025</v>
       </c>
       <c r="R92" t="n">
-        <v>6794145</v>
+        <v>6793989</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9812,7 +9809,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9831,10 +9827,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132814725</v>
+        <v>132814849</v>
       </c>
       <c r="B93" t="n">
-        <v>79918</v>
+        <v>79328</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9842,21 +9838,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9866,10 +9862,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>420114</v>
+        <v>420548</v>
       </c>
       <c r="R93" t="n">
-        <v>6793974</v>
+        <v>6794121</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9928,10 +9924,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132814836</v>
+        <v>132814725</v>
       </c>
       <c r="B94" t="n">
-        <v>79328</v>
+        <v>79918</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9939,21 +9935,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9963,10 +9959,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>420025</v>
+        <v>420114</v>
       </c>
       <c r="R94" t="n">
-        <v>6793989</v>
+        <v>6793974</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10025,10 +10021,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132814849</v>
+        <v>132814735</v>
       </c>
       <c r="B95" t="n">
-        <v>79328</v>
+        <v>79918</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10036,34 +10032,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>420548</v>
+        <v>420683</v>
       </c>
       <c r="R95" t="n">
-        <v>6794121</v>
+        <v>6794145</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10104,6 +10103,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10122,53 +10122,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132814751</v>
+        <v>132814852</v>
       </c>
       <c r="B96" t="n">
-        <v>57142</v>
+        <v>79328</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>420599</v>
+        <v>420835</v>
       </c>
       <c r="R96" t="n">
-        <v>6794022</v>
+        <v>6794144</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10227,53 +10219,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132814749</v>
+        <v>132814851</v>
       </c>
       <c r="B97" t="n">
-        <v>57142</v>
+        <v>79328</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>420604</v>
+        <v>420801</v>
       </c>
       <c r="R97" t="n">
-        <v>6794012</v>
+        <v>6794114</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10332,10 +10316,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132814852</v>
+        <v>132814742</v>
       </c>
       <c r="B98" t="n">
-        <v>79328</v>
+        <v>57954</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10343,34 +10327,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>420835</v>
+        <v>420570</v>
       </c>
       <c r="R98" t="n">
-        <v>6794144</v>
+        <v>6794049</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10429,45 +10421,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132814851</v>
+        <v>132814782</v>
       </c>
       <c r="B99" t="n">
-        <v>79328</v>
+        <v>8455</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>420801</v>
+        <v>420074</v>
       </c>
       <c r="R99" t="n">
-        <v>6794114</v>
+        <v>6793987</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10508,6 +10509,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10720,32 +10722,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132814742</v>
+        <v>132814749</v>
       </c>
       <c r="B102" t="n">
-        <v>57954</v>
+        <v>57142</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10753,7 +10755,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -10763,10 +10765,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>420570</v>
+        <v>420604</v>
       </c>
       <c r="R102" t="n">
-        <v>6794049</v>
+        <v>6794012</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10825,10 +10827,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132814782</v>
+        <v>132814751</v>
       </c>
       <c r="B103" t="n">
-        <v>8455</v>
+        <v>57142</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10836,30 +10838,29 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -10869,10 +10870,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>420074</v>
+        <v>420599</v>
       </c>
       <c r="R103" t="n">
-        <v>6793987</v>
+        <v>6794022</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10913,7 +10914,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132814768</v>
+        <v>132814859</v>
       </c>
       <c r="B104" t="n">
-        <v>57951</v>
+        <v>79328</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10943,42 +10943,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>420900</v>
+        <v>420739</v>
       </c>
       <c r="R104" t="n">
-        <v>6794252</v>
+        <v>6794114</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11037,10 +11029,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132814859</v>
+        <v>132814777</v>
       </c>
       <c r="B105" t="n">
-        <v>79328</v>
+        <v>79086</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11048,21 +11040,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11072,10 +11064,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>420739</v>
+        <v>420706</v>
       </c>
       <c r="R105" t="n">
-        <v>6794114</v>
+        <v>6794078</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11231,10 +11223,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132814777</v>
+        <v>132814768</v>
       </c>
       <c r="B107" t="n">
-        <v>79086</v>
+        <v>57951</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11242,34 +11234,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>420706</v>
+        <v>420900</v>
       </c>
       <c r="R107" t="n">
-        <v>6794078</v>
+        <v>6794252</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>132814710</v>
       </c>
       <c r="B4" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>132814846</v>
       </c>
       <c r="B7" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132814831</v>
+        <v>132814705</v>
       </c>
       <c r="B10" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>420020</v>
+        <v>419964</v>
       </c>
       <c r="R10" t="n">
-        <v>6794011</v>
+        <v>6793990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132814827</v>
+        <v>132814839</v>
       </c>
       <c r="B11" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>420331</v>
+        <v>420171</v>
       </c>
       <c r="R11" t="n">
-        <v>6794169</v>
+        <v>6793959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132814839</v>
+        <v>132814831</v>
       </c>
       <c r="B12" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>420171</v>
+        <v>420020</v>
       </c>
       <c r="R12" t="n">
-        <v>6793959</v>
+        <v>6794011</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132814705</v>
+        <v>132814827</v>
       </c>
       <c r="B13" t="n">
-        <v>79947</v>
+        <v>79329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419964</v>
+        <v>420331</v>
       </c>
       <c r="R13" t="n">
-        <v>6793990</v>
+        <v>6794169</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132814732</v>
+        <v>132814711</v>
       </c>
       <c r="B14" t="n">
-        <v>79918</v>
+        <v>79948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,21 +1906,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420740</v>
+        <v>420109</v>
       </c>
       <c r="R14" t="n">
-        <v>6794120</v>
+        <v>6793976</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814861</v>
+        <v>132814712</v>
       </c>
       <c r="B15" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420752</v>
+        <v>420126</v>
       </c>
       <c r="R15" t="n">
-        <v>6794099</v>
+        <v>6793969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132814863</v>
+        <v>132814861</v>
       </c>
       <c r="B16" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420725</v>
+        <v>420752</v>
       </c>
       <c r="R16" t="n">
-        <v>6794081</v>
+        <v>6794099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132814761</v>
+        <v>132814860</v>
       </c>
       <c r="B17" t="n">
-        <v>57951</v>
+        <v>79329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,42 +2197,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420119</v>
+        <v>420745</v>
       </c>
       <c r="R17" t="n">
-        <v>6794010</v>
+        <v>6794098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,10 +2283,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132814762</v>
+        <v>132814863</v>
       </c>
       <c r="B18" t="n">
-        <v>57951</v>
+        <v>79329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,42 +2294,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>419986</v>
+        <v>420725</v>
       </c>
       <c r="R18" t="n">
-        <v>6793995</v>
+        <v>6794081</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,10 +2380,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132814860</v>
+        <v>132814792</v>
       </c>
       <c r="B19" t="n">
-        <v>79328</v>
+        <v>57133</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2407,34 +2391,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420745</v>
+        <v>420554</v>
       </c>
       <c r="R19" t="n">
-        <v>6794098</v>
+        <v>6794096</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814792</v>
+        <v>132814732</v>
       </c>
       <c r="B21" t="n">
-        <v>57133</v>
+        <v>79919</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,42 +2601,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420554</v>
+        <v>420740</v>
       </c>
       <c r="R21" t="n">
-        <v>6794096</v>
+        <v>6794120</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,10 +2687,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814711</v>
+        <v>132814761</v>
       </c>
       <c r="B22" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2714,34 +2698,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420109</v>
+        <v>420119</v>
       </c>
       <c r="R22" t="n">
-        <v>6793976</v>
+        <v>6794010</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2800,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132814712</v>
+        <v>132814762</v>
       </c>
       <c r="B23" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2811,34 +2803,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>420126</v>
+        <v>419986</v>
       </c>
       <c r="R23" t="n">
-        <v>6793969</v>
+        <v>6793995</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814865</v>
+        <v>132814715</v>
       </c>
       <c r="B24" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420586</v>
+        <v>420524</v>
       </c>
       <c r="R24" t="n">
-        <v>6794106</v>
+        <v>6794233</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814715</v>
+        <v>132814865</v>
       </c>
       <c r="B25" t="n">
-        <v>79947</v>
+        <v>79329</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420524</v>
+        <v>420586</v>
       </c>
       <c r="R25" t="n">
-        <v>6794233</v>
+        <v>6794106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132814864</v>
+        <v>132814728</v>
       </c>
       <c r="B28" t="n">
-        <v>79328</v>
+        <v>79919</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>420690</v>
+        <v>420875</v>
       </c>
       <c r="R28" t="n">
-        <v>6794088</v>
+        <v>6794212</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
         <v>132814832</v>
       </c>
       <c r="B29" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132814844</v>
+        <v>132814706</v>
       </c>
       <c r="B30" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>420421</v>
+        <v>419997</v>
       </c>
       <c r="R30" t="n">
-        <v>6794149</v>
+        <v>6793998</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132814706</v>
+        <v>132814864</v>
       </c>
       <c r="B31" t="n">
-        <v>79947</v>
+        <v>79329</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419997</v>
+        <v>420690</v>
       </c>
       <c r="R31" t="n">
-        <v>6793998</v>
+        <v>6794088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132814737</v>
+        <v>132814844</v>
       </c>
       <c r="B32" t="n">
-        <v>57954</v>
+        <v>79329</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,42 +3704,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>420586</v>
+        <v>420421</v>
       </c>
       <c r="R32" t="n">
-        <v>6794009</v>
+        <v>6794149</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132814728</v>
+        <v>132814737</v>
       </c>
       <c r="B33" t="n">
-        <v>79918</v>
+        <v>57954</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3809,34 +3801,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>420875</v>
+        <v>420586</v>
       </c>
       <c r="R33" t="n">
-        <v>6794212</v>
+        <v>6794009</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3898,7 +3898,7 @@
         <v>132814828</v>
       </c>
       <c r="B34" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4307,41 +4307,40 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132814788</v>
+        <v>132814748</v>
       </c>
       <c r="B38" t="n">
-        <v>8455</v>
+        <v>57954</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4351,10 +4350,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420693</v>
+        <v>420910</v>
       </c>
       <c r="R38" t="n">
-        <v>6794082</v>
+        <v>6794235</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4395,7 +4394,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4414,41 +4412,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814787</v>
+        <v>132814767</v>
       </c>
       <c r="B39" t="n">
-        <v>8455</v>
+        <v>57951</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4458,10 +4455,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420878</v>
+        <v>420588</v>
       </c>
       <c r="R39" t="n">
-        <v>6794218</v>
+        <v>6794046</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,7 +4499,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4524,7 +4520,7 @@
         <v>132814847</v>
       </c>
       <c r="B40" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4618,10 +4614,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132814748</v>
+        <v>132814838</v>
       </c>
       <c r="B41" t="n">
-        <v>57954</v>
+        <v>79329</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,42 +4625,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>420910</v>
+        <v>420073</v>
       </c>
       <c r="R41" t="n">
-        <v>6794235</v>
+        <v>6793986</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4723,10 +4711,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814838</v>
+        <v>132814713</v>
       </c>
       <c r="B42" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4734,21 +4722,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4758,10 +4746,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420073</v>
+        <v>420131</v>
       </c>
       <c r="R42" t="n">
-        <v>6793986</v>
+        <v>6793962</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4820,10 +4808,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132814713</v>
+        <v>132814701</v>
       </c>
       <c r="B43" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4855,10 +4843,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>420131</v>
+        <v>420311</v>
       </c>
       <c r="R43" t="n">
-        <v>6793962</v>
+        <v>6794104</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,45 +4905,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814701</v>
+        <v>132814788</v>
       </c>
       <c r="B44" t="n">
-        <v>79947</v>
+        <v>8455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420311</v>
+        <v>420693</v>
       </c>
       <c r="R44" t="n">
-        <v>6794104</v>
+        <v>6794082</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,6 +4993,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5014,40 +5012,41 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814767</v>
+        <v>132814787</v>
       </c>
       <c r="B45" t="n">
-        <v>57951</v>
+        <v>8455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5057,10 +5056,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420588</v>
+        <v>420878</v>
       </c>
       <c r="R45" t="n">
-        <v>6794046</v>
+        <v>6794218</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5101,6 +5100,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5119,10 +5119,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132814857</v>
+        <v>132814763</v>
       </c>
       <c r="B46" t="n">
-        <v>79328</v>
+        <v>57951</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5130,34 +5130,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>420920</v>
+        <v>420057</v>
       </c>
       <c r="R46" t="n">
-        <v>6794226</v>
+        <v>6793966</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5216,45 +5224,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132814858</v>
+        <v>132814780</v>
       </c>
       <c r="B47" t="n">
-        <v>79328</v>
+        <v>8455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>420778</v>
+        <v>420313</v>
       </c>
       <c r="R47" t="n">
-        <v>6794174</v>
+        <v>6794133</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5295,6 +5312,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5313,54 +5331,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132814780</v>
+        <v>132814857</v>
       </c>
       <c r="B48" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>420313</v>
+        <v>420920</v>
       </c>
       <c r="R48" t="n">
-        <v>6794133</v>
+        <v>6794226</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5401,7 +5410,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5420,10 +5428,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132814763</v>
+        <v>132814858</v>
       </c>
       <c r="B49" t="n">
-        <v>57951</v>
+        <v>79329</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5431,42 +5439,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>420057</v>
+        <v>420778</v>
       </c>
       <c r="R49" t="n">
-        <v>6793966</v>
+        <v>6794174</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
         <v>132814841</v>
       </c>
       <c r="B50" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>132814843</v>
       </c>
       <c r="B51" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132814759</v>
+        <v>132814829</v>
       </c>
       <c r="B52" t="n">
-        <v>91933</v>
+        <v>79329</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,37 +5730,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>420574</v>
+        <v>420188</v>
       </c>
       <c r="R52" t="n">
-        <v>6794086</v>
+        <v>6794047</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5801,7 +5798,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5820,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132814758</v>
+        <v>132814759</v>
       </c>
       <c r="B53" t="n">
-        <v>91933</v>
+        <v>91934</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5858,10 +5854,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>420939</v>
+        <v>420574</v>
       </c>
       <c r="R53" t="n">
-        <v>6794202</v>
+        <v>6794086</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5921,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814829</v>
+        <v>132814848</v>
       </c>
       <c r="B54" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5956,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420188</v>
+        <v>420528</v>
       </c>
       <c r="R54" t="n">
-        <v>6794047</v>
+        <v>6794160</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6018,10 +6014,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132814848</v>
+        <v>132814758</v>
       </c>
       <c r="B55" t="n">
-        <v>79328</v>
+        <v>91934</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6029,34 +6025,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>420528</v>
+        <v>420939</v>
       </c>
       <c r="R55" t="n">
-        <v>6794160</v>
+        <v>6794202</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6097,6 +6096,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6115,10 +6115,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132814764</v>
+        <v>132814718</v>
       </c>
       <c r="B56" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6126,42 +6126,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>420073</v>
+        <v>420827</v>
       </c>
       <c r="R56" t="n">
-        <v>6793986</v>
+        <v>6794180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6220,10 +6212,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132814718</v>
+        <v>132814764</v>
       </c>
       <c r="B57" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6231,34 +6223,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>420827</v>
+        <v>420073</v>
       </c>
       <c r="R57" t="n">
-        <v>6794180</v>
+        <v>6793986</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6320,7 +6320,7 @@
         <v>132814837</v>
       </c>
       <c r="B58" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>132814853</v>
       </c>
       <c r="B59" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>132814729</v>
       </c>
       <c r="B60" t="n">
-        <v>79918</v>
+        <v>79919</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6608,45 +6608,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132814776</v>
+        <v>132814750</v>
       </c>
       <c r="B61" t="n">
-        <v>79086</v>
+        <v>57142</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>420807</v>
+        <v>420114</v>
       </c>
       <c r="R61" t="n">
-        <v>6794179</v>
+        <v>6793974</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6705,10 +6713,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132814856</v>
+        <v>132814776</v>
       </c>
       <c r="B62" t="n">
-        <v>79328</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6716,21 +6724,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6740,10 +6748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>420936</v>
+        <v>420807</v>
       </c>
       <c r="R62" t="n">
-        <v>6794205</v>
+        <v>6794179</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6802,10 +6810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132814704</v>
+        <v>132814856</v>
       </c>
       <c r="B63" t="n">
-        <v>79947</v>
+        <v>79329</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6813,21 +6821,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6837,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419964</v>
+        <v>420936</v>
       </c>
       <c r="R63" t="n">
-        <v>6793993</v>
+        <v>6794205</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6899,53 +6907,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132814750</v>
+        <v>132814704</v>
       </c>
       <c r="B64" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>420114</v>
+        <v>419964</v>
       </c>
       <c r="R64" t="n">
-        <v>6793974</v>
+        <v>6793993</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
         <v>132814720</v>
       </c>
       <c r="B65" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132814719</v>
+        <v>132814794</v>
       </c>
       <c r="B67" t="n">
-        <v>79947</v>
+        <v>56522</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7219,34 +7219,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>206004</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>420742</v>
+        <v>420170</v>
       </c>
       <c r="R67" t="n">
-        <v>6794108</v>
+        <v>6793954</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7305,10 +7313,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132814794</v>
+        <v>132814730</v>
       </c>
       <c r="B68" t="n">
-        <v>56522</v>
+        <v>79919</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7316,42 +7324,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>206004</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>420170</v>
+        <v>420787</v>
       </c>
       <c r="R68" t="n">
-        <v>6793954</v>
+        <v>6794163</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7410,54 +7410,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814791</v>
+        <v>132814727</v>
       </c>
       <c r="B69" t="n">
-        <v>8455</v>
+        <v>79919</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420112</v>
+        <v>420903</v>
       </c>
       <c r="R69" t="n">
-        <v>6793976</v>
+        <v>6794237</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7498,7 +7489,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7520,7 +7510,7 @@
         <v>132814826</v>
       </c>
       <c r="B70" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7617,7 +7607,7 @@
         <v>132814716</v>
       </c>
       <c r="B71" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7711,10 +7701,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814766</v>
+        <v>132814719</v>
       </c>
       <c r="B72" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,42 +7712,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420516</v>
+        <v>420742</v>
       </c>
       <c r="R72" t="n">
-        <v>6794196</v>
+        <v>6794108</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7816,10 +7798,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132814730</v>
+        <v>132814766</v>
       </c>
       <c r="B73" t="n">
-        <v>79918</v>
+        <v>57951</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7827,34 +7809,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>420787</v>
+        <v>420516</v>
       </c>
       <c r="R73" t="n">
-        <v>6794163</v>
+        <v>6794196</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7913,45 +7903,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132814727</v>
+        <v>132814791</v>
       </c>
       <c r="B74" t="n">
-        <v>79918</v>
+        <v>8455</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>420903</v>
+        <v>420112</v>
       </c>
       <c r="R74" t="n">
-        <v>6794237</v>
+        <v>6793976</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7992,6 +7991,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132814714</v>
+        <v>132814845</v>
       </c>
       <c r="B75" t="n">
-        <v>79947</v>
+        <v>79329</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8021,21 +8021,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>420233</v>
+        <v>420474</v>
       </c>
       <c r="R75" t="n">
-        <v>6793967</v>
+        <v>6794142</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8107,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132814845</v>
+        <v>132814714</v>
       </c>
       <c r="B76" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,21 +8118,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>420474</v>
+        <v>420233</v>
       </c>
       <c r="R76" t="n">
-        <v>6794142</v>
+        <v>6793967</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,7 +8419,7 @@
         <v>132814775</v>
       </c>
       <c r="B79" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>132814726</v>
       </c>
       <c r="B80" t="n">
-        <v>79918</v>
+        <v>79919</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132814830</v>
+        <v>132814866</v>
       </c>
       <c r="B81" t="n">
-        <v>79328</v>
+        <v>78336</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8625,34 +8625,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>420156</v>
+        <v>420768</v>
       </c>
       <c r="R81" t="n">
-        <v>6794036</v>
+        <v>6794178</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8693,8 +8696,34 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -8711,54 +8740,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132814783</v>
+        <v>132814723</v>
       </c>
       <c r="B82" t="n">
-        <v>8455</v>
+        <v>79948</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>420406</v>
+        <v>420646</v>
       </c>
       <c r="R82" t="n">
-        <v>6794117</v>
+        <v>6794161</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8799,7 +8819,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8818,10 +8837,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132814866</v>
+        <v>132814840</v>
       </c>
       <c r="B83" t="n">
-        <v>78335</v>
+        <v>79329</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8829,37 +8848,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>420768</v>
+        <v>420214</v>
       </c>
       <c r="R83" t="n">
-        <v>6794178</v>
+        <v>6793964</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8900,34 +8916,8 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -8944,10 +8934,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132814723</v>
+        <v>132814830</v>
       </c>
       <c r="B84" t="n">
-        <v>79947</v>
+        <v>79329</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8955,21 +8945,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8979,10 +8969,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>420646</v>
+        <v>420156</v>
       </c>
       <c r="R84" t="n">
-        <v>6794161</v>
+        <v>6794036</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9041,45 +9031,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132814840</v>
+        <v>132814783</v>
       </c>
       <c r="B85" t="n">
-        <v>79328</v>
+        <v>8455</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>420214</v>
+        <v>420406</v>
       </c>
       <c r="R85" t="n">
-        <v>6793964</v>
+        <v>6794117</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9120,6 +9119,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132814833</v>
+        <v>132814702</v>
       </c>
       <c r="B87" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,21 +9256,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419996</v>
+        <v>420119</v>
       </c>
       <c r="R87" t="n">
-        <v>6793995</v>
+        <v>6794012</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132814702</v>
+        <v>132814850</v>
       </c>
       <c r="B88" t="n">
-        <v>79947</v>
+        <v>79329</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9353,21 +9353,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9377,10 +9377,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>420119</v>
+        <v>420549</v>
       </c>
       <c r="R88" t="n">
-        <v>6794012</v>
+        <v>6794103</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9439,10 +9439,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132814850</v>
+        <v>132814833</v>
       </c>
       <c r="B89" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>420549</v>
+        <v>419996</v>
       </c>
       <c r="R89" t="n">
-        <v>6794103</v>
+        <v>6793995</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9539,7 +9539,7 @@
         <v>132814734</v>
       </c>
       <c r="B90" t="n">
-        <v>79918</v>
+        <v>79919</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>132814731</v>
       </c>
       <c r="B91" t="n">
-        <v>79918</v>
+        <v>79919</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>132814836</v>
       </c>
       <c r="B92" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>132814849</v>
       </c>
       <c r="B93" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9924,10 +9924,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132814725</v>
+        <v>132814735</v>
       </c>
       <c r="B94" t="n">
-        <v>79918</v>
+        <v>79919</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9953,16 +9953,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>420114</v>
+        <v>420683</v>
       </c>
       <c r="R94" t="n">
-        <v>6793974</v>
+        <v>6794145</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10003,6 +10006,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10021,10 +10025,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132814735</v>
+        <v>132814725</v>
       </c>
       <c r="B95" t="n">
-        <v>79918</v>
+        <v>79919</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10050,19 +10054,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>420683</v>
+        <v>420114</v>
       </c>
       <c r="R95" t="n">
-        <v>6794145</v>
+        <v>6793974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10103,7 +10104,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>132814852</v>
       </c>
       <c r="B96" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>132814851</v>
       </c>
       <c r="B97" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10316,10 +10316,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132814742</v>
+        <v>132814724</v>
       </c>
       <c r="B98" t="n">
-        <v>57954</v>
+        <v>79948</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,42 +10327,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>420570</v>
+        <v>420166</v>
       </c>
       <c r="R98" t="n">
-        <v>6794049</v>
+        <v>6793967</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10421,54 +10413,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132814782</v>
+        <v>132814721</v>
       </c>
       <c r="B99" t="n">
-        <v>8455</v>
+        <v>79948</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>420074</v>
+        <v>420709</v>
       </c>
       <c r="R99" t="n">
-        <v>6793987</v>
+        <v>6794077</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10509,7 +10492,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10528,10 +10510,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132814724</v>
+        <v>132814742</v>
       </c>
       <c r="B100" t="n">
-        <v>79947</v>
+        <v>57954</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10539,34 +10521,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>420166</v>
+        <v>420570</v>
       </c>
       <c r="R100" t="n">
-        <v>6793967</v>
+        <v>6794049</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10625,45 +10615,53 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132814721</v>
+        <v>132814751</v>
       </c>
       <c r="B101" t="n">
-        <v>79947</v>
+        <v>57142</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>420709</v>
+        <v>420599</v>
       </c>
       <c r="R101" t="n">
-        <v>6794077</v>
+        <v>6794022</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10827,10 +10825,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132814751</v>
+        <v>132814782</v>
       </c>
       <c r="B103" t="n">
-        <v>57142</v>
+        <v>8455</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10838,29 +10836,30 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -10870,10 +10869,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>420599</v>
+        <v>420074</v>
       </c>
       <c r="R103" t="n">
-        <v>6794022</v>
+        <v>6793987</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10914,6 +10913,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10935,7 +10935,7 @@
         <v>132814859</v>
       </c>
       <c r="B104" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11029,10 +11029,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132814777</v>
+        <v>132814709</v>
       </c>
       <c r="B105" t="n">
-        <v>79086</v>
+        <v>79948</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11040,21 +11040,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11064,10 +11064,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>420706</v>
+        <v>420028</v>
       </c>
       <c r="R105" t="n">
-        <v>6794078</v>
+        <v>6793991</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11126,10 +11126,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132814709</v>
+        <v>132814768</v>
       </c>
       <c r="B106" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11137,34 +11137,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>420028</v>
+        <v>420900</v>
       </c>
       <c r="R106" t="n">
-        <v>6793991</v>
+        <v>6794252</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11223,10 +11231,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132814768</v>
+        <v>132814777</v>
       </c>
       <c r="B107" t="n">
-        <v>57951</v>
+        <v>79087</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11234,42 +11242,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>420900</v>
+        <v>420706</v>
       </c>
       <c r="R107" t="n">
-        <v>6794252</v>
+        <v>6794078</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132814711</v>
+        <v>132814792</v>
       </c>
       <c r="B14" t="n">
-        <v>79948</v>
+        <v>57133</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,34 +1906,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420109</v>
+        <v>420554</v>
       </c>
       <c r="R14" t="n">
-        <v>6793976</v>
+        <v>6794096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,45 +2000,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814712</v>
+        <v>132814773</v>
       </c>
       <c r="B15" t="n">
-        <v>79948</v>
+        <v>57145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420126</v>
+        <v>420920</v>
       </c>
       <c r="R15" t="n">
-        <v>6793969</v>
+        <v>6794225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2105,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132814861</v>
+        <v>132814711</v>
       </c>
       <c r="B16" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2116,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420752</v>
+        <v>420109</v>
       </c>
       <c r="R16" t="n">
-        <v>6794099</v>
+        <v>6793976</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,10 +2202,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132814860</v>
+        <v>132814712</v>
       </c>
       <c r="B17" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,21 +2213,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2237,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420745</v>
+        <v>420126</v>
       </c>
       <c r="R17" t="n">
-        <v>6794098</v>
+        <v>6793969</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2283,7 +2299,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132814863</v>
+        <v>132814861</v>
       </c>
       <c r="B18" t="n">
         <v>79329</v>
@@ -2318,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>420725</v>
+        <v>420752</v>
       </c>
       <c r="R18" t="n">
-        <v>6794081</v>
+        <v>6794099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,10 +2396,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132814792</v>
+        <v>132814860</v>
       </c>
       <c r="B19" t="n">
-        <v>57133</v>
+        <v>79329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,42 +2407,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420554</v>
+        <v>420745</v>
       </c>
       <c r="R19" t="n">
-        <v>6794096</v>
+        <v>6794098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,53 +2493,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132814773</v>
+        <v>132814863</v>
       </c>
       <c r="B20" t="n">
-        <v>57145</v>
+        <v>79329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>420920</v>
+        <v>420725</v>
       </c>
       <c r="R20" t="n">
-        <v>6794225</v>
+        <v>6794081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814732</v>
+        <v>132814761</v>
       </c>
       <c r="B21" t="n">
-        <v>79919</v>
+        <v>57951</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2601,34 +2601,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420740</v>
+        <v>420119</v>
       </c>
       <c r="R21" t="n">
-        <v>6794120</v>
+        <v>6794010</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,7 +2695,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814761</v>
+        <v>132814762</v>
       </c>
       <c r="B22" t="n">
         <v>57951</v>
@@ -2720,7 +2728,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2730,10 +2738,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420119</v>
+        <v>419986</v>
       </c>
       <c r="R22" t="n">
-        <v>6794010</v>
+        <v>6793995</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,10 +2800,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132814762</v>
+        <v>132814732</v>
       </c>
       <c r="B23" t="n">
-        <v>57951</v>
+        <v>79919</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,42 +2811,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419986</v>
+        <v>420740</v>
       </c>
       <c r="R23" t="n">
-        <v>6793995</v>
+        <v>6794120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132814748</v>
+        <v>132814847</v>
       </c>
       <c r="B38" t="n">
-        <v>57954</v>
+        <v>79329</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4318,42 +4318,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420910</v>
+        <v>420443</v>
       </c>
       <c r="R38" t="n">
-        <v>6794235</v>
+        <v>6794222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4412,10 +4404,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814767</v>
+        <v>132814838</v>
       </c>
       <c r="B39" t="n">
-        <v>57951</v>
+        <v>79329</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4423,42 +4415,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420588</v>
+        <v>420073</v>
       </c>
       <c r="R39" t="n">
-        <v>6794046</v>
+        <v>6793986</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4517,10 +4501,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132814847</v>
+        <v>132814713</v>
       </c>
       <c r="B40" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4528,21 +4512,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4552,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>420443</v>
+        <v>420131</v>
       </c>
       <c r="R40" t="n">
-        <v>6794222</v>
+        <v>6793962</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4614,10 +4598,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132814838</v>
+        <v>132814701</v>
       </c>
       <c r="B41" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4625,21 +4609,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4649,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>420073</v>
+        <v>420311</v>
       </c>
       <c r="R41" t="n">
-        <v>6793986</v>
+        <v>6794104</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4711,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814713</v>
+        <v>132814748</v>
       </c>
       <c r="B42" t="n">
-        <v>79948</v>
+        <v>57954</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4722,34 +4706,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420131</v>
+        <v>420910</v>
       </c>
       <c r="R42" t="n">
-        <v>6793962</v>
+        <v>6794235</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4808,45 +4800,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132814701</v>
+        <v>132814788</v>
       </c>
       <c r="B43" t="n">
-        <v>79948</v>
+        <v>8455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>420311</v>
+        <v>420693</v>
       </c>
       <c r="R43" t="n">
-        <v>6794104</v>
+        <v>6794082</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4887,6 +4888,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4905,7 +4907,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814788</v>
+        <v>132814787</v>
       </c>
       <c r="B44" t="n">
         <v>8455</v>
@@ -4939,7 +4941,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4949,10 +4951,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420693</v>
+        <v>420878</v>
       </c>
       <c r="R44" t="n">
-        <v>6794082</v>
+        <v>6794218</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,41 +5014,40 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814787</v>
+        <v>132814767</v>
       </c>
       <c r="B45" t="n">
-        <v>8455</v>
+        <v>57951</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5056,10 +5057,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420878</v>
+        <v>420588</v>
       </c>
       <c r="R45" t="n">
-        <v>6794218</v>
+        <v>6794046</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,7 +5101,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6608,53 +6608,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132814750</v>
+        <v>132814856</v>
       </c>
       <c r="B61" t="n">
-        <v>57142</v>
+        <v>79329</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>420114</v>
+        <v>420936</v>
       </c>
       <c r="R61" t="n">
-        <v>6793974</v>
+        <v>6794205</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6713,10 +6705,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132814776</v>
+        <v>132814704</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79948</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6724,21 +6716,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6748,10 +6740,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>420807</v>
+        <v>419964</v>
       </c>
       <c r="R62" t="n">
-        <v>6794179</v>
+        <v>6793993</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,45 +6802,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132814856</v>
+        <v>132814750</v>
       </c>
       <c r="B63" t="n">
-        <v>79329</v>
+        <v>57142</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>420936</v>
+        <v>420114</v>
       </c>
       <c r="R63" t="n">
-        <v>6794205</v>
+        <v>6793974</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132814704</v>
+        <v>132814776</v>
       </c>
       <c r="B64" t="n">
-        <v>79948</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6918,21 +6918,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419964</v>
+        <v>420807</v>
       </c>
       <c r="R64" t="n">
-        <v>6793993</v>
+        <v>6794179</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,45 +7004,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132814720</v>
+        <v>132814789</v>
       </c>
       <c r="B65" t="n">
-        <v>79948</v>
+        <v>8455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>420755</v>
+        <v>420681</v>
       </c>
       <c r="R65" t="n">
-        <v>6794087</v>
+        <v>6794073</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7083,6 +7092,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7101,54 +7111,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132814789</v>
+        <v>132814720</v>
       </c>
       <c r="B66" t="n">
-        <v>8455</v>
+        <v>79948</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>420681</v>
+        <v>420755</v>
       </c>
       <c r="R66" t="n">
-        <v>6794073</v>
+        <v>6794087</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7189,7 +7190,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7313,45 +7313,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132814730</v>
+        <v>132814791</v>
       </c>
       <c r="B68" t="n">
-        <v>79919</v>
+        <v>8455</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>420787</v>
+        <v>420112</v>
       </c>
       <c r="R68" t="n">
-        <v>6794163</v>
+        <v>6793976</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7392,6 +7401,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7410,7 +7420,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814727</v>
+        <v>132814730</v>
       </c>
       <c r="B69" t="n">
         <v>79919</v>
@@ -7445,10 +7455,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420903</v>
+        <v>420787</v>
       </c>
       <c r="R69" t="n">
-        <v>6794237</v>
+        <v>6794163</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7507,10 +7517,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132814826</v>
+        <v>132814727</v>
       </c>
       <c r="B70" t="n">
-        <v>79329</v>
+        <v>79919</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7518,21 +7528,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7542,10 +7552,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>420418</v>
+        <v>420903</v>
       </c>
       <c r="R70" t="n">
-        <v>6794158</v>
+        <v>6794237</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7604,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132814716</v>
+        <v>132814826</v>
       </c>
       <c r="B71" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7615,21 +7625,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7639,10 +7649,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>420748</v>
+        <v>420418</v>
       </c>
       <c r="R71" t="n">
-        <v>6794107</v>
+        <v>6794158</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7701,7 +7711,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814719</v>
+        <v>132814716</v>
       </c>
       <c r="B72" t="n">
         <v>79948</v>
@@ -7736,10 +7746,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420742</v>
+        <v>420748</v>
       </c>
       <c r="R72" t="n">
-        <v>6794108</v>
+        <v>6794107</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7798,10 +7808,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132814766</v>
+        <v>132814719</v>
       </c>
       <c r="B73" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7809,42 +7819,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>420516</v>
+        <v>420742</v>
       </c>
       <c r="R73" t="n">
-        <v>6794196</v>
+        <v>6794108</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7903,41 +7905,40 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132814791</v>
+        <v>132814766</v>
       </c>
       <c r="B74" t="n">
-        <v>8455</v>
+        <v>57951</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -7947,10 +7948,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>420112</v>
+        <v>420516</v>
       </c>
       <c r="R74" t="n">
-        <v>6793976</v>
+        <v>6794196</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7991,7 +7992,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132814771</v>
+        <v>132814710</v>
       </c>
       <c r="B2" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420677</v>
+        <v>420053</v>
       </c>
       <c r="R2" t="n">
-        <v>6794147</v>
+        <v>6793980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132814765</v>
+        <v>132814771</v>
       </c>
       <c r="B3" t="n">
         <v>57951</v>
@@ -813,7 +809,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420459</v>
+        <v>420677</v>
       </c>
       <c r="R3" t="n">
-        <v>6794159</v>
+        <v>6794147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132814710</v>
+        <v>132814765</v>
       </c>
       <c r="B4" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,26 +892,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420053</v>
+        <v>420459</v>
       </c>
       <c r="R4" t="n">
-        <v>6793980</v>
+        <v>6794159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +968,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132814792</v>
+        <v>132814761</v>
       </c>
       <c r="B14" t="n">
-        <v>57133</v>
+        <v>57951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,16 +1906,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420554</v>
+        <v>420119</v>
       </c>
       <c r="R14" t="n">
-        <v>6794096</v>
+        <v>6794010</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,27 +2000,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814773</v>
+        <v>132814762</v>
       </c>
       <c r="B15" t="n">
-        <v>57145</v>
+        <v>57951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2033,7 +2033,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420920</v>
+        <v>419986</v>
       </c>
       <c r="R15" t="n">
-        <v>6794225</v>
+        <v>6793995</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814761</v>
+        <v>132814792</v>
       </c>
       <c r="B21" t="n">
-        <v>57951</v>
+        <v>57133</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2623,7 +2623,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420119</v>
+        <v>420554</v>
       </c>
       <c r="R21" t="n">
-        <v>6794010</v>
+        <v>6794096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,27 +2695,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814762</v>
+        <v>132814773</v>
       </c>
       <c r="B22" t="n">
-        <v>57951</v>
+        <v>57145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2728,7 +2728,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419986</v>
+        <v>420920</v>
       </c>
       <c r="R22" t="n">
-        <v>6793995</v>
+        <v>6794225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,45 +2897,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814715</v>
+        <v>132814786</v>
       </c>
       <c r="B24" t="n">
-        <v>79948</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420524</v>
+        <v>420459</v>
       </c>
       <c r="R24" t="n">
-        <v>6794233</v>
+        <v>6794178</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,6 +2985,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2994,45 +3004,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814865</v>
+        <v>132814784</v>
       </c>
       <c r="B25" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420586</v>
+        <v>420420</v>
       </c>
       <c r="R25" t="n">
-        <v>6794106</v>
+        <v>6794140</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3073,6 +3092,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3091,54 +3111,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132814786</v>
+        <v>132814715</v>
       </c>
       <c r="B26" t="n">
-        <v>8455</v>
+        <v>79948</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>420459</v>
+        <v>420524</v>
       </c>
       <c r="R26" t="n">
-        <v>6794178</v>
+        <v>6794233</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,7 +3190,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3198,54 +3208,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132814784</v>
+        <v>132814865</v>
       </c>
       <c r="B27" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>420420</v>
+        <v>420586</v>
       </c>
       <c r="R27" t="n">
-        <v>6794140</v>
+        <v>6794106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3286,7 +3287,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132814728</v>
+        <v>132814832</v>
       </c>
       <c r="B28" t="n">
-        <v>79919</v>
+        <v>79329</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>420875</v>
+        <v>419983</v>
       </c>
       <c r="R28" t="n">
-        <v>6794212</v>
+        <v>6793990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132814832</v>
+        <v>132814706</v>
       </c>
       <c r="B29" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419983</v>
+        <v>419997</v>
       </c>
       <c r="R29" t="n">
-        <v>6793990</v>
+        <v>6793998</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132814706</v>
+        <v>132814864</v>
       </c>
       <c r="B30" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419997</v>
+        <v>420690</v>
       </c>
       <c r="R30" t="n">
-        <v>6793998</v>
+        <v>6794088</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132814864</v>
+        <v>132814844</v>
       </c>
       <c r="B31" t="n">
         <v>79329</v>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>420690</v>
+        <v>420421</v>
       </c>
       <c r="R31" t="n">
-        <v>6794088</v>
+        <v>6794149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132814844</v>
+        <v>132814737</v>
       </c>
       <c r="B32" t="n">
-        <v>79329</v>
+        <v>57954</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,34 +3704,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>420421</v>
+        <v>420586</v>
       </c>
       <c r="R32" t="n">
-        <v>6794149</v>
+        <v>6794009</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,10 +3798,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132814737</v>
+        <v>132814728</v>
       </c>
       <c r="B33" t="n">
-        <v>57954</v>
+        <v>79919</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,42 +3809,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>420586</v>
+        <v>420875</v>
       </c>
       <c r="R33" t="n">
-        <v>6794009</v>
+        <v>6794212</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132814828</v>
+        <v>132814769</v>
       </c>
       <c r="B34" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3906,34 +3906,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>420306</v>
+        <v>420899</v>
       </c>
       <c r="R34" t="n">
-        <v>6794101</v>
+        <v>6794245</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132814769</v>
+        <v>132814741</v>
       </c>
       <c r="B35" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4003,16 +4011,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4025,7 +4033,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4035,10 +4043,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>420899</v>
+        <v>420574</v>
       </c>
       <c r="R35" t="n">
-        <v>6794245</v>
+        <v>6794086</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,7 +4105,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132814741</v>
+        <v>132814740</v>
       </c>
       <c r="B36" t="n">
         <v>57954</v>
@@ -4140,10 +4148,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>420574</v>
+        <v>420104</v>
       </c>
       <c r="R36" t="n">
-        <v>6794086</v>
+        <v>6794033</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4202,10 +4210,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132814740</v>
+        <v>132814828</v>
       </c>
       <c r="B37" t="n">
-        <v>57954</v>
+        <v>79329</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4213,42 +4221,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>420104</v>
+        <v>420306</v>
       </c>
       <c r="R37" t="n">
-        <v>6794033</v>
+        <v>6794101</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814748</v>
+        <v>132814767</v>
       </c>
       <c r="B42" t="n">
-        <v>57954</v>
+        <v>57951</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,16 +4706,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4728,7 +4728,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420910</v>
+        <v>420588</v>
       </c>
       <c r="R42" t="n">
-        <v>6794235</v>
+        <v>6794046</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4800,41 +4800,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132814788</v>
+        <v>132814748</v>
       </c>
       <c r="B43" t="n">
-        <v>8455</v>
+        <v>57954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4844,10 +4843,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>420693</v>
+        <v>420910</v>
       </c>
       <c r="R43" t="n">
-        <v>6794082</v>
+        <v>6794235</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,7 +4887,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4907,7 +4905,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814787</v>
+        <v>132814788</v>
       </c>
       <c r="B44" t="n">
         <v>8455</v>
@@ -4941,7 +4939,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4951,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420878</v>
+        <v>420693</v>
       </c>
       <c r="R44" t="n">
-        <v>6794218</v>
+        <v>6794082</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5014,40 +5012,41 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814767</v>
+        <v>132814787</v>
       </c>
       <c r="B45" t="n">
-        <v>57951</v>
+        <v>8455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5057,10 +5056,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420588</v>
+        <v>420878</v>
       </c>
       <c r="R45" t="n">
-        <v>6794046</v>
+        <v>6794218</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5101,6 +5100,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5119,10 +5119,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132814763</v>
+        <v>132814857</v>
       </c>
       <c r="B46" t="n">
-        <v>57951</v>
+        <v>79329</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5130,42 +5130,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>420057</v>
+        <v>420920</v>
       </c>
       <c r="R46" t="n">
-        <v>6793966</v>
+        <v>6794226</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5224,54 +5216,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132814780</v>
+        <v>132814858</v>
       </c>
       <c r="B47" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>420313</v>
+        <v>420778</v>
       </c>
       <c r="R47" t="n">
-        <v>6794133</v>
+        <v>6794174</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5312,7 +5295,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5331,7 +5313,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132814857</v>
+        <v>132814841</v>
       </c>
       <c r="B48" t="n">
         <v>79329</v>
@@ -5366,10 +5348,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>420920</v>
+        <v>420224</v>
       </c>
       <c r="R48" t="n">
-        <v>6794226</v>
+        <v>6793969</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5428,7 +5410,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132814858</v>
+        <v>132814843</v>
       </c>
       <c r="B49" t="n">
         <v>79329</v>
@@ -5463,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>420778</v>
+        <v>420223</v>
       </c>
       <c r="R49" t="n">
-        <v>6794174</v>
+        <v>6793998</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5525,45 +5507,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132814841</v>
+        <v>132814780</v>
       </c>
       <c r="B50" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>420224</v>
+        <v>420313</v>
       </c>
       <c r="R50" t="n">
-        <v>6793969</v>
+        <v>6794133</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5604,6 +5595,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5622,10 +5614,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132814843</v>
+        <v>132814763</v>
       </c>
       <c r="B51" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5633,34 +5625,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>420223</v>
+        <v>420057</v>
       </c>
       <c r="R51" t="n">
-        <v>6793998</v>
+        <v>6793966</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132814829</v>
+        <v>132814759</v>
       </c>
       <c r="B52" t="n">
-        <v>79329</v>
+        <v>91934</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,34 +5730,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>420188</v>
+        <v>420574</v>
       </c>
       <c r="R52" t="n">
-        <v>6794047</v>
+        <v>6794086</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5798,6 +5801,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5816,7 +5820,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132814759</v>
+        <v>132814758</v>
       </c>
       <c r="B53" t="n">
         <v>91934</v>
@@ -5854,10 +5858,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>420574</v>
+        <v>420939</v>
       </c>
       <c r="R53" t="n">
-        <v>6794086</v>
+        <v>6794202</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5917,10 +5921,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814848</v>
+        <v>132814764</v>
       </c>
       <c r="B54" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5928,34 +5932,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420528</v>
+        <v>420073</v>
       </c>
       <c r="R54" t="n">
-        <v>6794160</v>
+        <v>6793986</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6014,10 +6026,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132814758</v>
+        <v>132814829</v>
       </c>
       <c r="B55" t="n">
-        <v>91934</v>
+        <v>79329</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6025,37 +6037,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>420939</v>
+        <v>420188</v>
       </c>
       <c r="R55" t="n">
-        <v>6794202</v>
+        <v>6794047</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6096,7 +6105,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6115,10 +6123,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132814718</v>
+        <v>132814848</v>
       </c>
       <c r="B56" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6126,21 +6134,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6150,10 +6158,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>420827</v>
+        <v>420528</v>
       </c>
       <c r="R56" t="n">
-        <v>6794180</v>
+        <v>6794160</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,10 +6220,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132814764</v>
+        <v>132814718</v>
       </c>
       <c r="B57" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6223,42 +6231,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>420073</v>
+        <v>420827</v>
       </c>
       <c r="R57" t="n">
-        <v>6793986</v>
+        <v>6794180</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6608,45 +6608,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132814856</v>
+        <v>132814750</v>
       </c>
       <c r="B61" t="n">
-        <v>79329</v>
+        <v>57142</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>420936</v>
+        <v>420114</v>
       </c>
       <c r="R61" t="n">
-        <v>6794205</v>
+        <v>6793974</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6705,10 +6713,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132814704</v>
+        <v>132814856</v>
       </c>
       <c r="B62" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6716,21 +6724,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6740,10 +6748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419964</v>
+        <v>420936</v>
       </c>
       <c r="R62" t="n">
-        <v>6793993</v>
+        <v>6794205</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6802,53 +6810,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132814750</v>
+        <v>132814704</v>
       </c>
       <c r="B63" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>420114</v>
+        <v>419964</v>
       </c>
       <c r="R63" t="n">
-        <v>6793974</v>
+        <v>6793993</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7004,54 +7004,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132814789</v>
+        <v>132814720</v>
       </c>
       <c r="B65" t="n">
-        <v>8455</v>
+        <v>79948</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>420681</v>
+        <v>420755</v>
       </c>
       <c r="R65" t="n">
-        <v>6794073</v>
+        <v>6794087</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7092,7 +7083,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7111,45 +7101,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132814720</v>
+        <v>132814789</v>
       </c>
       <c r="B66" t="n">
-        <v>79948</v>
+        <v>8455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>420755</v>
+        <v>420681</v>
       </c>
       <c r="R66" t="n">
-        <v>6794087</v>
+        <v>6794073</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,6 +7189,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132814794</v>
+        <v>132814826</v>
       </c>
       <c r="B67" t="n">
-        <v>56522</v>
+        <v>79329</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7219,42 +7219,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>420170</v>
+        <v>420418</v>
       </c>
       <c r="R67" t="n">
-        <v>6793954</v>
+        <v>6794158</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7313,54 +7305,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132814791</v>
+        <v>132814716</v>
       </c>
       <c r="B68" t="n">
-        <v>8455</v>
+        <v>79948</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>420112</v>
+        <v>420748</v>
       </c>
       <c r="R68" t="n">
-        <v>6793976</v>
+        <v>6794107</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7401,7 +7384,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7420,10 +7402,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814730</v>
+        <v>132814719</v>
       </c>
       <c r="B69" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,21 +7413,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7455,10 +7437,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420787</v>
+        <v>420742</v>
       </c>
       <c r="R69" t="n">
-        <v>6794163</v>
+        <v>6794108</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7517,10 +7499,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132814727</v>
+        <v>132814766</v>
       </c>
       <c r="B70" t="n">
-        <v>79919</v>
+        <v>57951</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7528,34 +7510,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>420903</v>
+        <v>420516</v>
       </c>
       <c r="R70" t="n">
-        <v>6794237</v>
+        <v>6794196</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7614,10 +7604,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132814826</v>
+        <v>132814794</v>
       </c>
       <c r="B71" t="n">
-        <v>79329</v>
+        <v>56522</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,34 +7615,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>420418</v>
+        <v>420170</v>
       </c>
       <c r="R71" t="n">
-        <v>6794158</v>
+        <v>6793954</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7711,45 +7709,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814716</v>
+        <v>132814791</v>
       </c>
       <c r="B72" t="n">
-        <v>79948</v>
+        <v>8455</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420748</v>
+        <v>420112</v>
       </c>
       <c r="R72" t="n">
-        <v>6794107</v>
+        <v>6793976</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7790,6 +7797,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7808,10 +7816,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132814719</v>
+        <v>132814730</v>
       </c>
       <c r="B73" t="n">
-        <v>79948</v>
+        <v>79919</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7819,21 +7827,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7843,10 +7851,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>420742</v>
+        <v>420787</v>
       </c>
       <c r="R73" t="n">
-        <v>6794108</v>
+        <v>6794163</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7905,10 +7913,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132814766</v>
+        <v>132814727</v>
       </c>
       <c r="B74" t="n">
-        <v>57951</v>
+        <v>79919</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7916,42 +7924,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>420516</v>
+        <v>420903</v>
       </c>
       <c r="R74" t="n">
-        <v>6794196</v>
+        <v>6794237</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132814702</v>
+        <v>132814734</v>
       </c>
       <c r="B87" t="n">
-        <v>79948</v>
+        <v>79919</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,21 +9256,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>420119</v>
+        <v>420696</v>
       </c>
       <c r="R87" t="n">
-        <v>6794012</v>
+        <v>6794141</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132814850</v>
+        <v>132814731</v>
       </c>
       <c r="B88" t="n">
-        <v>79329</v>
+        <v>79919</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9353,21 +9353,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9377,10 +9377,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>420549</v>
+        <v>420768</v>
       </c>
       <c r="R88" t="n">
-        <v>6794103</v>
+        <v>6794179</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9439,10 +9439,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132814833</v>
+        <v>132814702</v>
       </c>
       <c r="B89" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9450,21 +9450,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419996</v>
+        <v>420119</v>
       </c>
       <c r="R89" t="n">
-        <v>6793995</v>
+        <v>6794012</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9536,10 +9536,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132814734</v>
+        <v>132814850</v>
       </c>
       <c r="B90" t="n">
-        <v>79919</v>
+        <v>79329</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9547,21 +9547,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>420696</v>
+        <v>420549</v>
       </c>
       <c r="R90" t="n">
-        <v>6794141</v>
+        <v>6794103</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132814731</v>
+        <v>132814833</v>
       </c>
       <c r="B91" t="n">
-        <v>79919</v>
+        <v>79329</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9644,21 +9644,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>420768</v>
+        <v>419996</v>
       </c>
       <c r="R91" t="n">
-        <v>6794179</v>
+        <v>6793995</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10122,10 +10122,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132814852</v>
+        <v>132814724</v>
       </c>
       <c r="B96" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10133,21 +10133,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10157,10 +10157,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>420835</v>
+        <v>420166</v>
       </c>
       <c r="R96" t="n">
-        <v>6794144</v>
+        <v>6793967</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10219,10 +10219,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132814851</v>
+        <v>132814721</v>
       </c>
       <c r="B97" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10230,21 +10230,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>420801</v>
+        <v>420709</v>
       </c>
       <c r="R97" t="n">
-        <v>6794114</v>
+        <v>6794077</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10316,45 +10316,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132814724</v>
+        <v>132814782</v>
       </c>
       <c r="B98" t="n">
-        <v>79948</v>
+        <v>8455</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>420166</v>
+        <v>420074</v>
       </c>
       <c r="R98" t="n">
-        <v>6793967</v>
+        <v>6793987</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10395,6 +10404,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10413,45 +10423,53 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132814721</v>
+        <v>132814751</v>
       </c>
       <c r="B99" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>420709</v>
+        <v>420599</v>
       </c>
       <c r="R99" t="n">
-        <v>6794077</v>
+        <v>6794022</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10510,32 +10528,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132814742</v>
+        <v>132814749</v>
       </c>
       <c r="B100" t="n">
-        <v>57954</v>
+        <v>57142</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10543,7 +10561,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -10553,10 +10571,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>420570</v>
+        <v>420604</v>
       </c>
       <c r="R100" t="n">
-        <v>6794049</v>
+        <v>6794012</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10615,53 +10633,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132814751</v>
+        <v>132814852</v>
       </c>
       <c r="B101" t="n">
-        <v>57142</v>
+        <v>79329</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>420599</v>
+        <v>420835</v>
       </c>
       <c r="R101" t="n">
-        <v>6794022</v>
+        <v>6794144</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10720,53 +10730,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132814749</v>
+        <v>132814851</v>
       </c>
       <c r="B102" t="n">
-        <v>57142</v>
+        <v>79329</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>420604</v>
+        <v>420801</v>
       </c>
       <c r="R102" t="n">
-        <v>6794012</v>
+        <v>6794114</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10825,41 +10827,40 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132814782</v>
+        <v>132814742</v>
       </c>
       <c r="B103" t="n">
-        <v>8455</v>
+        <v>57954</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -10869,10 +10870,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>420074</v>
+        <v>420570</v>
       </c>
       <c r="R103" t="n">
-        <v>6793987</v>
+        <v>6794049</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10913,7 +10914,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132814859</v>
+        <v>132814768</v>
       </c>
       <c r="B104" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10943,34 +10943,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>420739</v>
+        <v>420900</v>
       </c>
       <c r="R104" t="n">
-        <v>6794114</v>
+        <v>6794252</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11029,10 +11037,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132814709</v>
+        <v>132814859</v>
       </c>
       <c r="B105" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11040,21 +11048,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11064,10 +11072,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>420028</v>
+        <v>420739</v>
       </c>
       <c r="R105" t="n">
-        <v>6793991</v>
+        <v>6794114</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11126,10 +11134,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132814768</v>
+        <v>132814709</v>
       </c>
       <c r="B106" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11137,42 +11145,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>420900</v>
+        <v>420028</v>
       </c>
       <c r="R106" t="n">
-        <v>6794252</v>
+        <v>6793991</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11433,7 +11433,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132814820</v>
+        <v>132814801</v>
       </c>
       <c r="B109" t="n">
         <v>57954</v>
@@ -11476,10 +11476,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>420740</v>
+        <v>420233</v>
       </c>
       <c r="R109" t="n">
-        <v>6794115</v>
+        <v>6793977</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132814801</v>
+        <v>132814820</v>
       </c>
       <c r="B110" t="n">
         <v>57954</v>
@@ -11581,10 +11581,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>420233</v>
+        <v>420740</v>
       </c>
       <c r="R110" t="n">
-        <v>6793977</v>
+        <v>6794115</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132814846</v>
+        <v>132814738</v>
       </c>
       <c r="B7" t="n">
-        <v>79329</v>
+        <v>57954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1211,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420455</v>
+        <v>420583</v>
       </c>
       <c r="R7" t="n">
-        <v>6794188</v>
+        <v>6794016</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132814738</v>
+        <v>132814744</v>
       </c>
       <c r="B8" t="n">
         <v>57954</v>
@@ -1340,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420583</v>
+        <v>420576</v>
       </c>
       <c r="R8" t="n">
-        <v>6794016</v>
+        <v>6794051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132814744</v>
+        <v>132814846</v>
       </c>
       <c r="B9" t="n">
-        <v>57954</v>
+        <v>79329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1421,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420576</v>
+        <v>420455</v>
       </c>
       <c r="R9" t="n">
-        <v>6794051</v>
+        <v>6794188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132814741</v>
+        <v>132814828</v>
       </c>
       <c r="B35" t="n">
-        <v>57954</v>
+        <v>79329</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,42 +4011,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>420574</v>
+        <v>420306</v>
       </c>
       <c r="R35" t="n">
-        <v>6794086</v>
+        <v>6794101</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4105,7 +4097,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132814740</v>
+        <v>132814741</v>
       </c>
       <c r="B36" t="n">
         <v>57954</v>
@@ -4148,10 +4140,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>420104</v>
+        <v>420574</v>
       </c>
       <c r="R36" t="n">
-        <v>6794033</v>
+        <v>6794086</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4210,10 +4202,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132814828</v>
+        <v>132814740</v>
       </c>
       <c r="B37" t="n">
-        <v>79329</v>
+        <v>57954</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,34 +4213,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>420306</v>
+        <v>420104</v>
       </c>
       <c r="R37" t="n">
-        <v>6794101</v>
+        <v>6794033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4307,45 +4307,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132814847</v>
+        <v>132814788</v>
       </c>
       <c r="B38" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420443</v>
+        <v>420693</v>
       </c>
       <c r="R38" t="n">
-        <v>6794222</v>
+        <v>6794082</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4386,6 +4395,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4404,45 +4414,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814838</v>
+        <v>132814787</v>
       </c>
       <c r="B39" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420073</v>
+        <v>420878</v>
       </c>
       <c r="R39" t="n">
-        <v>6793986</v>
+        <v>6794218</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,6 +4502,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4501,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132814713</v>
+        <v>132814847</v>
       </c>
       <c r="B40" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>420131</v>
+        <v>420443</v>
       </c>
       <c r="R40" t="n">
-        <v>6793962</v>
+        <v>6794222</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4598,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132814701</v>
+        <v>132814838</v>
       </c>
       <c r="B41" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4609,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>420311</v>
+        <v>420073</v>
       </c>
       <c r="R41" t="n">
-        <v>6794104</v>
+        <v>6793986</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814767</v>
+        <v>132814713</v>
       </c>
       <c r="B42" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,42 +4726,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420588</v>
+        <v>420131</v>
       </c>
       <c r="R42" t="n">
-        <v>6794046</v>
+        <v>6793962</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4800,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132814748</v>
+        <v>132814701</v>
       </c>
       <c r="B43" t="n">
-        <v>57954</v>
+        <v>79948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4811,42 +4823,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>420910</v>
+        <v>420311</v>
       </c>
       <c r="R43" t="n">
-        <v>6794235</v>
+        <v>6794104</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4905,41 +4909,40 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814788</v>
+        <v>132814767</v>
       </c>
       <c r="B44" t="n">
-        <v>8455</v>
+        <v>57951</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4949,10 +4952,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420693</v>
+        <v>420588</v>
       </c>
       <c r="R44" t="n">
-        <v>6794082</v>
+        <v>6794046</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4993,7 +4996,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5012,41 +5014,40 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814787</v>
+        <v>132814748</v>
       </c>
       <c r="B45" t="n">
-        <v>8455</v>
+        <v>57954</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5056,10 +5057,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420878</v>
+        <v>420910</v>
       </c>
       <c r="R45" t="n">
-        <v>6794218</v>
+        <v>6794235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,7 +5101,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814764</v>
+        <v>132814829</v>
       </c>
       <c r="B54" t="n">
-        <v>57951</v>
+        <v>79329</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5932,42 +5932,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420073</v>
+        <v>420188</v>
       </c>
       <c r="R54" t="n">
-        <v>6793986</v>
+        <v>6794047</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6026,7 +6018,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132814829</v>
+        <v>132814848</v>
       </c>
       <c r="B55" t="n">
         <v>79329</v>
@@ -6061,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>420188</v>
+        <v>420528</v>
       </c>
       <c r="R55" t="n">
-        <v>6794047</v>
+        <v>6794160</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6123,10 +6115,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132814848</v>
+        <v>132814718</v>
       </c>
       <c r="B56" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6134,21 +6126,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6158,10 +6150,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>420528</v>
+        <v>420827</v>
       </c>
       <c r="R56" t="n">
-        <v>6794160</v>
+        <v>6794180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6220,10 +6212,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132814718</v>
+        <v>132814764</v>
       </c>
       <c r="B57" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6231,34 +6223,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>420827</v>
+        <v>420073</v>
       </c>
       <c r="R57" t="n">
-        <v>6794180</v>
+        <v>6793986</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132814866</v>
+        <v>132814723</v>
       </c>
       <c r="B81" t="n">
-        <v>78336</v>
+        <v>79948</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8625,37 +8625,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>420768</v>
+        <v>420646</v>
       </c>
       <c r="R81" t="n">
-        <v>6794178</v>
+        <v>6794161</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8696,34 +8693,8 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -8740,10 +8711,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132814723</v>
+        <v>132814840</v>
       </c>
       <c r="B82" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8751,21 +8722,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8775,10 +8746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>420646</v>
+        <v>420214</v>
       </c>
       <c r="R82" t="n">
-        <v>6794161</v>
+        <v>6793964</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8837,7 +8808,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132814840</v>
+        <v>132814830</v>
       </c>
       <c r="B83" t="n">
         <v>79329</v>
@@ -8872,10 +8843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>420214</v>
+        <v>420156</v>
       </c>
       <c r="R83" t="n">
-        <v>6793964</v>
+        <v>6794036</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8934,10 +8905,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132814830</v>
+        <v>132814866</v>
       </c>
       <c r="B84" t="n">
-        <v>79329</v>
+        <v>78336</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8945,34 +8916,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>420156</v>
+        <v>420768</v>
       </c>
       <c r="R84" t="n">
-        <v>6794036</v>
+        <v>6794178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9013,8 +8987,34 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10122,45 +10122,53 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132814724</v>
+        <v>132814751</v>
       </c>
       <c r="B96" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>420166</v>
+        <v>420599</v>
       </c>
       <c r="R96" t="n">
-        <v>6793967</v>
+        <v>6794022</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10219,45 +10227,53 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132814721</v>
+        <v>132814749</v>
       </c>
       <c r="B97" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>420709</v>
+        <v>420604</v>
       </c>
       <c r="R97" t="n">
-        <v>6794077</v>
+        <v>6794012</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10316,54 +10332,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132814782</v>
+        <v>132814724</v>
       </c>
       <c r="B98" t="n">
-        <v>8455</v>
+        <v>79948</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>420074</v>
+        <v>420166</v>
       </c>
       <c r="R98" t="n">
-        <v>6793987</v>
+        <v>6793967</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10404,7 +10411,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10423,53 +10429,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132814751</v>
+        <v>132814721</v>
       </c>
       <c r="B99" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>420599</v>
+        <v>420709</v>
       </c>
       <c r="R99" t="n">
-        <v>6794022</v>
+        <v>6794077</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10528,10 +10526,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132814749</v>
+        <v>132814782</v>
       </c>
       <c r="B100" t="n">
-        <v>57142</v>
+        <v>8455</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10539,29 +10537,30 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -10571,10 +10570,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>420604</v>
+        <v>420074</v>
       </c>
       <c r="R100" t="n">
-        <v>6794012</v>
+        <v>6793987</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10615,6 +10614,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132814710</v>
+        <v>132814771</v>
       </c>
       <c r="B2" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420053</v>
+        <v>420677</v>
       </c>
       <c r="R2" t="n">
-        <v>6793980</v>
+        <v>6794147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132814771</v>
+        <v>132814765</v>
       </c>
       <c r="B3" t="n">
         <v>57951</v>
@@ -809,7 +813,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -819,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420677</v>
+        <v>420459</v>
       </c>
       <c r="R3" t="n">
-        <v>6794147</v>
+        <v>6794159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132814765</v>
+        <v>132814710</v>
       </c>
       <c r="B4" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,31 +896,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -924,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420459</v>
+        <v>420053</v>
       </c>
       <c r="R4" t="n">
-        <v>6794159</v>
+        <v>6793980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +967,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132814738</v>
+        <v>132814846</v>
       </c>
       <c r="B7" t="n">
-        <v>57954</v>
+        <v>79329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,42 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420583</v>
+        <v>420455</v>
       </c>
       <c r="R7" t="n">
-        <v>6794016</v>
+        <v>6794188</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132814744</v>
+        <v>132814738</v>
       </c>
       <c r="B8" t="n">
         <v>57954</v>
@@ -1348,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420576</v>
+        <v>420583</v>
       </c>
       <c r="R8" t="n">
-        <v>6794051</v>
+        <v>6794016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132814846</v>
+        <v>132814744</v>
       </c>
       <c r="B9" t="n">
-        <v>79329</v>
+        <v>57954</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420455</v>
+        <v>420576</v>
       </c>
       <c r="R9" t="n">
-        <v>6794188</v>
+        <v>6794051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132814761</v>
+        <v>132814711</v>
       </c>
       <c r="B14" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,42 +1906,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420119</v>
+        <v>420109</v>
       </c>
       <c r="R14" t="n">
-        <v>6794010</v>
+        <v>6793976</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814762</v>
+        <v>132814712</v>
       </c>
       <c r="B15" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,42 +2003,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419986</v>
+        <v>420126</v>
       </c>
       <c r="R15" t="n">
-        <v>6793995</v>
+        <v>6793969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132814711</v>
+        <v>132814861</v>
       </c>
       <c r="B16" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2116,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2140,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420109</v>
+        <v>420752</v>
       </c>
       <c r="R16" t="n">
-        <v>6793976</v>
+        <v>6794099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132814712</v>
+        <v>132814860</v>
       </c>
       <c r="B17" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2213,21 +2197,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2237,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420126</v>
+        <v>420745</v>
       </c>
       <c r="R17" t="n">
-        <v>6793969</v>
+        <v>6794098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,7 +2283,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132814861</v>
+        <v>132814863</v>
       </c>
       <c r="B18" t="n">
         <v>79329</v>
@@ -2334,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>420752</v>
+        <v>420725</v>
       </c>
       <c r="R18" t="n">
-        <v>6794099</v>
+        <v>6794081</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,10 +2380,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132814860</v>
+        <v>132814761</v>
       </c>
       <c r="B19" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2407,34 +2391,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420745</v>
+        <v>420119</v>
       </c>
       <c r="R19" t="n">
-        <v>6794098</v>
+        <v>6794010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2493,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132814863</v>
+        <v>132814762</v>
       </c>
       <c r="B20" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2504,34 +2496,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>420725</v>
+        <v>419986</v>
       </c>
       <c r="R20" t="n">
-        <v>6794081</v>
+        <v>6793995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814792</v>
+        <v>132814732</v>
       </c>
       <c r="B21" t="n">
-        <v>57133</v>
+        <v>79919</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2601,42 +2601,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420554</v>
+        <v>420740</v>
       </c>
       <c r="R21" t="n">
-        <v>6794096</v>
+        <v>6794120</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,27 +2687,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814773</v>
+        <v>132814792</v>
       </c>
       <c r="B22" t="n">
-        <v>57145</v>
+        <v>57133</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2728,7 +2720,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2738,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420920</v>
+        <v>420554</v>
       </c>
       <c r="R22" t="n">
-        <v>6794225</v>
+        <v>6794096</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2800,45 +2792,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132814732</v>
+        <v>132814773</v>
       </c>
       <c r="B23" t="n">
-        <v>79919</v>
+        <v>57145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>420740</v>
+        <v>420920</v>
       </c>
       <c r="R23" t="n">
-        <v>6794120</v>
+        <v>6794225</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,54 +2897,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814786</v>
+        <v>132814715</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>79948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420459</v>
+        <v>420524</v>
       </c>
       <c r="R24" t="n">
-        <v>6794178</v>
+        <v>6794233</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2985,7 +2976,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3004,54 +2994,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814784</v>
+        <v>132814865</v>
       </c>
       <c r="B25" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420420</v>
+        <v>420586</v>
       </c>
       <c r="R25" t="n">
-        <v>6794140</v>
+        <v>6794106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3092,7 +3073,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3111,45 +3091,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132814715</v>
+        <v>132814786</v>
       </c>
       <c r="B26" t="n">
-        <v>79948</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>420524</v>
+        <v>420459</v>
       </c>
       <c r="R26" t="n">
-        <v>6794233</v>
+        <v>6794178</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3179,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3208,45 +3198,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132814865</v>
+        <v>132814784</v>
       </c>
       <c r="B27" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>420586</v>
+        <v>420420</v>
       </c>
       <c r="R27" t="n">
-        <v>6794106</v>
+        <v>6794140</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3287,6 +3286,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132814832</v>
+        <v>132814728</v>
       </c>
       <c r="B28" t="n">
-        <v>79329</v>
+        <v>79919</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419983</v>
+        <v>420875</v>
       </c>
       <c r="R28" t="n">
-        <v>6793990</v>
+        <v>6794212</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132814706</v>
+        <v>132814832</v>
       </c>
       <c r="B29" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419997</v>
+        <v>419983</v>
       </c>
       <c r="R29" t="n">
-        <v>6793998</v>
+        <v>6793990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132814864</v>
+        <v>132814706</v>
       </c>
       <c r="B30" t="n">
-        <v>79329</v>
+        <v>79948</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>420690</v>
+        <v>419997</v>
       </c>
       <c r="R30" t="n">
-        <v>6794088</v>
+        <v>6793998</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132814844</v>
+        <v>132814864</v>
       </c>
       <c r="B31" t="n">
         <v>79329</v>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>420421</v>
+        <v>420690</v>
       </c>
       <c r="R31" t="n">
-        <v>6794149</v>
+        <v>6794088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132814737</v>
+        <v>132814844</v>
       </c>
       <c r="B32" t="n">
-        <v>57954</v>
+        <v>79329</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,42 +3704,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>420586</v>
+        <v>420421</v>
       </c>
       <c r="R32" t="n">
-        <v>6794009</v>
+        <v>6794149</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3798,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132814728</v>
+        <v>132814737</v>
       </c>
       <c r="B33" t="n">
-        <v>79919</v>
+        <v>57954</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3809,34 +3801,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>420875</v>
+        <v>420586</v>
       </c>
       <c r="R33" t="n">
-        <v>6794212</v>
+        <v>6794009</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5119,10 +5119,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132814857</v>
+        <v>132814763</v>
       </c>
       <c r="B46" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5130,34 +5130,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>420920</v>
+        <v>420057</v>
       </c>
       <c r="R46" t="n">
-        <v>6794226</v>
+        <v>6793966</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5216,7 +5224,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132814858</v>
+        <v>132814857</v>
       </c>
       <c r="B47" t="n">
         <v>79329</v>
@@ -5251,10 +5259,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>420778</v>
+        <v>420920</v>
       </c>
       <c r="R47" t="n">
-        <v>6794174</v>
+        <v>6794226</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5313,7 +5321,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132814841</v>
+        <v>132814858</v>
       </c>
       <c r="B48" t="n">
         <v>79329</v>
@@ -5348,10 +5356,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>420224</v>
+        <v>420778</v>
       </c>
       <c r="R48" t="n">
-        <v>6793969</v>
+        <v>6794174</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5410,7 +5418,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132814843</v>
+        <v>132814841</v>
       </c>
       <c r="B49" t="n">
         <v>79329</v>
@@ -5445,10 +5453,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>420223</v>
+        <v>420224</v>
       </c>
       <c r="R49" t="n">
-        <v>6793998</v>
+        <v>6793969</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5507,54 +5515,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132814780</v>
+        <v>132814843</v>
       </c>
       <c r="B50" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>420313</v>
+        <v>420223</v>
       </c>
       <c r="R50" t="n">
-        <v>6794133</v>
+        <v>6793998</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5595,7 +5594,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5614,40 +5612,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132814763</v>
+        <v>132814780</v>
       </c>
       <c r="B51" t="n">
-        <v>57951</v>
+        <v>8455</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -5657,10 +5656,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>420057</v>
+        <v>420313</v>
       </c>
       <c r="R51" t="n">
-        <v>6793966</v>
+        <v>6794133</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5701,6 +5700,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814829</v>
+        <v>132814764</v>
       </c>
       <c r="B54" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5932,34 +5932,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420188</v>
+        <v>420073</v>
       </c>
       <c r="R54" t="n">
-        <v>6794047</v>
+        <v>6793986</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6018,7 +6026,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132814848</v>
+        <v>132814829</v>
       </c>
       <c r="B55" t="n">
         <v>79329</v>
@@ -6053,10 +6061,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>420528</v>
+        <v>420188</v>
       </c>
       <c r="R55" t="n">
-        <v>6794160</v>
+        <v>6794047</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6115,10 +6123,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132814718</v>
+        <v>132814848</v>
       </c>
       <c r="B56" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6126,21 +6134,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6150,10 +6158,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>420827</v>
+        <v>420528</v>
       </c>
       <c r="R56" t="n">
-        <v>6794180</v>
+        <v>6794160</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,10 +6220,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132814764</v>
+        <v>132814718</v>
       </c>
       <c r="B57" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6223,42 +6231,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>420073</v>
+        <v>420827</v>
       </c>
       <c r="R57" t="n">
-        <v>6793986</v>
+        <v>6794180</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132814837</v>
+        <v>132814729</v>
       </c>
       <c r="B58" t="n">
-        <v>79329</v>
+        <v>79919</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>420071</v>
+        <v>420826</v>
       </c>
       <c r="R58" t="n">
-        <v>6793979</v>
+        <v>6794184</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6414,7 +6414,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132814853</v>
+        <v>132814837</v>
       </c>
       <c r="B59" t="n">
         <v>79329</v>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>420890</v>
+        <v>420071</v>
       </c>
       <c r="R59" t="n">
-        <v>6794166</v>
+        <v>6793979</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132814729</v>
+        <v>132814853</v>
       </c>
       <c r="B60" t="n">
-        <v>79919</v>
+        <v>79329</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>420826</v>
+        <v>420890</v>
       </c>
       <c r="R60" t="n">
-        <v>6794184</v>
+        <v>6794166</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132814856</v>
+        <v>132814776</v>
       </c>
       <c r="B62" t="n">
-        <v>79329</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6724,21 +6724,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>420936</v>
+        <v>420807</v>
       </c>
       <c r="R62" t="n">
-        <v>6794205</v>
+        <v>6794179</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,10 +6810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132814704</v>
+        <v>132814856</v>
       </c>
       <c r="B63" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6821,21 +6821,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419964</v>
+        <v>420936</v>
       </c>
       <c r="R63" t="n">
-        <v>6793993</v>
+        <v>6794205</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132814776</v>
+        <v>132814704</v>
       </c>
       <c r="B64" t="n">
-        <v>79087</v>
+        <v>79948</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6918,21 +6918,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>420807</v>
+        <v>419964</v>
       </c>
       <c r="R64" t="n">
-        <v>6794179</v>
+        <v>6793993</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132814734</v>
+        <v>132814702</v>
       </c>
       <c r="B87" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,21 +9256,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>420696</v>
+        <v>420119</v>
       </c>
       <c r="R87" t="n">
-        <v>6794141</v>
+        <v>6794012</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132814731</v>
+        <v>132814850</v>
       </c>
       <c r="B88" t="n">
-        <v>79919</v>
+        <v>79329</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9353,21 +9353,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9377,10 +9377,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>420768</v>
+        <v>420549</v>
       </c>
       <c r="R88" t="n">
-        <v>6794179</v>
+        <v>6794103</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9439,10 +9439,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132814702</v>
+        <v>132814833</v>
       </c>
       <c r="B89" t="n">
-        <v>79948</v>
+        <v>79329</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9450,21 +9450,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>420119</v>
+        <v>419996</v>
       </c>
       <c r="R89" t="n">
-        <v>6794012</v>
+        <v>6793995</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9536,10 +9536,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132814850</v>
+        <v>132814734</v>
       </c>
       <c r="B90" t="n">
-        <v>79329</v>
+        <v>79919</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9547,21 +9547,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>420549</v>
+        <v>420696</v>
       </c>
       <c r="R90" t="n">
-        <v>6794103</v>
+        <v>6794141</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132814833</v>
+        <v>132814731</v>
       </c>
       <c r="B91" t="n">
-        <v>79329</v>
+        <v>79919</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9644,21 +9644,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419996</v>
+        <v>420768</v>
       </c>
       <c r="R91" t="n">
-        <v>6793995</v>
+        <v>6794179</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -675,41 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132814790</v>
+        <v>132814771</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420678</v>
+        <v>420677</v>
       </c>
       <c r="R2" t="n">
-        <v>6794095</v>
+        <v>6794147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,41 +780,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132814785</v>
+        <v>132814765</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -826,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420460</v>
+        <v>420459</v>
       </c>
       <c r="R3" t="n">
-        <v>6794156</v>
+        <v>6794159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +867,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132814771</v>
+        <v>132814710</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,31 +896,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420677</v>
+        <v>420053</v>
       </c>
       <c r="R4" t="n">
-        <v>6794147</v>
+        <v>6793980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +967,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,40 +986,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132814765</v>
+        <v>132814790</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1037,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420459</v>
+        <v>420678</v>
       </c>
       <c r="R5" t="n">
-        <v>6794159</v>
+        <v>6794095</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,6 +1074,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,37 +1093,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132814710</v>
+        <v>132814785</v>
       </c>
       <c r="B6" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>420053</v>
+        <v>420460</v>
       </c>
       <c r="R6" t="n">
-        <v>6793980</v>
+        <v>6794156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132814738</v>
+        <v>132814744</v>
       </c>
       <c r="B8" t="n">
         <v>57958</v>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420583</v>
+        <v>420576</v>
       </c>
       <c r="R8" t="n">
-        <v>6794016</v>
+        <v>6794051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132814744</v>
+        <v>132814738</v>
       </c>
       <c r="B9" t="n">
         <v>57958</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420576</v>
+        <v>420583</v>
       </c>
       <c r="R9" t="n">
-        <v>6794051</v>
+        <v>6794016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132814705</v>
+        <v>132814839</v>
       </c>
       <c r="B10" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419964</v>
+        <v>420171</v>
       </c>
       <c r="R10" t="n">
-        <v>6793990</v>
+        <v>6793959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132814839</v>
+        <v>132814831</v>
       </c>
       <c r="B11" t="n">
         <v>79333</v>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>420171</v>
+        <v>420020</v>
       </c>
       <c r="R11" t="n">
-        <v>6793959</v>
+        <v>6794011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132814831</v>
+        <v>132814827</v>
       </c>
       <c r="B12" t="n">
         <v>79333</v>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>420020</v>
+        <v>420331</v>
       </c>
       <c r="R12" t="n">
-        <v>6794011</v>
+        <v>6794169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132814827</v>
+        <v>132814705</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>420331</v>
+        <v>419964</v>
       </c>
       <c r="R13" t="n">
-        <v>6794169</v>
+        <v>6793990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132814761</v>
+        <v>132814711</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,42 +1906,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420119</v>
+        <v>420109</v>
       </c>
       <c r="R14" t="n">
-        <v>6794010</v>
+        <v>6793976</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814762</v>
+        <v>132814712</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,42 +2003,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419986</v>
+        <v>420126</v>
       </c>
       <c r="R15" t="n">
-        <v>6793995</v>
+        <v>6793969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132814732</v>
+        <v>132814861</v>
       </c>
       <c r="B16" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2116,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2140,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420740</v>
+        <v>420752</v>
       </c>
       <c r="R16" t="n">
-        <v>6794120</v>
+        <v>6794099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132814711</v>
+        <v>132814860</v>
       </c>
       <c r="B17" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2213,21 +2197,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2237,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420109</v>
+        <v>420745</v>
       </c>
       <c r="R17" t="n">
-        <v>6793976</v>
+        <v>6794098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,10 +2283,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132814712</v>
+        <v>132814863</v>
       </c>
       <c r="B18" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2310,21 +2294,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2334,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>420126</v>
+        <v>420725</v>
       </c>
       <c r="R18" t="n">
-        <v>6793969</v>
+        <v>6794081</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,10 +2380,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132814861</v>
+        <v>132814762</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2407,34 +2391,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420752</v>
+        <v>419986</v>
       </c>
       <c r="R19" t="n">
-        <v>6794099</v>
+        <v>6793995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2493,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132814860</v>
+        <v>132814761</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2504,34 +2496,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>420745</v>
+        <v>420119</v>
       </c>
       <c r="R20" t="n">
-        <v>6794098</v>
+        <v>6794010</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814863</v>
+        <v>132814792</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2601,34 +2601,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420725</v>
+        <v>420554</v>
       </c>
       <c r="R21" t="n">
-        <v>6794081</v>
+        <v>6794096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,27 +2695,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814792</v>
+        <v>132814773</v>
       </c>
       <c r="B22" t="n">
-        <v>57136</v>
+        <v>57148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2720,7 +2728,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2730,10 +2738,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420554</v>
+        <v>420920</v>
       </c>
       <c r="R22" t="n">
-        <v>6794096</v>
+        <v>6794225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,53 +2800,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132814773</v>
+        <v>132814732</v>
       </c>
       <c r="B23" t="n">
-        <v>57148</v>
+        <v>79923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>420920</v>
+        <v>420740</v>
       </c>
       <c r="R23" t="n">
-        <v>6794225</v>
+        <v>6794120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,54 +2897,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814786</v>
+        <v>132814715</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420459</v>
+        <v>420524</v>
       </c>
       <c r="R24" t="n">
-        <v>6794178</v>
+        <v>6794233</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2985,7 +2976,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3004,54 +2994,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814784</v>
+        <v>132814865</v>
       </c>
       <c r="B25" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420420</v>
+        <v>420586</v>
       </c>
       <c r="R25" t="n">
-        <v>6794140</v>
+        <v>6794106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3092,7 +3073,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3111,45 +3091,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132814715</v>
+        <v>132814786</v>
       </c>
       <c r="B26" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>420524</v>
+        <v>420459</v>
       </c>
       <c r="R26" t="n">
-        <v>6794233</v>
+        <v>6794178</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3179,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3208,45 +3198,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132814865</v>
+        <v>132814784</v>
       </c>
       <c r="B27" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>420586</v>
+        <v>420420</v>
       </c>
       <c r="R27" t="n">
-        <v>6794106</v>
+        <v>6794140</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3287,6 +3286,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132814706</v>
+        <v>132814864</v>
       </c>
       <c r="B29" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419997</v>
+        <v>420690</v>
       </c>
       <c r="R29" t="n">
-        <v>6793998</v>
+        <v>6794088</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132814864</v>
+        <v>132814844</v>
       </c>
       <c r="B30" t="n">
         <v>79333</v>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>420690</v>
+        <v>420421</v>
       </c>
       <c r="R30" t="n">
-        <v>6794088</v>
+        <v>6794149</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132814844</v>
+        <v>132814737</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,34 +3607,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>420421</v>
+        <v>420586</v>
       </c>
       <c r="R31" t="n">
-        <v>6794149</v>
+        <v>6794009</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132814737</v>
+        <v>132814706</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>79952</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,42 +3712,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>420586</v>
+        <v>419997</v>
       </c>
       <c r="R32" t="n">
-        <v>6794009</v>
+        <v>6793998</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132814828</v>
+        <v>132814769</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3906,34 +3906,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>420306</v>
+        <v>420899</v>
       </c>
       <c r="R34" t="n">
-        <v>6794101</v>
+        <v>6794245</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132814769</v>
+        <v>132814828</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4003,42 +4011,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>420899</v>
+        <v>420306</v>
       </c>
       <c r="R35" t="n">
-        <v>6794245</v>
+        <v>6794101</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814847</v>
+        <v>132814748</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4423,34 +4423,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420443</v>
+        <v>420910</v>
       </c>
       <c r="R39" t="n">
-        <v>6794222</v>
+        <v>6794235</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4509,45 +4517,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132814838</v>
+        <v>132814788</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>420073</v>
+        <v>420693</v>
       </c>
       <c r="R40" t="n">
-        <v>6793986</v>
+        <v>6794082</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4588,6 +4605,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4606,45 +4624,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132814713</v>
+        <v>132814787</v>
       </c>
       <c r="B41" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>420131</v>
+        <v>420878</v>
       </c>
       <c r="R41" t="n">
-        <v>6793962</v>
+        <v>6794218</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4685,6 +4712,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4703,7 +4731,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814701</v>
+        <v>132814713</v>
       </c>
       <c r="B42" t="n">
         <v>79952</v>
@@ -4738,10 +4766,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420311</v>
+        <v>420131</v>
       </c>
       <c r="R42" t="n">
-        <v>6794104</v>
+        <v>6793962</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4800,10 +4828,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132814748</v>
+        <v>132814701</v>
       </c>
       <c r="B43" t="n">
-        <v>57958</v>
+        <v>79952</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4811,42 +4839,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>420910</v>
+        <v>420311</v>
       </c>
       <c r="R43" t="n">
-        <v>6794235</v>
+        <v>6794104</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4905,54 +4925,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814788</v>
+        <v>132814847</v>
       </c>
       <c r="B44" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420693</v>
+        <v>420443</v>
       </c>
       <c r="R44" t="n">
-        <v>6794082</v>
+        <v>6794222</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4993,7 +5004,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5012,54 +5022,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814787</v>
+        <v>132814838</v>
       </c>
       <c r="B45" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420878</v>
+        <v>420073</v>
       </c>
       <c r="R45" t="n">
-        <v>6794218</v>
+        <v>6793986</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,7 +5101,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5119,10 +5119,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132814763</v>
+        <v>132814857</v>
       </c>
       <c r="B46" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5130,42 +5130,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>420057</v>
+        <v>420920</v>
       </c>
       <c r="R46" t="n">
-        <v>6793966</v>
+        <v>6794226</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5224,7 +5216,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132814857</v>
+        <v>132814858</v>
       </c>
       <c r="B47" t="n">
         <v>79333</v>
@@ -5259,10 +5251,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>420920</v>
+        <v>420778</v>
       </c>
       <c r="R47" t="n">
-        <v>6794226</v>
+        <v>6794174</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5321,7 +5313,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132814858</v>
+        <v>132814841</v>
       </c>
       <c r="B48" t="n">
         <v>79333</v>
@@ -5356,10 +5348,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>420778</v>
+        <v>420224</v>
       </c>
       <c r="R48" t="n">
-        <v>6794174</v>
+        <v>6793969</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5418,7 +5410,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132814841</v>
+        <v>132814843</v>
       </c>
       <c r="B49" t="n">
         <v>79333</v>
@@ -5453,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>420224</v>
+        <v>420223</v>
       </c>
       <c r="R49" t="n">
-        <v>6793969</v>
+        <v>6793998</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5515,10 +5507,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132814843</v>
+        <v>132814763</v>
       </c>
       <c r="B50" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5526,34 +5518,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>420223</v>
+        <v>420057</v>
       </c>
       <c r="R50" t="n">
-        <v>6793998</v>
+        <v>6793966</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132814829</v>
+        <v>132814764</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,34 +5730,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>420188</v>
+        <v>420073</v>
       </c>
       <c r="R52" t="n">
-        <v>6794047</v>
+        <v>6793986</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5816,10 +5824,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132814759</v>
+        <v>132814718</v>
       </c>
       <c r="B53" t="n">
-        <v>91939</v>
+        <v>79952</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,37 +5835,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>420574</v>
+        <v>420827</v>
       </c>
       <c r="R53" t="n">
-        <v>6794086</v>
+        <v>6794180</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5898,7 +5903,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5917,7 +5921,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814848</v>
+        <v>132814829</v>
       </c>
       <c r="B54" t="n">
         <v>79333</v>
@@ -5952,10 +5956,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420528</v>
+        <v>420188</v>
       </c>
       <c r="R54" t="n">
-        <v>6794160</v>
+        <v>6794047</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6014,7 +6018,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132814758</v>
+        <v>132814759</v>
       </c>
       <c r="B55" t="n">
         <v>91939</v>
@@ -6052,10 +6056,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>420939</v>
+        <v>420574</v>
       </c>
       <c r="R55" t="n">
-        <v>6794202</v>
+        <v>6794086</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6115,10 +6119,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132814718</v>
+        <v>132814848</v>
       </c>
       <c r="B56" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6126,21 +6130,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6150,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>420827</v>
+        <v>420528</v>
       </c>
       <c r="R56" t="n">
-        <v>6794180</v>
+        <v>6794160</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,10 +6216,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132814764</v>
+        <v>132814758</v>
       </c>
       <c r="B57" t="n">
-        <v>57955</v>
+        <v>91939</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6223,31 +6227,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6255,10 +6254,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>420073</v>
+        <v>420939</v>
       </c>
       <c r="R57" t="n">
-        <v>6793986</v>
+        <v>6794202</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6299,6 +6298,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132814856</v>
+        <v>132814704</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>420936</v>
+        <v>419964</v>
       </c>
       <c r="R61" t="n">
-        <v>6794205</v>
+        <v>6793993</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132814704</v>
+        <v>132814856</v>
       </c>
       <c r="B62" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6716,21 +6716,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419964</v>
+        <v>420936</v>
       </c>
       <c r="R62" t="n">
-        <v>6793993</v>
+        <v>6794205</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7208,40 +7208,41 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132814766</v>
+        <v>132814791</v>
       </c>
       <c r="B67" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7251,10 +7252,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>420516</v>
+        <v>420112</v>
       </c>
       <c r="R67" t="n">
-        <v>6794196</v>
+        <v>6793976</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7295,6 +7296,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7418,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814826</v>
+        <v>132814730</v>
       </c>
       <c r="B69" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7429,21 +7431,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7453,10 +7455,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420418</v>
+        <v>420787</v>
       </c>
       <c r="R69" t="n">
-        <v>6794158</v>
+        <v>6794163</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7515,10 +7517,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132814716</v>
+        <v>132814727</v>
       </c>
       <c r="B70" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7526,21 +7528,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7550,10 +7552,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>420748</v>
+        <v>420903</v>
       </c>
       <c r="R70" t="n">
-        <v>6794107</v>
+        <v>6794237</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7612,10 +7614,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132814719</v>
+        <v>132814766</v>
       </c>
       <c r="B71" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7623,34 +7625,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>420742</v>
+        <v>420516</v>
       </c>
       <c r="R71" t="n">
-        <v>6794108</v>
+        <v>6794196</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7709,54 +7719,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814791</v>
+        <v>132814716</v>
       </c>
       <c r="B72" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420112</v>
+        <v>420748</v>
       </c>
       <c r="R72" t="n">
-        <v>6793976</v>
+        <v>6794107</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7797,7 +7798,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7816,10 +7816,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132814730</v>
+        <v>132814719</v>
       </c>
       <c r="B73" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7827,21 +7827,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>420787</v>
+        <v>420742</v>
       </c>
       <c r="R73" t="n">
-        <v>6794163</v>
+        <v>6794108</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7913,10 +7913,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132814727</v>
+        <v>132814826</v>
       </c>
       <c r="B74" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7924,21 +7924,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>420903</v>
+        <v>420418</v>
       </c>
       <c r="R74" t="n">
-        <v>6794237</v>
+        <v>6794158</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8010,45 +8010,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132814845</v>
+        <v>132814781</v>
       </c>
       <c r="B75" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>420474</v>
+        <v>420113</v>
       </c>
       <c r="R75" t="n">
-        <v>6794142</v>
+        <v>6794031</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8089,6 +8098,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8107,10 +8117,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132814714</v>
+        <v>132814770</v>
       </c>
       <c r="B76" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,34 +8128,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>420233</v>
+        <v>420758</v>
       </c>
       <c r="R76" t="n">
-        <v>6793967</v>
+        <v>6794147</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8204,10 +8222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132814770</v>
+        <v>132814845</v>
       </c>
       <c r="B77" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8215,42 +8233,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>420758</v>
+        <v>420474</v>
       </c>
       <c r="R77" t="n">
-        <v>6794147</v>
+        <v>6794142</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8309,43 +8319,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132814781</v>
+        <v>132814775</v>
       </c>
       <c r="B78" t="n">
-        <v>8455</v>
+        <v>79091</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8353,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>420113</v>
+        <v>420905</v>
       </c>
       <c r="R78" t="n">
-        <v>6794031</v>
+        <v>6794232</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8416,10 +8420,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132814775</v>
+        <v>132814726</v>
       </c>
       <c r="B79" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8427,37 +8431,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>420905</v>
+        <v>420503</v>
       </c>
       <c r="R79" t="n">
-        <v>6794232</v>
+        <v>6794242</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8498,7 +8499,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132814726</v>
+        <v>132814714</v>
       </c>
       <c r="B80" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8528,21 +8528,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>420503</v>
+        <v>420233</v>
       </c>
       <c r="R80" t="n">
-        <v>6794242</v>
+        <v>6793967</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8614,37 +8614,43 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132814866</v>
+        <v>132814783</v>
       </c>
       <c r="B81" t="n">
-        <v>78340</v>
+        <v>8455</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8652,10 +8658,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>420768</v>
+        <v>420406</v>
       </c>
       <c r="R81" t="n">
-        <v>6794178</v>
+        <v>6794117</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8699,31 +8705,6 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -8740,45 +8721,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132814723</v>
+        <v>132814779</v>
       </c>
       <c r="B82" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>420646</v>
+        <v>420605</v>
       </c>
       <c r="R82" t="n">
-        <v>6794161</v>
+        <v>6794008</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8819,6 +8809,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8837,10 +8828,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132814840</v>
+        <v>132814866</v>
       </c>
       <c r="B83" t="n">
-        <v>79333</v>
+        <v>78340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8848,34 +8839,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>420214</v>
+        <v>420768</v>
       </c>
       <c r="R83" t="n">
-        <v>6793964</v>
+        <v>6794178</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8916,8 +8910,34 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -8934,10 +8954,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132814830</v>
+        <v>132814723</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8945,21 +8965,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8969,10 +8989,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>420156</v>
+        <v>420646</v>
       </c>
       <c r="R84" t="n">
-        <v>6794036</v>
+        <v>6794161</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9031,54 +9051,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132814783</v>
+        <v>132814840</v>
       </c>
       <c r="B85" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>420406</v>
+        <v>420214</v>
       </c>
       <c r="R85" t="n">
-        <v>6794117</v>
+        <v>6793964</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9119,7 +9130,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9138,54 +9148,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132814779</v>
+        <v>132814830</v>
       </c>
       <c r="B86" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>420605</v>
+        <v>420156</v>
       </c>
       <c r="R86" t="n">
-        <v>6794008</v>
+        <v>6794036</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9226,7 +9227,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10122,54 +10122,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132814782</v>
+        <v>132814724</v>
       </c>
       <c r="B96" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>420074</v>
+        <v>420166</v>
       </c>
       <c r="R96" t="n">
-        <v>6793987</v>
+        <v>6793967</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10210,7 +10201,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10229,10 +10219,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132814852</v>
+        <v>132814721</v>
       </c>
       <c r="B97" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10240,21 +10230,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10264,10 +10254,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>420835</v>
+        <v>420709</v>
       </c>
       <c r="R97" t="n">
-        <v>6794144</v>
+        <v>6794077</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10326,7 +10316,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132814851</v>
+        <v>132814852</v>
       </c>
       <c r="B98" t="n">
         <v>79333</v>
@@ -10361,10 +10351,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>420801</v>
+        <v>420835</v>
       </c>
       <c r="R98" t="n">
-        <v>6794114</v>
+        <v>6794144</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10423,10 +10413,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132814724</v>
+        <v>132814851</v>
       </c>
       <c r="B99" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10434,21 +10424,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10458,10 +10448,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>420166</v>
+        <v>420801</v>
       </c>
       <c r="R99" t="n">
-        <v>6793967</v>
+        <v>6794114</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10520,10 +10510,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132814721</v>
+        <v>132814742</v>
       </c>
       <c r="B100" t="n">
-        <v>79952</v>
+        <v>57958</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10531,34 +10521,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>420709</v>
+        <v>420570</v>
       </c>
       <c r="R100" t="n">
-        <v>6794077</v>
+        <v>6794049</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10617,32 +10615,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132814742</v>
+        <v>132814751</v>
       </c>
       <c r="B101" t="n">
-        <v>57958</v>
+        <v>57145</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10650,7 +10648,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -10660,10 +10658,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>420570</v>
+        <v>420599</v>
       </c>
       <c r="R101" t="n">
-        <v>6794049</v>
+        <v>6794022</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10827,10 +10825,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132814751</v>
+        <v>132814782</v>
       </c>
       <c r="B103" t="n">
-        <v>57145</v>
+        <v>8455</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10838,29 +10836,30 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -10870,10 +10869,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>420599</v>
+        <v>420074</v>
       </c>
       <c r="R103" t="n">
-        <v>6794022</v>
+        <v>6793987</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10914,6 +10913,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132814768</v>
+        <v>132814709</v>
       </c>
       <c r="B104" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10943,42 +10943,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>420900</v>
+        <v>420028</v>
       </c>
       <c r="R104" t="n">
-        <v>6794252</v>
+        <v>6793991</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11037,10 +11029,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132814777</v>
+        <v>132814859</v>
       </c>
       <c r="B105" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11048,21 +11040,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11072,10 +11064,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>420706</v>
+        <v>420739</v>
       </c>
       <c r="R105" t="n">
-        <v>6794078</v>
+        <v>6794114</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11134,10 +11126,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132814859</v>
+        <v>132814768</v>
       </c>
       <c r="B106" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11145,34 +11137,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>420739</v>
+        <v>420900</v>
       </c>
       <c r="R106" t="n">
-        <v>6794114</v>
+        <v>6794252</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11231,10 +11231,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132814709</v>
+        <v>132814777</v>
       </c>
       <c r="B107" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11242,21 +11242,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11266,10 +11266,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>420028</v>
+        <v>420706</v>
       </c>
       <c r="R107" t="n">
-        <v>6793991</v>
+        <v>6794078</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132814771</v>
+        <v>132814710</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420677</v>
+        <v>420053</v>
       </c>
       <c r="R2" t="n">
-        <v>6794147</v>
+        <v>6793980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132814765</v>
+        <v>132814771</v>
       </c>
       <c r="B3" t="n">
         <v>57955</v>
@@ -813,7 +809,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420459</v>
+        <v>420677</v>
       </c>
       <c r="R3" t="n">
-        <v>6794159</v>
+        <v>6794147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132814710</v>
+        <v>132814765</v>
       </c>
       <c r="B4" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,26 +892,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420053</v>
+        <v>420459</v>
       </c>
       <c r="R4" t="n">
-        <v>6793980</v>
+        <v>6794159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +968,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132814744</v>
+        <v>132814738</v>
       </c>
       <c r="B8" t="n">
         <v>57958</v>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420576</v>
+        <v>420583</v>
       </c>
       <c r="R8" t="n">
-        <v>6794051</v>
+        <v>6794016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132814738</v>
+        <v>132814744</v>
       </c>
       <c r="B9" t="n">
         <v>57958</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420583</v>
+        <v>420576</v>
       </c>
       <c r="R9" t="n">
-        <v>6794016</v>
+        <v>6794051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132814839</v>
+        <v>132814705</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>420171</v>
+        <v>419964</v>
       </c>
       <c r="R10" t="n">
-        <v>6793959</v>
+        <v>6793990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132814831</v>
+        <v>132814839</v>
       </c>
       <c r="B11" t="n">
         <v>79333</v>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>420020</v>
+        <v>420171</v>
       </c>
       <c r="R11" t="n">
-        <v>6794011</v>
+        <v>6793959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132814827</v>
+        <v>132814831</v>
       </c>
       <c r="B12" t="n">
         <v>79333</v>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>420331</v>
+        <v>420020</v>
       </c>
       <c r="R12" t="n">
-        <v>6794169</v>
+        <v>6794011</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132814705</v>
+        <v>132814827</v>
       </c>
       <c r="B13" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419964</v>
+        <v>420331</v>
       </c>
       <c r="R13" t="n">
-        <v>6793990</v>
+        <v>6794169</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132814762</v>
+        <v>132814732</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>79923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,42 +2391,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>419986</v>
+        <v>420740</v>
       </c>
       <c r="R19" t="n">
-        <v>6793995</v>
+        <v>6794120</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814792</v>
+        <v>132814762</v>
       </c>
       <c r="B21" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2601,16 +2593,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2623,7 +2615,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2633,10 +2625,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420554</v>
+        <v>419986</v>
       </c>
       <c r="R21" t="n">
-        <v>6794096</v>
+        <v>6793995</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,27 +2687,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814773</v>
+        <v>132814792</v>
       </c>
       <c r="B22" t="n">
-        <v>57148</v>
+        <v>57136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2728,7 +2720,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2738,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420920</v>
+        <v>420554</v>
       </c>
       <c r="R22" t="n">
-        <v>6794225</v>
+        <v>6794096</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2800,45 +2792,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132814732</v>
+        <v>132814773</v>
       </c>
       <c r="B23" t="n">
-        <v>79923</v>
+        <v>57148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>420740</v>
+        <v>420920</v>
       </c>
       <c r="R23" t="n">
-        <v>6794120</v>
+        <v>6794225</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,45 +2897,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814715</v>
+        <v>132814786</v>
       </c>
       <c r="B24" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420524</v>
+        <v>420459</v>
       </c>
       <c r="R24" t="n">
-        <v>6794233</v>
+        <v>6794178</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,6 +2985,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2994,45 +3004,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814865</v>
+        <v>132814784</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420586</v>
+        <v>420420</v>
       </c>
       <c r="R25" t="n">
-        <v>6794106</v>
+        <v>6794140</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3073,6 +3092,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3091,54 +3111,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132814786</v>
+        <v>132814715</v>
       </c>
       <c r="B26" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>420459</v>
+        <v>420524</v>
       </c>
       <c r="R26" t="n">
-        <v>6794178</v>
+        <v>6794233</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,7 +3190,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3198,54 +3208,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132814784</v>
+        <v>132814865</v>
       </c>
       <c r="B27" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>420420</v>
+        <v>420586</v>
       </c>
       <c r="R27" t="n">
-        <v>6794140</v>
+        <v>6794106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3286,7 +3287,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132814864</v>
+        <v>132814706</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>420690</v>
+        <v>419997</v>
       </c>
       <c r="R29" t="n">
-        <v>6794088</v>
+        <v>6793998</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132814844</v>
+        <v>132814864</v>
       </c>
       <c r="B30" t="n">
         <v>79333</v>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>420421</v>
+        <v>420690</v>
       </c>
       <c r="R30" t="n">
-        <v>6794149</v>
+        <v>6794088</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132814737</v>
+        <v>132814844</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,42 +3607,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>420586</v>
+        <v>420421</v>
       </c>
       <c r="R31" t="n">
-        <v>6794009</v>
+        <v>6794149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132814706</v>
+        <v>132814737</v>
       </c>
       <c r="B32" t="n">
-        <v>79952</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3712,34 +3704,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419997</v>
+        <v>420586</v>
       </c>
       <c r="R32" t="n">
-        <v>6793998</v>
+        <v>6794009</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132814769</v>
+        <v>132814828</v>
       </c>
       <c r="B34" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3906,42 +3906,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>420899</v>
+        <v>420306</v>
       </c>
       <c r="R34" t="n">
-        <v>6794245</v>
+        <v>6794101</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4000,10 +3992,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132814828</v>
+        <v>132814769</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,34 +4003,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>420306</v>
+        <v>420899</v>
       </c>
       <c r="R35" t="n">
-        <v>6794101</v>
+        <v>6794245</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132814767</v>
+        <v>132814847</v>
       </c>
       <c r="B38" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4318,42 +4318,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420588</v>
+        <v>420443</v>
       </c>
       <c r="R38" t="n">
-        <v>6794046</v>
+        <v>6794222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4412,10 +4404,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814748</v>
+        <v>132814838</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4423,42 +4415,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420910</v>
+        <v>420073</v>
       </c>
       <c r="R39" t="n">
-        <v>6794235</v>
+        <v>6793986</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4517,54 +4501,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132814788</v>
+        <v>132814713</v>
       </c>
       <c r="B40" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>420693</v>
+        <v>420131</v>
       </c>
       <c r="R40" t="n">
-        <v>6794082</v>
+        <v>6793962</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4605,7 +4580,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4624,54 +4598,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132814787</v>
+        <v>132814701</v>
       </c>
       <c r="B41" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>420878</v>
+        <v>420311</v>
       </c>
       <c r="R41" t="n">
-        <v>6794218</v>
+        <v>6794104</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4712,7 +4677,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4731,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814713</v>
+        <v>132814748</v>
       </c>
       <c r="B42" t="n">
-        <v>79952</v>
+        <v>57958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4742,34 +4706,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420131</v>
+        <v>420910</v>
       </c>
       <c r="R42" t="n">
-        <v>6793962</v>
+        <v>6794235</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4828,45 +4800,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132814701</v>
+        <v>132814788</v>
       </c>
       <c r="B43" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>420311</v>
+        <v>420693</v>
       </c>
       <c r="R43" t="n">
-        <v>6794104</v>
+        <v>6794082</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4907,6 +4888,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4925,45 +4907,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814847</v>
+        <v>132814787</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420443</v>
+        <v>420878</v>
       </c>
       <c r="R44" t="n">
-        <v>6794222</v>
+        <v>6794218</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5004,6 +4995,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5022,10 +5014,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814838</v>
+        <v>132814767</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5033,34 +5025,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420073</v>
+        <v>420588</v>
       </c>
       <c r="R45" t="n">
-        <v>6793986</v>
+        <v>6794046</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5824,10 +5824,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132814718</v>
+        <v>132814829</v>
       </c>
       <c r="B53" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>420827</v>
+        <v>420188</v>
       </c>
       <c r="R53" t="n">
-        <v>6794180</v>
+        <v>6794047</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814829</v>
+        <v>132814759</v>
       </c>
       <c r="B54" t="n">
-        <v>79333</v>
+        <v>91939</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5932,34 +5932,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420188</v>
+        <v>420574</v>
       </c>
       <c r="R54" t="n">
-        <v>6794047</v>
+        <v>6794086</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6000,6 +6003,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6018,10 +6022,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132814759</v>
+        <v>132814848</v>
       </c>
       <c r="B55" t="n">
-        <v>91939</v>
+        <v>79333</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6029,37 +6033,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>420574</v>
+        <v>420528</v>
       </c>
       <c r="R55" t="n">
-        <v>6794086</v>
+        <v>6794160</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6100,7 +6101,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6119,10 +6119,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132814848</v>
+        <v>132814758</v>
       </c>
       <c r="B56" t="n">
-        <v>79333</v>
+        <v>91939</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6130,34 +6130,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>420528</v>
+        <v>420939</v>
       </c>
       <c r="R56" t="n">
-        <v>6794160</v>
+        <v>6794202</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6198,6 +6201,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6216,10 +6220,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132814758</v>
+        <v>132814718</v>
       </c>
       <c r="B57" t="n">
-        <v>91939</v>
+        <v>79952</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6227,37 +6231,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>420939</v>
+        <v>420827</v>
       </c>
       <c r="R57" t="n">
-        <v>6794202</v>
+        <v>6794180</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6298,7 +6299,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6608,45 +6608,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132814704</v>
+        <v>132814750</v>
       </c>
       <c r="B61" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419964</v>
+        <v>420114</v>
       </c>
       <c r="R61" t="n">
-        <v>6793993</v>
+        <v>6793974</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6705,10 +6713,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132814856</v>
+        <v>132814776</v>
       </c>
       <c r="B62" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6716,21 +6724,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6740,10 +6748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>420936</v>
+        <v>420807</v>
       </c>
       <c r="R62" t="n">
-        <v>6794205</v>
+        <v>6794179</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6802,10 +6810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132814776</v>
+        <v>132814856</v>
       </c>
       <c r="B63" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6813,21 +6821,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6837,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>420807</v>
+        <v>420936</v>
       </c>
       <c r="R63" t="n">
-        <v>6794179</v>
+        <v>6794205</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6899,53 +6907,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132814750</v>
+        <v>132814704</v>
       </c>
       <c r="B64" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>420114</v>
+        <v>419964</v>
       </c>
       <c r="R64" t="n">
-        <v>6793974</v>
+        <v>6793993</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7208,41 +7208,40 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132814791</v>
+        <v>132814766</v>
       </c>
       <c r="B67" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7252,10 +7251,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>420112</v>
+        <v>420516</v>
       </c>
       <c r="R67" t="n">
-        <v>6793976</v>
+        <v>6794196</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7296,7 +7295,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7315,40 +7313,41 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132814794</v>
+        <v>132814791</v>
       </c>
       <c r="B68" t="n">
-        <v>56522</v>
+        <v>8455</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7358,10 +7357,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>420170</v>
+        <v>420112</v>
       </c>
       <c r="R68" t="n">
-        <v>6793954</v>
+        <v>6793976</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7402,6 +7401,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814730</v>
+        <v>132814794</v>
       </c>
       <c r="B69" t="n">
-        <v>79923</v>
+        <v>56522</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,34 +7431,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>206004</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420787</v>
+        <v>420170</v>
       </c>
       <c r="R69" t="n">
-        <v>6794163</v>
+        <v>6793954</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7614,10 +7622,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132814766</v>
+        <v>132814730</v>
       </c>
       <c r="B71" t="n">
-        <v>57955</v>
+        <v>79923</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,42 +7633,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>420516</v>
+        <v>420787</v>
       </c>
       <c r="R71" t="n">
-        <v>6794196</v>
+        <v>6794163</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7719,10 +7719,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814716</v>
+        <v>132814826</v>
       </c>
       <c r="B72" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7730,21 +7730,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7754,10 +7754,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420748</v>
+        <v>420418</v>
       </c>
       <c r="R72" t="n">
-        <v>6794107</v>
+        <v>6794158</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7816,7 +7816,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132814719</v>
+        <v>132814716</v>
       </c>
       <c r="B73" t="n">
         <v>79952</v>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>420742</v>
+        <v>420748</v>
       </c>
       <c r="R73" t="n">
-        <v>6794108</v>
+        <v>6794107</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7913,10 +7913,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132814826</v>
+        <v>132814719</v>
       </c>
       <c r="B74" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7924,21 +7924,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>420418</v>
+        <v>420742</v>
       </c>
       <c r="R74" t="n">
-        <v>6794158</v>
+        <v>6794108</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8010,54 +8010,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132814781</v>
+        <v>132814845</v>
       </c>
       <c r="B75" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>420113</v>
+        <v>420474</v>
       </c>
       <c r="R75" t="n">
-        <v>6794031</v>
+        <v>6794142</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8098,7 +8089,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8117,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132814770</v>
+        <v>132814714</v>
       </c>
       <c r="B76" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8128,42 +8118,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>420758</v>
+        <v>420233</v>
       </c>
       <c r="R76" t="n">
-        <v>6794147</v>
+        <v>6793967</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,10 +8204,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132814845</v>
+        <v>132814770</v>
       </c>
       <c r="B77" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,34 +8215,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>420474</v>
+        <v>420758</v>
       </c>
       <c r="R77" t="n">
-        <v>6794142</v>
+        <v>6794147</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8319,10 +8309,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132814775</v>
+        <v>132814726</v>
       </c>
       <c r="B78" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,37 +8320,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>420905</v>
+        <v>420503</v>
       </c>
       <c r="R78" t="n">
-        <v>6794232</v>
+        <v>6794242</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8401,7 +8388,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8420,10 +8406,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132814726</v>
+        <v>132814775</v>
       </c>
       <c r="B79" t="n">
-        <v>79923</v>
+        <v>79091</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8431,34 +8417,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>420503</v>
+        <v>420905</v>
       </c>
       <c r="R79" t="n">
-        <v>6794242</v>
+        <v>6794232</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,6 +8488,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8517,45 +8507,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132814714</v>
+        <v>132814781</v>
       </c>
       <c r="B80" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>420233</v>
+        <v>420113</v>
       </c>
       <c r="R80" t="n">
-        <v>6793967</v>
+        <v>6794031</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8596,6 +8595,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132814702</v>
+        <v>132814731</v>
       </c>
       <c r="B87" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,21 +9256,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>420119</v>
+        <v>420768</v>
       </c>
       <c r="R87" t="n">
-        <v>6794012</v>
+        <v>6794179</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132814850</v>
+        <v>132814734</v>
       </c>
       <c r="B88" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9353,21 +9353,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9377,10 +9377,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>420549</v>
+        <v>420696</v>
       </c>
       <c r="R88" t="n">
-        <v>6794103</v>
+        <v>6794141</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9439,10 +9439,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132814833</v>
+        <v>132814702</v>
       </c>
       <c r="B89" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9450,21 +9450,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419996</v>
+        <v>420119</v>
       </c>
       <c r="R89" t="n">
-        <v>6793995</v>
+        <v>6794012</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9536,10 +9536,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132814734</v>
+        <v>132814850</v>
       </c>
       <c r="B90" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9547,21 +9547,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>420696</v>
+        <v>420549</v>
       </c>
       <c r="R90" t="n">
-        <v>6794141</v>
+        <v>6794103</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132814731</v>
+        <v>132814833</v>
       </c>
       <c r="B91" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9644,21 +9644,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>420768</v>
+        <v>419996</v>
       </c>
       <c r="R91" t="n">
-        <v>6794179</v>
+        <v>6793995</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132814735</v>
+        <v>132814836</v>
       </c>
       <c r="B92" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9741,37 +9741,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>420683</v>
+        <v>420025</v>
       </c>
       <c r="R92" t="n">
-        <v>6794145</v>
+        <v>6793989</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9812,7 +9809,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9831,10 +9827,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132814725</v>
+        <v>132814849</v>
       </c>
       <c r="B93" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9842,21 +9838,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9866,10 +9862,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>420114</v>
+        <v>420548</v>
       </c>
       <c r="R93" t="n">
-        <v>6793974</v>
+        <v>6794121</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9928,10 +9924,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132814836</v>
+        <v>132814735</v>
       </c>
       <c r="B94" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9939,34 +9935,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>420025</v>
+        <v>420683</v>
       </c>
       <c r="R94" t="n">
-        <v>6793989</v>
+        <v>6794145</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10007,6 +10006,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10025,10 +10025,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132814849</v>
+        <v>132814725</v>
       </c>
       <c r="B95" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10036,21 +10036,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>420548</v>
+        <v>420114</v>
       </c>
       <c r="R95" t="n">
-        <v>6794121</v>
+        <v>6793974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10122,10 +10122,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132814724</v>
+        <v>132814742</v>
       </c>
       <c r="B96" t="n">
-        <v>79952</v>
+        <v>57958</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10133,34 +10133,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>420166</v>
+        <v>420570</v>
       </c>
       <c r="R96" t="n">
-        <v>6793967</v>
+        <v>6794049</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10219,45 +10227,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132814721</v>
+        <v>132814782</v>
       </c>
       <c r="B97" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>420709</v>
+        <v>420074</v>
       </c>
       <c r="R97" t="n">
-        <v>6794077</v>
+        <v>6793987</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10298,6 +10315,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10510,10 +10528,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132814742</v>
+        <v>132814724</v>
       </c>
       <c r="B100" t="n">
-        <v>57958</v>
+        <v>79952</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10521,42 +10539,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>420570</v>
+        <v>420166</v>
       </c>
       <c r="R100" t="n">
-        <v>6794049</v>
+        <v>6793967</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10615,53 +10625,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132814751</v>
+        <v>132814721</v>
       </c>
       <c r="B101" t="n">
-        <v>57145</v>
+        <v>79952</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>420599</v>
+        <v>420709</v>
       </c>
       <c r="R101" t="n">
-        <v>6794022</v>
+        <v>6794077</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10825,10 +10827,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132814782</v>
+        <v>132814751</v>
       </c>
       <c r="B103" t="n">
-        <v>8455</v>
+        <v>57145</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10836,30 +10838,29 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -10869,10 +10870,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>420074</v>
+        <v>420599</v>
       </c>
       <c r="R103" t="n">
-        <v>6793987</v>
+        <v>6794022</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10913,7 +10914,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132814709</v>
+        <v>132814768</v>
       </c>
       <c r="B104" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10943,34 +10943,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>420028</v>
+        <v>420900</v>
       </c>
       <c r="R104" t="n">
-        <v>6793991</v>
+        <v>6794252</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11126,10 +11134,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132814768</v>
+        <v>132814709</v>
       </c>
       <c r="B106" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11137,42 +11145,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>420900</v>
+        <v>420028</v>
       </c>
       <c r="R106" t="n">
-        <v>6794252</v>
+        <v>6793991</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132814705</v>
+        <v>132814839</v>
       </c>
       <c r="B10" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419964</v>
+        <v>420171</v>
       </c>
       <c r="R10" t="n">
-        <v>6793990</v>
+        <v>6793959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132814839</v>
+        <v>132814831</v>
       </c>
       <c r="B11" t="n">
         <v>79333</v>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>420171</v>
+        <v>420020</v>
       </c>
       <c r="R11" t="n">
-        <v>6793959</v>
+        <v>6794011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132814831</v>
+        <v>132814827</v>
       </c>
       <c r="B12" t="n">
         <v>79333</v>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>420020</v>
+        <v>420331</v>
       </c>
       <c r="R12" t="n">
-        <v>6794011</v>
+        <v>6794169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132814827</v>
+        <v>132814705</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>420331</v>
+        <v>419964</v>
       </c>
       <c r="R13" t="n">
-        <v>6794169</v>
+        <v>6793990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132814711</v>
+        <v>132814732</v>
       </c>
       <c r="B14" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,21 +1906,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420109</v>
+        <v>420740</v>
       </c>
       <c r="R14" t="n">
-        <v>6793976</v>
+        <v>6794120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,7 +1992,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814712</v>
+        <v>132814711</v>
       </c>
       <c r="B15" t="n">
         <v>79952</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420126</v>
+        <v>420109</v>
       </c>
       <c r="R15" t="n">
-        <v>6793969</v>
+        <v>6793976</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132814861</v>
+        <v>132814712</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420752</v>
+        <v>420126</v>
       </c>
       <c r="R16" t="n">
-        <v>6794099</v>
+        <v>6793969</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132814860</v>
+        <v>132814861</v>
       </c>
       <c r="B17" t="n">
         <v>79333</v>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420745</v>
+        <v>420752</v>
       </c>
       <c r="R17" t="n">
-        <v>6794098</v>
+        <v>6794099</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132814863</v>
+        <v>132814860</v>
       </c>
       <c r="B18" t="n">
         <v>79333</v>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>420725</v>
+        <v>420745</v>
       </c>
       <c r="R18" t="n">
-        <v>6794081</v>
+        <v>6794098</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132814732</v>
+        <v>132814863</v>
       </c>
       <c r="B19" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,21 +2391,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420740</v>
+        <v>420725</v>
       </c>
       <c r="R19" t="n">
-        <v>6794120</v>
+        <v>6794081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132814761</v>
+        <v>132814762</v>
       </c>
       <c r="B20" t="n">
         <v>57955</v>
@@ -2510,7 +2510,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>420119</v>
+        <v>419986</v>
       </c>
       <c r="R20" t="n">
-        <v>6794010</v>
+        <v>6793995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814762</v>
+        <v>132814761</v>
       </c>
       <c r="B21" t="n">
         <v>57955</v>
@@ -2615,7 +2615,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419986</v>
+        <v>420119</v>
       </c>
       <c r="R21" t="n">
-        <v>6793995</v>
+        <v>6794010</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,54 +2897,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814786</v>
+        <v>132814715</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420459</v>
+        <v>420524</v>
       </c>
       <c r="R24" t="n">
-        <v>6794178</v>
+        <v>6794233</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2985,7 +2976,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3004,54 +2994,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814784</v>
+        <v>132814865</v>
       </c>
       <c r="B25" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420420</v>
+        <v>420586</v>
       </c>
       <c r="R25" t="n">
-        <v>6794140</v>
+        <v>6794106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3092,7 +3073,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3111,45 +3091,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132814715</v>
+        <v>132814786</v>
       </c>
       <c r="B26" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>420524</v>
+        <v>420459</v>
       </c>
       <c r="R26" t="n">
-        <v>6794233</v>
+        <v>6794178</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3179,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3208,45 +3198,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132814865</v>
+        <v>132814784</v>
       </c>
       <c r="B27" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>420586</v>
+        <v>420420</v>
       </c>
       <c r="R27" t="n">
-        <v>6794106</v>
+        <v>6794140</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3287,6 +3286,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132814832</v>
+        <v>132814706</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419983</v>
+        <v>419997</v>
       </c>
       <c r="R28" t="n">
-        <v>6793990</v>
+        <v>6793998</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132814706</v>
+        <v>132814832</v>
       </c>
       <c r="B29" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419997</v>
+        <v>419983</v>
       </c>
       <c r="R29" t="n">
-        <v>6793998</v>
+        <v>6793990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4307,45 +4307,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132814847</v>
+        <v>132814788</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420443</v>
+        <v>420693</v>
       </c>
       <c r="R38" t="n">
-        <v>6794222</v>
+        <v>6794082</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4386,6 +4395,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4404,45 +4414,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814838</v>
+        <v>132814787</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420073</v>
+        <v>420878</v>
       </c>
       <c r="R39" t="n">
-        <v>6793986</v>
+        <v>6794218</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,6 +4502,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4695,10 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132814748</v>
+        <v>132814847</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,42 +4726,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>420910</v>
+        <v>420443</v>
       </c>
       <c r="R42" t="n">
-        <v>6794235</v>
+        <v>6794222</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4800,54 +4812,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132814788</v>
+        <v>132814838</v>
       </c>
       <c r="B43" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>420693</v>
+        <v>420073</v>
       </c>
       <c r="R43" t="n">
-        <v>6794082</v>
+        <v>6793986</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,7 +4891,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4907,41 +4909,40 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814787</v>
+        <v>132814767</v>
       </c>
       <c r="B44" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4951,10 +4952,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420878</v>
+        <v>420588</v>
       </c>
       <c r="R44" t="n">
-        <v>6794218</v>
+        <v>6794046</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,7 +4996,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814767</v>
+        <v>132814748</v>
       </c>
       <c r="B45" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5047,7 +5047,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420588</v>
+        <v>420910</v>
       </c>
       <c r="R45" t="n">
-        <v>6794046</v>
+        <v>6794235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5313,10 +5313,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132814841</v>
+        <v>132814763</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5324,34 +5324,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>420224</v>
+        <v>420057</v>
       </c>
       <c r="R48" t="n">
-        <v>6793969</v>
+        <v>6793966</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5410,7 +5418,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132814843</v>
+        <v>132814841</v>
       </c>
       <c r="B49" t="n">
         <v>79333</v>
@@ -5445,10 +5453,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>420223</v>
+        <v>420224</v>
       </c>
       <c r="R49" t="n">
-        <v>6793998</v>
+        <v>6793969</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5507,10 +5515,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132814763</v>
+        <v>132814843</v>
       </c>
       <c r="B50" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5518,42 +5526,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>420057</v>
+        <v>420223</v>
       </c>
       <c r="R50" t="n">
-        <v>6793966</v>
+        <v>6793998</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132814764</v>
+        <v>132814718</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,42 +5730,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>420073</v>
+        <v>420827</v>
       </c>
       <c r="R52" t="n">
-        <v>6793986</v>
+        <v>6794180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6220,10 +6212,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132814718</v>
+        <v>132814764</v>
       </c>
       <c r="B57" t="n">
-        <v>79952</v>
+        <v>57955</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6231,34 +6223,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>420827</v>
+        <v>420073</v>
       </c>
       <c r="R57" t="n">
-        <v>6794180</v>
+        <v>6793986</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132814776</v>
+        <v>132814704</v>
       </c>
       <c r="B62" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6724,21 +6724,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>420807</v>
+        <v>419964</v>
       </c>
       <c r="R62" t="n">
-        <v>6794179</v>
+        <v>6793993</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132814704</v>
+        <v>132814776</v>
       </c>
       <c r="B64" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6918,21 +6918,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419964</v>
+        <v>420807</v>
       </c>
       <c r="R64" t="n">
-        <v>6793993</v>
+        <v>6794179</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,45 +7004,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132814720</v>
+        <v>132814789</v>
       </c>
       <c r="B65" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>420755</v>
+        <v>420681</v>
       </c>
       <c r="R65" t="n">
-        <v>6794087</v>
+        <v>6794073</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7083,6 +7092,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7101,54 +7111,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132814789</v>
+        <v>132814720</v>
       </c>
       <c r="B66" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>420681</v>
+        <v>420755</v>
       </c>
       <c r="R66" t="n">
-        <v>6794073</v>
+        <v>6794087</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7189,7 +7190,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132814766</v>
+        <v>132814716</v>
       </c>
       <c r="B67" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7219,42 +7219,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>420516</v>
+        <v>420748</v>
       </c>
       <c r="R67" t="n">
-        <v>6794196</v>
+        <v>6794107</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7313,54 +7305,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132814791</v>
+        <v>132814719</v>
       </c>
       <c r="B68" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>420112</v>
+        <v>420742</v>
       </c>
       <c r="R68" t="n">
-        <v>6793976</v>
+        <v>6794108</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7401,7 +7384,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7420,10 +7402,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814794</v>
+        <v>132814826</v>
       </c>
       <c r="B69" t="n">
-        <v>56522</v>
+        <v>79333</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,42 +7413,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420170</v>
+        <v>420418</v>
       </c>
       <c r="R69" t="n">
-        <v>6793954</v>
+        <v>6794158</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7525,10 +7499,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132814727</v>
+        <v>132814766</v>
       </c>
       <c r="B70" t="n">
-        <v>79923</v>
+        <v>57955</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7536,34 +7510,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>420903</v>
+        <v>420516</v>
       </c>
       <c r="R70" t="n">
-        <v>6794237</v>
+        <v>6794196</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7622,45 +7604,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132814730</v>
+        <v>132814791</v>
       </c>
       <c r="B71" t="n">
-        <v>79923</v>
+        <v>8455</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>420787</v>
+        <v>420112</v>
       </c>
       <c r="R71" t="n">
-        <v>6794163</v>
+        <v>6793976</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7701,6 +7692,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7719,10 +7711,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814826</v>
+        <v>132814730</v>
       </c>
       <c r="B72" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7730,21 +7722,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7754,10 +7746,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420418</v>
+        <v>420787</v>
       </c>
       <c r="R72" t="n">
-        <v>6794158</v>
+        <v>6794163</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7816,10 +7808,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132814716</v>
+        <v>132814727</v>
       </c>
       <c r="B73" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7827,21 +7819,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7851,10 +7843,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>420748</v>
+        <v>420903</v>
       </c>
       <c r="R73" t="n">
-        <v>6794107</v>
+        <v>6794237</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7913,10 +7905,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132814719</v>
+        <v>132814794</v>
       </c>
       <c r="B74" t="n">
-        <v>79952</v>
+        <v>56522</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7924,34 +7916,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>206004</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>420742</v>
+        <v>420170</v>
       </c>
       <c r="R74" t="n">
-        <v>6794108</v>
+        <v>6793954</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8010,10 +8010,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132814845</v>
+        <v>132814714</v>
       </c>
       <c r="B75" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8021,21 +8021,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>420474</v>
+        <v>420233</v>
       </c>
       <c r="R75" t="n">
-        <v>6794142</v>
+        <v>6793967</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8107,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132814714</v>
+        <v>132814845</v>
       </c>
       <c r="B76" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,21 +8118,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>420233</v>
+        <v>420474</v>
       </c>
       <c r="R76" t="n">
-        <v>6793967</v>
+        <v>6794142</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132814726</v>
+        <v>132814775</v>
       </c>
       <c r="B78" t="n">
-        <v>79923</v>
+        <v>79091</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8320,34 +8320,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>420503</v>
+        <v>420905</v>
       </c>
       <c r="R78" t="n">
-        <v>6794242</v>
+        <v>6794232</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8388,6 +8391,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8406,10 +8410,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132814775</v>
+        <v>132814726</v>
       </c>
       <c r="B79" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8417,37 +8421,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>420905</v>
+        <v>420503</v>
       </c>
       <c r="R79" t="n">
-        <v>6794232</v>
+        <v>6794242</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8488,7 +8489,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132814731</v>
+        <v>132814702</v>
       </c>
       <c r="B87" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,21 +9256,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>420768</v>
+        <v>420119</v>
       </c>
       <c r="R87" t="n">
-        <v>6794179</v>
+        <v>6794012</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132814734</v>
+        <v>132814850</v>
       </c>
       <c r="B88" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9353,21 +9353,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9377,10 +9377,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>420696</v>
+        <v>420549</v>
       </c>
       <c r="R88" t="n">
-        <v>6794141</v>
+        <v>6794103</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9439,10 +9439,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132814702</v>
+        <v>132814833</v>
       </c>
       <c r="B89" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9450,21 +9450,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>420119</v>
+        <v>419996</v>
       </c>
       <c r="R89" t="n">
-        <v>6794012</v>
+        <v>6793995</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9536,10 +9536,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132814850</v>
+        <v>132814734</v>
       </c>
       <c r="B90" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9547,21 +9547,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9571,10 +9571,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>420549</v>
+        <v>420696</v>
       </c>
       <c r="R90" t="n">
-        <v>6794103</v>
+        <v>6794141</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132814833</v>
+        <v>132814731</v>
       </c>
       <c r="B91" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9644,21 +9644,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419996</v>
+        <v>420768</v>
       </c>
       <c r="R91" t="n">
-        <v>6793995</v>
+        <v>6794179</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132814836</v>
+        <v>132814735</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9741,34 +9741,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>420025</v>
+        <v>420683</v>
       </c>
       <c r="R92" t="n">
-        <v>6793989</v>
+        <v>6794145</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9809,6 +9812,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9827,10 +9831,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132814849</v>
+        <v>132814725</v>
       </c>
       <c r="B93" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9838,21 +9842,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9862,10 +9866,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>420548</v>
+        <v>420114</v>
       </c>
       <c r="R93" t="n">
-        <v>6794121</v>
+        <v>6793974</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9924,10 +9928,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132814735</v>
+        <v>132814836</v>
       </c>
       <c r="B94" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9935,37 +9939,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>420683</v>
+        <v>420025</v>
       </c>
       <c r="R94" t="n">
-        <v>6794145</v>
+        <v>6793989</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10006,7 +10007,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10025,10 +10025,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132814725</v>
+        <v>132814849</v>
       </c>
       <c r="B95" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10036,21 +10036,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>420114</v>
+        <v>420548</v>
       </c>
       <c r="R95" t="n">
-        <v>6793974</v>
+        <v>6794121</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10122,10 +10122,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132814742</v>
+        <v>132814852</v>
       </c>
       <c r="B96" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10133,42 +10133,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>420570</v>
+        <v>420835</v>
       </c>
       <c r="R96" t="n">
-        <v>6794049</v>
+        <v>6794144</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10227,54 +10219,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132814782</v>
+        <v>132814851</v>
       </c>
       <c r="B97" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>420074</v>
+        <v>420801</v>
       </c>
       <c r="R97" t="n">
-        <v>6793987</v>
+        <v>6794114</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10315,7 +10298,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10334,10 +10316,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132814852</v>
+        <v>132814742</v>
       </c>
       <c r="B98" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10345,34 +10327,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>420835</v>
+        <v>420570</v>
       </c>
       <c r="R98" t="n">
-        <v>6794144</v>
+        <v>6794049</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10431,45 +10421,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132814851</v>
+        <v>132814782</v>
       </c>
       <c r="B99" t="n">
-        <v>79333</v>
+        <v>8455</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>420801</v>
+        <v>420074</v>
       </c>
       <c r="R99" t="n">
-        <v>6794114</v>
+        <v>6793987</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10510,6 +10509,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10722,7 +10722,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132814749</v>
+        <v>132814751</v>
       </c>
       <c r="B102" t="n">
         <v>57145</v>
@@ -10755,7 +10755,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -10765,10 +10765,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>420604</v>
+        <v>420599</v>
       </c>
       <c r="R102" t="n">
-        <v>6794012</v>
+        <v>6794022</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10827,7 +10827,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132814751</v>
+        <v>132814749</v>
       </c>
       <c r="B103" t="n">
         <v>57145</v>
@@ -10860,7 +10860,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>420599</v>
+        <v>420604</v>
       </c>
       <c r="R103" t="n">
-        <v>6794022</v>
+        <v>6794012</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132814768</v>
+        <v>132814709</v>
       </c>
       <c r="B104" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10943,42 +10943,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>420900</v>
+        <v>420028</v>
       </c>
       <c r="R104" t="n">
-        <v>6794252</v>
+        <v>6793991</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11037,10 +11029,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132814859</v>
+        <v>132814777</v>
       </c>
       <c r="B105" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11048,21 +11040,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11072,10 +11064,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>420739</v>
+        <v>420706</v>
       </c>
       <c r="R105" t="n">
-        <v>6794114</v>
+        <v>6794078</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11134,10 +11126,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132814709</v>
+        <v>132814859</v>
       </c>
       <c r="B106" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11145,21 +11137,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11169,10 +11161,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>420028</v>
+        <v>420739</v>
       </c>
       <c r="R106" t="n">
-        <v>6793991</v>
+        <v>6794114</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11231,10 +11223,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132814777</v>
+        <v>132814768</v>
       </c>
       <c r="B107" t="n">
-        <v>79091</v>
+        <v>57955</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11242,34 +11234,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>420706</v>
+        <v>420900</v>
       </c>
       <c r="R107" t="n">
-        <v>6794078</v>
+        <v>6794252</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132814738</v>
+        <v>132814744</v>
       </c>
       <c r="B8" t="n">
         <v>57958</v>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420583</v>
+        <v>420576</v>
       </c>
       <c r="R8" t="n">
-        <v>6794016</v>
+        <v>6794051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132814744</v>
+        <v>132814738</v>
       </c>
       <c r="B9" t="n">
         <v>57958</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420576</v>
+        <v>420583</v>
       </c>
       <c r="R9" t="n">
-        <v>6794051</v>
+        <v>6794016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132814732</v>
+        <v>132814711</v>
       </c>
       <c r="B14" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,21 +1906,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>420740</v>
+        <v>420109</v>
       </c>
       <c r="R14" t="n">
-        <v>6794120</v>
+        <v>6793976</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,7 +1992,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132814711</v>
+        <v>132814712</v>
       </c>
       <c r="B15" t="n">
         <v>79952</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420109</v>
+        <v>420126</v>
       </c>
       <c r="R15" t="n">
-        <v>6793976</v>
+        <v>6793969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132814712</v>
+        <v>132814861</v>
       </c>
       <c r="B16" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420126</v>
+        <v>420752</v>
       </c>
       <c r="R16" t="n">
-        <v>6793969</v>
+        <v>6794099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132814861</v>
+        <v>132814761</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,34 +2197,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420752</v>
+        <v>420119</v>
       </c>
       <c r="R17" t="n">
-        <v>6794099</v>
+        <v>6794010</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2283,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132814860</v>
+        <v>132814762</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2294,34 +2302,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>420745</v>
+        <v>419986</v>
       </c>
       <c r="R18" t="n">
-        <v>6794098</v>
+        <v>6793995</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2380,7 +2396,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132814863</v>
+        <v>132814860</v>
       </c>
       <c r="B19" t="n">
         <v>79333</v>
@@ -2415,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>420725</v>
+        <v>420745</v>
       </c>
       <c r="R19" t="n">
-        <v>6794081</v>
+        <v>6794098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2477,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132814762</v>
+        <v>132814863</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,42 +2504,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419986</v>
+        <v>420725</v>
       </c>
       <c r="R20" t="n">
-        <v>6793995</v>
+        <v>6794081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132814761</v>
+        <v>132814792</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,16 +2601,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2615,7 +2623,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2625,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>420119</v>
+        <v>420554</v>
       </c>
       <c r="R21" t="n">
-        <v>6794010</v>
+        <v>6794096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,27 +2695,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132814792</v>
+        <v>132814773</v>
       </c>
       <c r="B22" t="n">
-        <v>57136</v>
+        <v>57148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2720,7 +2728,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2730,10 +2738,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>420554</v>
+        <v>420920</v>
       </c>
       <c r="R22" t="n">
-        <v>6794096</v>
+        <v>6794225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,53 +2800,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132814773</v>
+        <v>132814732</v>
       </c>
       <c r="B23" t="n">
-        <v>57148</v>
+        <v>79923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>420920</v>
+        <v>420740</v>
       </c>
       <c r="R23" t="n">
-        <v>6794225</v>
+        <v>6794120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132814715</v>
+        <v>132814865</v>
       </c>
       <c r="B24" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>420524</v>
+        <v>420586</v>
       </c>
       <c r="R24" t="n">
-        <v>6794233</v>
+        <v>6794106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132814865</v>
+        <v>132814715</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420586</v>
+        <v>420524</v>
       </c>
       <c r="R25" t="n">
-        <v>6794106</v>
+        <v>6794233</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132814706</v>
+        <v>132814832</v>
       </c>
       <c r="B28" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419997</v>
+        <v>419983</v>
       </c>
       <c r="R28" t="n">
-        <v>6793998</v>
+        <v>6793990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3402,7 +3402,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132814832</v>
+        <v>132814864</v>
       </c>
       <c r="B29" t="n">
         <v>79333</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419983</v>
+        <v>420690</v>
       </c>
       <c r="R29" t="n">
-        <v>6793990</v>
+        <v>6794088</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132814864</v>
+        <v>132814706</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>420690</v>
+        <v>419997</v>
       </c>
       <c r="R30" t="n">
-        <v>6794088</v>
+        <v>6793998</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132814828</v>
+        <v>132814769</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3906,34 +3906,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>420306</v>
+        <v>420899</v>
       </c>
       <c r="R34" t="n">
-        <v>6794101</v>
+        <v>6794245</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132814769</v>
+        <v>132814828</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4003,42 +4011,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>420899</v>
+        <v>420306</v>
       </c>
       <c r="R35" t="n">
-        <v>6794245</v>
+        <v>6794101</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132814741</v>
+        <v>132814740</v>
       </c>
       <c r="B36" t="n">
         <v>57958</v>
@@ -4140,10 +4140,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>420574</v>
+        <v>420104</v>
       </c>
       <c r="R36" t="n">
-        <v>6794086</v>
+        <v>6794033</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4202,7 +4202,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132814740</v>
+        <v>132814741</v>
       </c>
       <c r="B37" t="n">
         <v>57958</v>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>420104</v>
+        <v>420574</v>
       </c>
       <c r="R37" t="n">
-        <v>6794033</v>
+        <v>6794086</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4307,41 +4307,40 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132814788</v>
+        <v>132814767</v>
       </c>
       <c r="B38" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4351,10 +4350,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>420693</v>
+        <v>420588</v>
       </c>
       <c r="R38" t="n">
-        <v>6794082</v>
+        <v>6794046</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4395,7 +4394,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4414,41 +4412,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132814787</v>
+        <v>132814748</v>
       </c>
       <c r="B39" t="n">
-        <v>8455</v>
+        <v>57958</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4458,10 +4455,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>420878</v>
+        <v>420910</v>
       </c>
       <c r="R39" t="n">
-        <v>6794218</v>
+        <v>6794235</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,7 +4499,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4521,45 +4517,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132814713</v>
+        <v>132814788</v>
       </c>
       <c r="B40" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>420131</v>
+        <v>420693</v>
       </c>
       <c r="R40" t="n">
-        <v>6793962</v>
+        <v>6794082</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,6 +4605,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4618,45 +4624,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132814701</v>
+        <v>132814787</v>
       </c>
       <c r="B41" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>420311</v>
+        <v>420878</v>
       </c>
       <c r="R41" t="n">
-        <v>6794104</v>
+        <v>6794218</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,6 +4712,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4909,10 +4925,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132814767</v>
+        <v>132814713</v>
       </c>
       <c r="B44" t="n">
-        <v>57955</v>
+        <v>79952</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,42 +4936,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>420588</v>
+        <v>420131</v>
       </c>
       <c r="R44" t="n">
-        <v>6794046</v>
+        <v>6793962</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5014,10 +5022,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132814748</v>
+        <v>132814701</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>79952</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5025,42 +5033,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>420910</v>
+        <v>420311</v>
       </c>
       <c r="R45" t="n">
-        <v>6794235</v>
+        <v>6794104</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5313,10 +5313,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132814763</v>
+        <v>132814841</v>
       </c>
       <c r="B48" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5324,42 +5324,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>420057</v>
+        <v>420224</v>
       </c>
       <c r="R48" t="n">
-        <v>6793966</v>
+        <v>6793969</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5418,7 +5410,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132814841</v>
+        <v>132814843</v>
       </c>
       <c r="B49" t="n">
         <v>79333</v>
@@ -5453,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>420224</v>
+        <v>420223</v>
       </c>
       <c r="R49" t="n">
-        <v>6793969</v>
+        <v>6793998</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5515,10 +5507,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132814843</v>
+        <v>132814763</v>
       </c>
       <c r="B50" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5526,34 +5518,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>420223</v>
+        <v>420057</v>
       </c>
       <c r="R50" t="n">
-        <v>6793998</v>
+        <v>6793966</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132814718</v>
+        <v>132814848</v>
       </c>
       <c r="B52" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,21 +5730,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5754,10 +5754,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>420827</v>
+        <v>420528</v>
       </c>
       <c r="R52" t="n">
-        <v>6794180</v>
+        <v>6794160</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132814829</v>
+        <v>132814718</v>
       </c>
       <c r="B53" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>420188</v>
+        <v>420827</v>
       </c>
       <c r="R53" t="n">
-        <v>6794047</v>
+        <v>6794180</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132814759</v>
+        <v>132814829</v>
       </c>
       <c r="B54" t="n">
-        <v>91939</v>
+        <v>79333</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5924,37 +5924,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>420574</v>
+        <v>420188</v>
       </c>
       <c r="R54" t="n">
-        <v>6794086</v>
+        <v>6794047</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5995,7 +5992,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6014,10 +6010,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132814848</v>
+        <v>132814759</v>
       </c>
       <c r="B55" t="n">
-        <v>79333</v>
+        <v>91939</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6025,34 +6021,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>420528</v>
+        <v>420574</v>
       </c>
       <c r="R55" t="n">
-        <v>6794160</v>
+        <v>6794086</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6093,6 +6092,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6317,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132814837</v>
+        <v>132814853</v>
       </c>
       <c r="B58" t="n">
         <v>79333</v>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>420071</v>
+        <v>420890</v>
       </c>
       <c r="R58" t="n">
-        <v>6793979</v>
+        <v>6794166</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6414,7 +6414,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132814853</v>
+        <v>132814837</v>
       </c>
       <c r="B59" t="n">
         <v>79333</v>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>420890</v>
+        <v>420071</v>
       </c>
       <c r="R59" t="n">
-        <v>6794166</v>
+        <v>6793979</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6608,53 +6608,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132814750</v>
+        <v>132814856</v>
       </c>
       <c r="B61" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>420114</v>
+        <v>420936</v>
       </c>
       <c r="R61" t="n">
-        <v>6793974</v>
+        <v>6794205</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6810,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132814856</v>
+        <v>132814776</v>
       </c>
       <c r="B63" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6821,21 +6813,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6845,10 +6837,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>420936</v>
+        <v>420807</v>
       </c>
       <c r="R63" t="n">
-        <v>6794205</v>
+        <v>6794179</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,45 +6899,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132814776</v>
+        <v>132814750</v>
       </c>
       <c r="B64" t="n">
-        <v>79091</v>
+        <v>57145</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>420807</v>
+        <v>420114</v>
       </c>
       <c r="R64" t="n">
-        <v>6794179</v>
+        <v>6793974</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,54 +7004,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132814789</v>
+        <v>132814720</v>
       </c>
       <c r="B65" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>420681</v>
+        <v>420755</v>
       </c>
       <c r="R65" t="n">
-        <v>6794073</v>
+        <v>6794087</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7092,7 +7083,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7111,45 +7101,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132814720</v>
+        <v>132814789</v>
       </c>
       <c r="B66" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>420755</v>
+        <v>420681</v>
       </c>
       <c r="R66" t="n">
-        <v>6794087</v>
+        <v>6794073</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,6 +7189,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7208,45 +7208,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132814716</v>
+        <v>132814791</v>
       </c>
       <c r="B67" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>420748</v>
+        <v>420112</v>
       </c>
       <c r="R67" t="n">
-        <v>6794107</v>
+        <v>6793976</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7287,6 +7296,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7305,10 +7315,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132814719</v>
+        <v>132814730</v>
       </c>
       <c r="B68" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7316,21 +7326,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7340,10 +7350,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>420742</v>
+        <v>420787</v>
       </c>
       <c r="R68" t="n">
-        <v>6794108</v>
+        <v>6794163</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7402,10 +7412,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132814826</v>
+        <v>132814727</v>
       </c>
       <c r="B69" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7413,21 +7423,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7437,10 +7447,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>420418</v>
+        <v>420903</v>
       </c>
       <c r="R69" t="n">
-        <v>6794158</v>
+        <v>6794237</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7499,10 +7509,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132814766</v>
+        <v>132814794</v>
       </c>
       <c r="B70" t="n">
-        <v>57955</v>
+        <v>56522</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7510,21 +7520,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7532,7 +7542,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7542,10 +7552,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>420516</v>
+        <v>420170</v>
       </c>
       <c r="R70" t="n">
-        <v>6794196</v>
+        <v>6793954</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7604,54 +7614,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132814791</v>
+        <v>132814826</v>
       </c>
       <c r="B71" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>420112</v>
+        <v>420418</v>
       </c>
       <c r="R71" t="n">
-        <v>6793976</v>
+        <v>6794158</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7692,7 +7693,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132814730</v>
+        <v>132814716</v>
       </c>
       <c r="B72" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,21 +7722,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>420787</v>
+        <v>420748</v>
       </c>
       <c r="R72" t="n">
-        <v>6794163</v>
+        <v>6794107</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132814727</v>
+        <v>132814719</v>
       </c>
       <c r="B73" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7819,21 +7819,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>420903</v>
+        <v>420742</v>
       </c>
       <c r="R73" t="n">
-        <v>6794237</v>
+        <v>6794108</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132814794</v>
+        <v>132814766</v>
       </c>
       <c r="B74" t="n">
-        <v>56522</v>
+        <v>57955</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7916,21 +7916,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7938,7 +7938,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>420170</v>
+        <v>420516</v>
       </c>
       <c r="R74" t="n">
-        <v>6793954</v>
+        <v>6794196</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8010,45 +8010,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132814714</v>
+        <v>132814781</v>
       </c>
       <c r="B75" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>420233</v>
+        <v>420113</v>
       </c>
       <c r="R75" t="n">
-        <v>6793967</v>
+        <v>6794031</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8089,6 +8098,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8107,10 +8117,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132814845</v>
+        <v>132814775</v>
       </c>
       <c r="B76" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,34 +8128,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>420474</v>
+        <v>420905</v>
       </c>
       <c r="R76" t="n">
-        <v>6794142</v>
+        <v>6794232</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8186,6 +8199,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8204,10 +8218,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132814770</v>
+        <v>132814726</v>
       </c>
       <c r="B77" t="n">
-        <v>57955</v>
+        <v>79923</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8215,42 +8229,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>420758</v>
+        <v>420503</v>
       </c>
       <c r="R77" t="n">
-        <v>6794147</v>
+        <v>6794242</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8309,10 +8315,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132814775</v>
+        <v>132814845</v>
       </c>
       <c r="B78" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8320,37 +8326,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>420905</v>
+        <v>420474</v>
       </c>
       <c r="R78" t="n">
-        <v>6794232</v>
+        <v>6794142</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8391,7 +8394,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8410,10 +8412,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132814726</v>
+        <v>132814714</v>
       </c>
       <c r="B79" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8421,21 +8423,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8445,10 +8447,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>420503</v>
+        <v>420233</v>
       </c>
       <c r="R79" t="n">
-        <v>6794242</v>
+        <v>6793967</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8507,41 +8509,40 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132814781</v>
+        <v>132814770</v>
       </c>
       <c r="B80" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8551,10 +8552,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>420113</v>
+        <v>420758</v>
       </c>
       <c r="R80" t="n">
-        <v>6794031</v>
+        <v>6794147</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8595,7 +8596,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8614,54 +8614,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132814783</v>
+        <v>132814840</v>
       </c>
       <c r="B81" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>420406</v>
+        <v>420214</v>
       </c>
       <c r="R81" t="n">
-        <v>6794117</v>
+        <v>6793964</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8702,7 +8693,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8721,54 +8711,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132814779</v>
+        <v>132814830</v>
       </c>
       <c r="B82" t="n">
-        <v>8455</v>
+        <v>79333</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>420605</v>
+        <v>420156</v>
       </c>
       <c r="R82" t="n">
-        <v>6794008</v>
+        <v>6794036</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8809,7 +8790,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8828,37 +8808,43 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132814866</v>
+        <v>132814783</v>
       </c>
       <c r="B83" t="n">
-        <v>78340</v>
+        <v>8455</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6487</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8866,10 +8852,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>420768</v>
+        <v>420406</v>
       </c>
       <c r="R83" t="n">
-        <v>6794178</v>
+        <v>6794117</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8913,31 +8899,6 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -8954,45 +8915,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132814723</v>
+        <v>132814779</v>
       </c>
       <c r="B84" t="n">
-        <v>79952</v>
+        <v>8455</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>420646</v>
+        <v>420605</v>
       </c>
       <c r="R84" t="n">
-        <v>6794161</v>
+        <v>6794008</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9033,6 +9003,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9051,10 +9022,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132814840</v>
+        <v>132814866</v>
       </c>
       <c r="B85" t="n">
-        <v>79333</v>
+        <v>78340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9062,34 +9033,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>420214</v>
+        <v>420768</v>
       </c>
       <c r="R85" t="n">
-        <v>6793964</v>
+        <v>6794178</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9130,8 +9104,34 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9148,10 +9148,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132814830</v>
+        <v>132814723</v>
       </c>
       <c r="B86" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9159,21 +9159,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9183,10 +9183,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>420156</v>
+        <v>420646</v>
       </c>
       <c r="R86" t="n">
-        <v>6794036</v>
+        <v>6794161</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132814702</v>
+        <v>132814833</v>
       </c>
       <c r="B87" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,21 +9256,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>420119</v>
+        <v>419996</v>
       </c>
       <c r="R87" t="n">
-        <v>6794012</v>
+        <v>6793995</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132814850</v>
+        <v>132814702</v>
       </c>
       <c r="B88" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9353,21 +9353,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9377,10 +9377,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>420549</v>
+        <v>420119</v>
       </c>
       <c r="R88" t="n">
-        <v>6794103</v>
+        <v>6794012</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9439,7 +9439,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132814833</v>
+        <v>132814850</v>
       </c>
       <c r="B89" t="n">
         <v>79333</v>
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419996</v>
+        <v>420549</v>
       </c>
       <c r="R89" t="n">
-        <v>6793995</v>
+        <v>6794103</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132814735</v>
+        <v>132814836</v>
       </c>
       <c r="B92" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9741,37 +9741,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>420683</v>
+        <v>420025</v>
       </c>
       <c r="R92" t="n">
-        <v>6794145</v>
+        <v>6793989</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9812,7 +9809,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9831,10 +9827,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132814725</v>
+        <v>132814849</v>
       </c>
       <c r="B93" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9842,21 +9838,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9866,10 +9862,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>420114</v>
+        <v>420548</v>
       </c>
       <c r="R93" t="n">
-        <v>6793974</v>
+        <v>6794121</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9928,10 +9924,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132814836</v>
+        <v>132814735</v>
       </c>
       <c r="B94" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9939,34 +9935,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>420025</v>
+        <v>420683</v>
       </c>
       <c r="R94" t="n">
-        <v>6793989</v>
+        <v>6794145</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10007,6 +10006,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10025,10 +10025,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132814849</v>
+        <v>132814725</v>
       </c>
       <c r="B95" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10036,21 +10036,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>420548</v>
+        <v>420114</v>
       </c>
       <c r="R95" t="n">
-        <v>6794121</v>
+        <v>6793974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10316,10 +10316,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132814742</v>
+        <v>132814724</v>
       </c>
       <c r="B98" t="n">
-        <v>57958</v>
+        <v>79952</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10327,42 +10327,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>420570</v>
+        <v>420166</v>
       </c>
       <c r="R98" t="n">
-        <v>6794049</v>
+        <v>6793967</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10421,54 +10413,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132814782</v>
+        <v>132814721</v>
       </c>
       <c r="B99" t="n">
-        <v>8455</v>
+        <v>79952</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>420074</v>
+        <v>420709</v>
       </c>
       <c r="R99" t="n">
-        <v>6793987</v>
+        <v>6794077</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10509,7 +10492,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10528,45 +10510,53 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132814724</v>
+        <v>132814751</v>
       </c>
       <c r="B100" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>420166</v>
+        <v>420599</v>
       </c>
       <c r="R100" t="n">
-        <v>6793967</v>
+        <v>6794022</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10625,45 +10615,53 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132814721</v>
+        <v>132814749</v>
       </c>
       <c r="B101" t="n">
-        <v>79952</v>
+        <v>57145</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Floj, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>420709</v>
+        <v>420604</v>
       </c>
       <c r="R101" t="n">
-        <v>6794077</v>
+        <v>6794012</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10722,10 +10720,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132814751</v>
+        <v>132814782</v>
       </c>
       <c r="B102" t="n">
-        <v>57145</v>
+        <v>8455</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10733,29 +10731,30 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -10765,10 +10764,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>420599</v>
+        <v>420074</v>
       </c>
       <c r="R102" t="n">
-        <v>6794022</v>
+        <v>6793987</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10809,6 +10808,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10827,32 +10827,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132814749</v>
+        <v>132814742</v>
       </c>
       <c r="B103" t="n">
-        <v>57145</v>
+        <v>57958</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10860,7 +10860,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>420604</v>
+        <v>420570</v>
       </c>
       <c r="R103" t="n">
-        <v>6794012</v>
+        <v>6794049</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132814709</v>
+        <v>132814859</v>
       </c>
       <c r="B104" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10943,21 +10943,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10967,10 +10967,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>420028</v>
+        <v>420739</v>
       </c>
       <c r="R104" t="n">
-        <v>6793991</v>
+        <v>6794114</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11126,10 +11126,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132814859</v>
+        <v>132814709</v>
       </c>
       <c r="B106" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11137,21 +11137,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11161,10 +11161,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>420739</v>
+        <v>420028</v>
       </c>
       <c r="R106" t="n">
-        <v>6794114</v>
+        <v>6793991</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11748,7 +11748,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132814811</v>
+        <v>132814823</v>
       </c>
       <c r="B112" t="n">
         <v>57958</v>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>420631</v>
+        <v>420695</v>
       </c>
       <c r="R112" t="n">
-        <v>6794041</v>
+        <v>6794083</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11853,7 +11853,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132814823</v>
+        <v>132814811</v>
       </c>
       <c r="B113" t="n">
         <v>57958</v>
@@ -11896,10 +11896,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>420695</v>
+        <v>420631</v>
       </c>
       <c r="R113" t="n">
-        <v>6794083</v>
+        <v>6794041</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 15715-2026 artfynd.xlsx
+++ b/artfynd/A 15715-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AZ129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110769243</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814755</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814757</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814758</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814759</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814826</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814827</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814828</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814829</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814830</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814831</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814832</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814833</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814834</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814836</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814837</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814838</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814839</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814840</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814841</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814843</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814844</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814845</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3025,6 +3145,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814846</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814847</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3219,6 +3349,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814848</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3316,6 +3451,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814849</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3413,6 +3553,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814850</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3510,6 +3655,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814851</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3607,6 +3757,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814852</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3704,6 +3859,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814853</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3801,6 +3961,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814854</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3898,6 +4063,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814855</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3995,6 +4165,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814856</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4092,6 +4267,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814857</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4189,6 +4369,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814858</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4286,6 +4471,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814859</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4383,6 +4573,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814860</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4480,6 +4675,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814861</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4577,6 +4777,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814862</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4674,6 +4879,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814863</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4771,6 +4981,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814864</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4868,6 +5083,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814865</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4965,6 +5185,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814701</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5062,6 +5287,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814702</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5159,6 +5389,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814703</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5256,6 +5491,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814704</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5353,6 +5593,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814705</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5450,6 +5695,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814706</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5547,6 +5797,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814708</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5644,6 +5899,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814709</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5745,6 +6005,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814710</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5842,6 +6107,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814711</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5939,6 +6209,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814712</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6036,6 +6311,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814713</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6133,6 +6413,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814714</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6230,6 +6515,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814715</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6327,6 +6617,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814716</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6424,6 +6719,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814717</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6521,6 +6821,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814718</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6618,6 +6923,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814719</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6715,6 +7025,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814720</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6812,6 +7127,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814721</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6909,6 +7229,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814723</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7006,6 +7331,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814724</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7132,6 +7462,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814866</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7237,6 +7572,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814760</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7342,6 +7682,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814761</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7447,6 +7792,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814762</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7552,6 +7902,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814763</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7657,6 +8012,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814764</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7762,6 +8122,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814765</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7867,6 +8232,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814766</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7972,6 +8342,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814767</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8077,6 +8452,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814768</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8182,6 +8562,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814769</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8287,6 +8672,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814770</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8392,6 +8782,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814771</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8493,6 +8888,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814736</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8598,6 +8998,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814737</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8703,6 +9108,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814738</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8808,6 +9218,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814739</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8913,6 +9328,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814740</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9018,6 +9438,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814741</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9123,6 +9548,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814742</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9228,6 +9658,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814744</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9333,6 +9768,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814748</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9438,6 +9878,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814801</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9543,6 +9988,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814805</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9648,6 +10098,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814811</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9753,6 +10208,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814812</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9858,6 +10318,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814815</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9963,6 +10428,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814820</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10068,6 +10538,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814823</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10173,6 +10648,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814749</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10278,6 +10758,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814750</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10383,6 +10868,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814751</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10488,6 +10978,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814792</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10593,6 +11088,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814793</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10698,6 +11198,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814773</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10805,6 +11310,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814779</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10912,6 +11422,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814780</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11019,6 +11534,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814781</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11126,6 +11646,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814782</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11233,6 +11758,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814783</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11340,6 +11870,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814784</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11447,6 +11982,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814785</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11554,6 +12094,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814786</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11661,6 +12206,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814787</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11768,6 +12318,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814788</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11875,6 +12430,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814789</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11982,6 +12542,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814790</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12089,6 +12654,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814791</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12194,6 +12764,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814794</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12291,6 +12866,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814774</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12392,6 +12972,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814775</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12489,6 +13074,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814776</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12586,6 +13176,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814777</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12683,6 +13278,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814725</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12780,6 +13380,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814726</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12877,6 +13482,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814727</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12974,6 +13584,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814728</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13071,6 +13686,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814729</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13168,6 +13788,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814730</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13265,6 +13890,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814731</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13362,6 +13992,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814732</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13459,6 +14094,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814734</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13560,8 +14200,143 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132814735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>